--- a/Estudo-Rotas-RJ-Eficiencia.xlsx
+++ b/Estudo-Rotas-RJ-Eficiencia.xlsx
@@ -79,7 +79,7 @@
     <t>Cleide — PROPOSTA</t>
   </si>
   <si>
-    <t>10h25</t>
+    <t>10h45</t>
   </si>
   <si>
     <t>Lucas — HOJE</t>
@@ -94,7 +94,7 @@
     <t>Lucas — PROPOSTA</t>
   </si>
   <si>
-    <t>15h26</t>
+    <t>15h25</t>
   </si>
   <si>
     <t>Anderson — HOJE</t>
@@ -106,7 +106,7 @@
     <t>Anderson — PROPOSTA</t>
   </si>
   <si>
-    <t>14h31</t>
+    <t>14h10</t>
   </si>
   <si>
     <t>TOTAL (3 promotores)</t>
@@ -121,7 +121,7 @@
     <t>130 → 115</t>
   </si>
   <si>
-    <t>1524 → 1414 km</t>
+    <t>1524 → 1380 km</t>
   </si>
   <si>
     <t>10 → 8 (1 dia)</t>
@@ -130,7 +130,7 @@
     <t>O QUE MUDA (resumo executivo)</t>
   </si>
   <si>
-    <t>• TODO MUNDO roda menos: Cleide 434 → 391 km (-43), Anderson 509 → 481 (-28), Lucas 581 → 542 (-39). Total -110 km/sem (-7%).</t>
+    <t>• TODO MUNDO roda menos: Cleide 434 → 377 km (-57), Anderson 509 → 462 (-48), Lucas 581 → 542 (-39). Total -144 km/sem (-7%).</t>
   </si>
   <si>
     <t>• Cleide (ônibus): seg/qua/sex viram loops LOCAIS de Nova Iguaçu/Mesquita/Nilópolis (37-42 km); ter/qui/sáb = corredor Meriti→Caxias (ônibus direto Via Light/Dutra). Nunca mais de 6 lojas/dia. Adeus Tijuca.</t>
@@ -325,109 +325,121 @@
     <t>→</t>
   </si>
   <si>
+    <t>1h33</t>
+  </si>
+  <si>
+    <t>Terça</t>
+  </si>
+  <si>
+    <t>1h29</t>
+  </si>
+  <si>
+    <t>1h43</t>
+  </si>
+  <si>
+    <t>Quarta</t>
+  </si>
+  <si>
+    <t>2h06</t>
+  </si>
+  <si>
+    <t>1h17</t>
+  </si>
+  <si>
+    <t>Quinta</t>
+  </si>
+  <si>
     <t>2h20</t>
   </si>
   <si>
-    <t>Terça</t>
-  </si>
-  <si>
-    <t>1h29</t>
-  </si>
-  <si>
-    <t>1h19</t>
-  </si>
-  <si>
-    <t>Quarta</t>
-  </si>
-  <si>
-    <t>2h06</t>
-  </si>
-  <si>
-    <t>1h42</t>
-  </si>
-  <si>
-    <t>Quinta</t>
-  </si>
-  <si>
     <t>Sexta</t>
   </si>
   <si>
     <t>2h02</t>
   </si>
   <si>
+    <t>1h31</t>
+  </si>
+  <si>
+    <t>Sábado</t>
+  </si>
+  <si>
+    <t>1h53</t>
+  </si>
+  <si>
+    <t>2h21</t>
+  </si>
+  <si>
+    <t>SEMANA</t>
+  </si>
+  <si>
+    <t>Lucas (Moto)</t>
+  </si>
+  <si>
+    <t>2h44</t>
+  </si>
+  <si>
+    <t>2h26</t>
+  </si>
+  <si>
+    <t>2h47</t>
+  </si>
+  <si>
+    <t>2h42</t>
+  </si>
+  <si>
+    <t>2h38</t>
+  </si>
+  <si>
+    <t>2h27</t>
+  </si>
+  <si>
+    <t>2h40</t>
+  </si>
+  <si>
+    <t>2h45</t>
+  </si>
+  <si>
+    <t>2h36</t>
+  </si>
+  <si>
+    <t>2h33</t>
+  </si>
+  <si>
+    <t>2h32</t>
+  </si>
+  <si>
+    <t>Anderson (Moto)</t>
+  </si>
+  <si>
+    <t>2h35</t>
+  </si>
+  <si>
+    <t>2h39</t>
+  </si>
+  <si>
+    <t>2h46</t>
+  </si>
+  <si>
     <t>2h18</t>
   </si>
   <si>
-    <t>Sábado</t>
-  </si>
-  <si>
-    <t>1h53</t>
-  </si>
-  <si>
-    <t>1h27</t>
-  </si>
-  <si>
-    <t>SEMANA</t>
-  </si>
-  <si>
-    <t>Lucas (Moto)</t>
-  </si>
-  <si>
-    <t>2h44</t>
-  </si>
-  <si>
-    <t>2h26</t>
-  </si>
-  <si>
-    <t>2h47</t>
-  </si>
-  <si>
-    <t>2h42</t>
-  </si>
-  <si>
-    <t>2h38</t>
-  </si>
-  <si>
-    <t>2h35</t>
-  </si>
-  <si>
-    <t>2h40</t>
-  </si>
-  <si>
-    <t>2h45</t>
-  </si>
-  <si>
-    <t>2h36</t>
-  </si>
-  <si>
-    <t>2h32</t>
-  </si>
-  <si>
-    <t>Anderson (Moto)</t>
-  </si>
-  <si>
-    <t>2h49</t>
-  </si>
-  <si>
-    <t>2h46</t>
-  </si>
-  <si>
-    <t>2h33</t>
-  </si>
-  <si>
     <t>1h41</t>
   </si>
   <si>
     <t>2h53</t>
   </si>
   <si>
-    <t>2h16</t>
+    <t>1h21</t>
+  </si>
+  <si>
+    <t>2h52</t>
   </si>
   <si>
     <t>3h07</t>
   </si>
   <si>
-    <t>1h36</t>
+    <t>2h15</t>
   </si>
   <si>
     <t>Cleide de Oliveira Lira — ROTA PROPOSTA (Ônibus)</t>
@@ -436,7 +448,7 @@
     <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (carro, referência — ela roda de ônibus)</t>
   </si>
   <si>
-    <t>SEGUNDA — 6 lojas · 94.7 km · 2h20</t>
+    <t>SEGUNDA — 6 lojas · 41.3 km · 1h33</t>
   </si>
   <si>
     <t>#</t>
@@ -463,378 +475,363 @@
     <t>Rosa dos Ventos</t>
   </si>
   <si>
+    <t>ASSAÍ NOVA IGUAÇU VIA LIGHT - 291 - RJ</t>
+  </si>
+  <si>
+    <t>Santa Eugenia</t>
+  </si>
+  <si>
+    <t>16 min</t>
+  </si>
+  <si>
+    <t>Jardim Tropical</t>
+  </si>
+  <si>
+    <t>15 min</t>
+  </si>
+  <si>
     <t>ASSAÍ MESQUITA - 142 - RJ</t>
   </si>
   <si>
     <t>Jacutinga</t>
   </si>
   <si>
-    <t>16 min</t>
+    <t>7 min</t>
+  </si>
+  <si>
+    <t>Bairro Industrial</t>
+  </si>
+  <si>
+    <t>1 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ NILÓPOLIS - 36 - RJ</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>18 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ NOVA IGUAÇU - 30 - RJ</t>
+  </si>
+  <si>
+    <t>CASA (volta)</t>
+  </si>
+  <si>
+    <t>19 min</t>
+  </si>
+  <si>
+    <t>TERÇA — 6 lojas · 64.3 km · 1h43</t>
+  </si>
+  <si>
+    <t>Piam</t>
+  </si>
+  <si>
+    <t>25 min</t>
+  </si>
+  <si>
+    <t>São Bento</t>
+  </si>
+  <si>
+    <t>23 min</t>
   </si>
   <si>
     <t>Vila Centenario</t>
   </si>
   <si>
+    <t>11 min</t>
+  </si>
+  <si>
+    <t>Vila Meriti</t>
+  </si>
+  <si>
+    <t>5 min</t>
+  </si>
+  <si>
+    <t>Venda Velha</t>
+  </si>
+  <si>
+    <t>13 min</t>
+  </si>
+  <si>
+    <t>2 min</t>
+  </si>
+  <si>
+    <t>24 min</t>
+  </si>
+  <si>
+    <t>QUARTA — 5 lojas · 36.9 km · 1h17</t>
+  </si>
+  <si>
+    <t>6 min</t>
+  </si>
+  <si>
+    <t>29 min</t>
+  </si>
+  <si>
+    <t>QUINTA — 6 lojas · 95 km · 2h20</t>
+  </si>
+  <si>
+    <t>22 min</t>
+  </si>
+  <si>
+    <t>Vila São Luis</t>
+  </si>
+  <si>
+    <t>14 min</t>
+  </si>
+  <si>
+    <t>Santa Cruz da Serra</t>
+  </si>
+  <si>
+    <t>SEXTA — 6 lojas · 41.1 km · 1h31</t>
+  </si>
+  <si>
+    <t>PREZUNIC NILÓPOLIS</t>
+  </si>
+  <si>
+    <t>SÁBADO — 6 lojas · 98.1 km · 2h21</t>
+  </si>
+  <si>
+    <t>45 min</t>
+  </si>
+  <si>
+    <t>Lucas Braz Monassa Vidal de Negreiros — ROTA PROPOSTA (Moto)</t>
+  </si>
+  <si>
+    <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (moto)</t>
+  </si>
+  <si>
+    <t>SEGUNDA — 5 lojas · 83 km · 2h26</t>
+  </si>
+  <si>
+    <t>ASSAÍ CEASA - 42 - RJ</t>
+  </si>
+  <si>
+    <t>Irajá</t>
+  </si>
+  <si>
+    <t>37 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ CAMPINHO - 37 - RJ</t>
+  </si>
+  <si>
+    <t>Campinho</t>
+  </si>
+  <si>
+    <t>ASSAÍ MEIER - 160 - RJ</t>
+  </si>
+  <si>
+    <t>Méier</t>
+  </si>
+  <si>
+    <t>ASSAÍ PILARES - 128 - RJ</t>
+  </si>
+  <si>
+    <t>Pilares</t>
+  </si>
+  <si>
+    <t>10 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ CARIOCA - 316 - RJ</t>
+  </si>
+  <si>
+    <t>Vila da Penha</t>
+  </si>
+  <si>
+    <t>TERÇA — 7 lojas · 96.9 km · 2h42</t>
+  </si>
+  <si>
+    <t>ASSAÍ CORDOVIL - 231 - RJ</t>
+  </si>
+  <si>
+    <t>Cordovil</t>
+  </si>
+  <si>
+    <t>38 min</t>
+  </si>
+  <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
+    <t>Tijuca</t>
+  </si>
+  <si>
+    <t>Vila Isabel</t>
+  </si>
+  <si>
+    <t>Inhaúma</t>
+  </si>
+  <si>
     <t>20 min</t>
   </si>
   <si>
-    <t>Vila São Luis</t>
-  </si>
-  <si>
-    <t>14 min</t>
-  </si>
-  <si>
-    <t>Santa Cruz da Serra</t>
-  </si>
-  <si>
-    <t>18 min</t>
-  </si>
-  <si>
-    <t>São Bento</t>
-  </si>
-  <si>
-    <t>22 min</t>
-  </si>
-  <si>
-    <t>Piam</t>
-  </si>
-  <si>
-    <t>25 min</t>
-  </si>
-  <si>
-    <t>CASA (volta)</t>
-  </si>
-  <si>
-    <t>TERÇA — 6 lojas · 47.4 km · 1h19</t>
-  </si>
-  <si>
-    <t>ASSAÍ NOVA IGUAÇU VIA LIGHT - 291 - RJ</t>
-  </si>
-  <si>
-    <t>Santa Eugenia</t>
-  </si>
-  <si>
-    <t>ASSAÍ NOVA IGUAÇU - 30 - RJ</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>6 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ NILÓPOLIS - 36 - RJ</t>
-  </si>
-  <si>
-    <t>13 min</t>
+    <t>51 min</t>
+  </si>
+  <si>
+    <t>QUARTA — 7 lojas · 82.9 km · 2h27</t>
+  </si>
+  <si>
+    <t>PREZUNIC VISTA ALEGRE</t>
+  </si>
+  <si>
+    <t>Vista Alegre</t>
+  </si>
+  <si>
+    <t>36 min</t>
   </si>
   <si>
     <t>17 min</t>
   </si>
   <si>
-    <t>Venda Velha</t>
+    <t>PREZUNIC MÉIER</t>
+  </si>
+  <si>
+    <t>QUINTA — 7 lojas · 97.8 km · 2h45</t>
+  </si>
+  <si>
+    <t>4 min</t>
+  </si>
+  <si>
+    <t>8 min</t>
+  </si>
+  <si>
+    <t>SEXTA — 6 lojas · 85.1 km · 2h33</t>
+  </si>
+  <si>
+    <t>PREZUNIC CAMPINHO</t>
+  </si>
+  <si>
+    <t>SÁBADO — 6 lojas · 96 km · 2h32</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>53 min</t>
+  </si>
+  <si>
+    <t>Anderson Camilo Supeleto — ROTA PROPOSTA (Moto)</t>
+  </si>
+  <si>
+    <t>Saída: Est. do Pré, 674 - Campo Grande, Rio de Janeiro - RJ, 23013-550 · km/tempo por trecho = Google (moto)</t>
+  </si>
+  <si>
+    <t>SEGUNDA — 6 lojas · 91.8 km · 2h39</t>
+  </si>
+  <si>
+    <t>Campo Grande</t>
+  </si>
+  <si>
+    <t>Realengo</t>
+  </si>
+  <si>
+    <t>ASSAÍ JACAREPAGUÁ MERCADÃO - 340 - RJ</t>
+  </si>
+  <si>
+    <t>Taquara</t>
+  </si>
+  <si>
+    <t>ASSAÍ AYRTON SENNA - 133 - RJ</t>
+  </si>
+  <si>
+    <t>Jacarepaguá</t>
+  </si>
+  <si>
+    <t>PREZUNIC BARRA MARAPENDI</t>
+  </si>
+  <si>
+    <t>Barra da Tijuca</t>
+  </si>
+  <si>
+    <t>12 min</t>
+  </si>
+  <si>
+    <t>PREZUNIC JARDIM OCEÂNICO</t>
+  </si>
+  <si>
+    <t>ASSAÍ BARRA DA TIJUCA - 245 - RJ</t>
+  </si>
+  <si>
+    <t>63 min</t>
+  </si>
+  <si>
+    <t>TERÇA — 8 lojas · 73.2 km · 2h18</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>28 min</t>
+  </si>
+  <si>
+    <t>PREZUNIC SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>ASSAÍ SANTA CRUZ - 201 - RJ</t>
+  </si>
+  <si>
+    <t>Bangu</t>
+  </si>
+  <si>
+    <t>ASSAÍ BANGU - 55 - RJ</t>
+  </si>
+  <si>
+    <t>QUARTA — 5 lojas · 95 km · 2h45</t>
+  </si>
+  <si>
+    <t>68 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ FREGUESIA 28 - RJ</t>
+  </si>
+  <si>
+    <t>Freguesia (Jacarepaguá)</t>
+  </si>
+  <si>
+    <t>DOM TAQUARA</t>
+  </si>
+  <si>
+    <t>QUINTA — 8 lojas · 37.7 km · 1h21</t>
+  </si>
+  <si>
+    <t>PREZUNIC TINGUÍ</t>
+  </si>
+  <si>
+    <t>PREZUNIC SENADOR CAMARÁ</t>
+  </si>
+  <si>
+    <t>Senador Camará</t>
+  </si>
+  <si>
+    <t>9 min</t>
+  </si>
+  <si>
+    <t>PREZUNIC CAMPO GRANDE</t>
+  </si>
+  <si>
+    <t>SEXTA — 7 lojas · 91.4 km · 2h52</t>
+  </si>
+  <si>
+    <t>33 min</t>
+  </si>
+  <si>
+    <t>PREZUNIC FREGUESIA</t>
   </si>
   <si>
     <t>3 min</t>
   </si>
   <si>
-    <t>Jardim Tropical</t>
-  </si>
-  <si>
-    <t>9 min</t>
-  </si>
-  <si>
-    <t>15 min</t>
-  </si>
-  <si>
-    <t>QUARTA — 6 lojas · 64.6 km · 1h42</t>
-  </si>
-  <si>
-    <t>Bairro Industrial</t>
-  </si>
-  <si>
-    <t>1 min</t>
-  </si>
-  <si>
-    <t>12 min</t>
-  </si>
-  <si>
-    <t>23 min</t>
-  </si>
-  <si>
-    <t>11 min</t>
-  </si>
-  <si>
-    <t>Vila Meriti</t>
-  </si>
-  <si>
-    <t>5 min</t>
-  </si>
-  <si>
-    <t>33 min</t>
-  </si>
-  <si>
-    <t>QUINTA — 6 lojas · 47.4 km · 1h19</t>
-  </si>
-  <si>
-    <t>SEXTA — 6 lojas · 92.9 km · 2h18</t>
-  </si>
-  <si>
-    <t>31 min</t>
-  </si>
-  <si>
-    <t>35 min</t>
-  </si>
-  <si>
-    <t>SÁBADO — 5 lojas · 44.4 km · 1h27</t>
-  </si>
-  <si>
-    <t>PREZUNIC NILÓPOLIS</t>
-  </si>
-  <si>
-    <t>21 min</t>
-  </si>
-  <si>
-    <t>29 min</t>
-  </si>
-  <si>
-    <t>Lucas Braz Monassa Vidal de Negreiros — ROTA PROPOSTA (Moto)</t>
-  </si>
-  <si>
-    <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (moto)</t>
-  </si>
-  <si>
-    <t>SEGUNDA — 5 lojas · 83 km · 2h26</t>
-  </si>
-  <si>
-    <t>ASSAÍ CEASA - 42 - RJ</t>
-  </si>
-  <si>
-    <t>Irajá</t>
-  </si>
-  <si>
-    <t>37 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ CAMPINHO - 37 - RJ</t>
-  </si>
-  <si>
-    <t>Campinho</t>
-  </si>
-  <si>
-    <t>19 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ MEIER - 160 - RJ</t>
-  </si>
-  <si>
-    <t>Méier</t>
-  </si>
-  <si>
-    <t>ASSAÍ PILARES - 128 - RJ</t>
-  </si>
-  <si>
-    <t>Pilares</t>
-  </si>
-  <si>
-    <t>10 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ CARIOCA - 316 - RJ</t>
-  </si>
-  <si>
-    <t>Vila da Penha</t>
-  </si>
-  <si>
-    <t>45 min</t>
-  </si>
-  <si>
-    <t>TERÇA — 7 lojas · 96.9 km · 2h42</t>
-  </si>
-  <si>
-    <t>ASSAÍ CORDOVIL - 231 - RJ</t>
-  </si>
-  <si>
-    <t>Cordovil</t>
-  </si>
-  <si>
-    <t>38 min</t>
-  </si>
-  <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
-    <t>Tijuca</t>
-  </si>
-  <si>
-    <t>Vila Isabel</t>
-  </si>
-  <si>
-    <t>Inhaúma</t>
-  </si>
-  <si>
-    <t>51 min</t>
-  </si>
-  <si>
-    <t>QUARTA — 7 lojas · 85.3 km · 2h35</t>
-  </si>
-  <si>
-    <t>PREZUNIC VISTA ALEGRE</t>
-  </si>
-  <si>
-    <t>Vista Alegre</t>
-  </si>
-  <si>
-    <t>36 min</t>
-  </si>
-  <si>
-    <t>PREZUNIC CAMPINHO</t>
-  </si>
-  <si>
-    <t>2 min</t>
-  </si>
-  <si>
-    <t>24 min</t>
-  </si>
-  <si>
-    <t>QUINTA — 7 lojas · 97.8 km · 2h45</t>
-  </si>
-  <si>
-    <t>4 min</t>
-  </si>
-  <si>
-    <t>8 min</t>
-  </si>
-  <si>
-    <t>SEXTA — 6 lojas · 82.6 km · 2h26</t>
-  </si>
-  <si>
-    <t>PREZUNIC MÉIER</t>
-  </si>
-  <si>
-    <t>SÁBADO — 6 lojas · 96 km · 2h32</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>53 min</t>
-  </si>
-  <si>
-    <t>Anderson Camilo Supeleto — ROTA PROPOSTA (Moto)</t>
-  </si>
-  <si>
-    <t>Saída: Est. do Pré, 674 - Campo Grande, Rio de Janeiro - RJ, 23013-550 · km/tempo por trecho = Google (moto)</t>
-  </si>
-  <si>
-    <t>SEGUNDA — 6 lojas · 97.5 km · 2h49</t>
-  </si>
-  <si>
-    <t>Campo Grande</t>
-  </si>
-  <si>
-    <t>PREZUNIC JARDIM OCEÂNICO</t>
-  </si>
-  <si>
-    <t>Barra da Tijuca</t>
-  </si>
-  <si>
-    <t>68 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ BARRA DA TIJUCA - 245 - RJ</t>
-  </si>
-  <si>
-    <t>ASSAÍ AYRTON SENNA - 133 - RJ</t>
-  </si>
-  <si>
-    <t>Jacarepaguá</t>
-  </si>
-  <si>
-    <t>ASSAÍ FREGUESIA 28 - RJ</t>
-  </si>
-  <si>
-    <t>Freguesia (Jacarepaguá)</t>
-  </si>
-  <si>
-    <t>PREZUNIC FREGUESIA</t>
-  </si>
-  <si>
-    <t>ASSAÍ JACAREPAGUÁ MERCADÃO - 340 - RJ</t>
-  </si>
-  <si>
-    <t>Taquara</t>
-  </si>
-  <si>
-    <t>54 min</t>
-  </si>
-  <si>
-    <t>TERÇA — 9 lojas · 79.4 km · 2h33</t>
-  </si>
-  <si>
-    <t>ASSAÍ BANGU - 55 - RJ</t>
-  </si>
-  <si>
-    <t>Bangu</t>
-  </si>
-  <si>
-    <t>Realengo</t>
-  </si>
-  <si>
-    <t>ASSAÍ SANTA CRUZ - 201 - RJ</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>PREZUNIC SANTA CRUZ</t>
-  </si>
-  <si>
-    <t>32 min</t>
-  </si>
-  <si>
-    <t>QUARTA — 5 lojas · 95 km · 2h45</t>
-  </si>
-  <si>
-    <t>DOM TAQUARA</t>
-  </si>
-  <si>
-    <t>7 min</t>
-  </si>
-  <si>
-    <t>QUINTA — 9 lojas · 72.5 km · 2h16</t>
-  </si>
-  <si>
-    <t>28 min</t>
+    <t>SÁBADO — 8 lojas · 72.4 km · 2h15</t>
   </si>
   <si>
     <t>27 min</t>
   </si>
   <si>
-    <t>PREZUNIC SENADOR CAMARÁ</t>
-  </si>
-  <si>
-    <t>Senador Camará</t>
-  </si>
-  <si>
-    <t>SEXTA — 5 lojas · 89.6 km · 2h32</t>
-  </si>
-  <si>
-    <t>PREZUNIC BARRA MARAPENDI</t>
-  </si>
-  <si>
-    <t>58 min</t>
-  </si>
-  <si>
-    <t>SÁBADO — 8 lojas · 46.9 km · 1h36</t>
-  </si>
-  <si>
-    <t>PREZUNIC CAMPO GRANDE</t>
-  </si>
-  <si>
-    <t>PREZUNIC TINGUÍ</t>
-  </si>
-  <si>
     <t>TODAS AS LOJAS — DE/PARA (promotor, frequência e dias)</t>
   </si>
   <si>
@@ -937,99 +934,99 @@
     <t>Ter/Qui</t>
   </si>
   <si>
+    <t>Qua/Sex</t>
+  </si>
+  <si>
+    <t>Estr. dos Bandeirantes, 1430 - Taquara, Rio de Janeiro - RJ, 22710-310</t>
+  </si>
+  <si>
+    <t>Av. Maracanã, 1188 - Tijuca, Rio de Janeiro - RJ, 20511-001</t>
+  </si>
+  <si>
+    <t>R. Mariz e Barros, 975 - Tijuca, Rio de Janeiro - RJ, 20270-004</t>
+  </si>
+  <si>
+    <t>Estr. do Mendanha, 3457 - Campo Grande, Rio de Janeiro - RJ, 23092-001</t>
+  </si>
+  <si>
+    <t>R. Dias da Cruz, 371 - Méier, Rio de Janeiro - RJ, 20720-010</t>
+  </si>
+  <si>
+    <t>BAIXADA</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 10521 - Jacutinga, Mesquita - RJ, 26574-751</t>
+  </si>
+  <si>
+    <t>Av. Getúlio de Moura, 1983 - Centro, Nilópolis - RJ, 26525-002</t>
+  </si>
+  <si>
+    <t>Av. Mal. Floriano Peixoto, 1448 - Centro, Nova Iguaçu - RJ, 26220-060</t>
+  </si>
+  <si>
+    <t>Av. Tancredo Neves, 3424 - Santa Eugenia, Nova Iguaçu - RJ, 26285-002</t>
+  </si>
+  <si>
+    <t>Av. Dom Hélder Câmara, 6350 - Pilares, Rio de Janeiro - RJ, 20771-001</t>
+  </si>
+  <si>
+    <t>Av. Brasil, 2251 - Vasco da Gama, Rio de Janeiro - RJ, 20930-041</t>
+  </si>
+  <si>
+    <t>Av. Padre Guilherme Decaminada, 2385 - Santa Cruz, Rio de Janeiro - RJ, 23575-000</t>
+  </si>
+  <si>
+    <t>Seg/Sex</t>
+  </si>
+  <si>
+    <t>Ter/Sáb</t>
+  </si>
+  <si>
+    <t>Estr. da Pedra, 2.500 - Santa Cruz, Rio de Janeiro - RJ, 23520-241</t>
+  </si>
+  <si>
+    <t>Seg/Sex/Sáb</t>
+  </si>
+  <si>
+    <t>MERITI</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 4301 - Centro, São João de Meriti - RJ, 25515-230</t>
+  </si>
+  <si>
+    <t>Av. Brasil, 32238 - Bangu, Rio de Janeiro - RJ, 21863-000</t>
+  </si>
+  <si>
+    <t>Av. Joaquim da Costa Lima, 2009 - Piam, Belford Roxo - RJ, 26183-000</t>
+  </si>
+  <si>
+    <t>Av. de Santa Cruz, Avenue, 12,516 - Campo Grande, Rio de Janeiro - RJ, 23010-002</t>
+  </si>
+  <si>
+    <t>Qui/Sáb</t>
+  </si>
+  <si>
+    <t>Rod. Washington Luiz, 3853 - Vila São Luis, Duque de Caxias - RJ, 25065-135</t>
+  </si>
+  <si>
+    <t>Avenida Automóvel Clube QUADRA37L - LOTE 489 - Santa Cruz da Serra, Duque de Caxias - RJ, 25267-135</t>
+  </si>
+  <si>
+    <t>Av. Itaóca, 2650 - Inhaúma, Rio de Janeiro - RJ, 21061-770</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 10201B - Bairro Industrial, Mesquita - RJ, 26574-751</t>
+  </si>
+  <si>
     <t>Seg/Qua</t>
   </si>
   <si>
-    <t>Estr. dos Bandeirantes, 1430 - Taquara, Rio de Janeiro - RJ, 22710-310</t>
-  </si>
-  <si>
-    <t>Av. Maracanã, 1188 - Tijuca, Rio de Janeiro - RJ, 20511-001</t>
-  </si>
-  <si>
-    <t>R. Mariz e Barros, 975 - Tijuca, Rio de Janeiro - RJ, 20270-004</t>
-  </si>
-  <si>
-    <t>Estr. do Mendanha, 3457 - Campo Grande, Rio de Janeiro - RJ, 23092-001</t>
-  </si>
-  <si>
-    <t>R. Dias da Cruz, 371 - Méier, Rio de Janeiro - RJ, 20720-010</t>
-  </si>
-  <si>
-    <t>BAIXADA</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 10521 - Jacutinga, Mesquita - RJ, 26574-751</t>
-  </si>
-  <si>
-    <t>Av. Getúlio de Moura, 1983 - Centro, Nilópolis - RJ, 26525-002</t>
-  </si>
-  <si>
-    <t>Av. Mal. Floriano Peixoto, 1448 - Centro, Nova Iguaçu - RJ, 26220-060</t>
-  </si>
-  <si>
-    <t>Av. Tancredo Neves, 3424 - Santa Eugenia, Nova Iguaçu - RJ, 26285-002</t>
-  </si>
-  <si>
-    <t>Av. Dom Hélder Câmara, 6350 - Pilares, Rio de Janeiro - RJ, 20771-001</t>
-  </si>
-  <si>
-    <t>Av. Brasil, 2251 - Vasco da Gama, Rio de Janeiro - RJ, 20930-041</t>
-  </si>
-  <si>
-    <t>Av. Padre Guilherme Decaminada, 2385 - Santa Cruz, Rio de Janeiro - RJ, 23575-000</t>
-  </si>
-  <si>
-    <t>Seg/Sex</t>
-  </si>
-  <si>
-    <t>Estr. da Pedra, 2.500 - Santa Cruz, Rio de Janeiro - RJ, 23520-241</t>
-  </si>
-  <si>
-    <t>Seg/Sex/Sáb</t>
-  </si>
-  <si>
-    <t>MERITI</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 4301 - Centro, São João de Meriti - RJ, 25515-230</t>
-  </si>
-  <si>
-    <t>Av. Brasil, 32238 - Bangu, Rio de Janeiro - RJ, 21863-000</t>
-  </si>
-  <si>
-    <t>Av. Joaquim da Costa Lima, 2009 - Piam, Belford Roxo - RJ, 26183-000</t>
-  </si>
-  <si>
-    <t>Av. de Santa Cruz, Avenue, 12,516 - Campo Grande, Rio de Janeiro - RJ, 23010-002</t>
-  </si>
-  <si>
-    <t>Qui/Sáb</t>
-  </si>
-  <si>
-    <t>Rod. Washington Luiz, 3853 - Vila São Luis, Duque de Caxias - RJ, 25065-135</t>
-  </si>
-  <si>
-    <t>Avenida Automóvel Clube QUADRA37L - LOTE 489 - Santa Cruz da Serra, Duque de Caxias - RJ, 25267-135</t>
-  </si>
-  <si>
-    <t>Av. Itaóca, 2650 - Inhaúma, Rio de Janeiro - RJ, 21061-770</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 10201B - Bairro Industrial, Mesquita - RJ, 26574-751</t>
-  </si>
-  <si>
-    <t>Qua/Sex</t>
-  </si>
-  <si>
     <t>Rod. Pres. Dutra, 13900 - Jardim Tropical, Nova Iguaçu - RJ, 26015-005</t>
   </si>
   <si>
     <t>Estr. Gen. Canrobert Pereira da Costa, 203 - Realengo, Rio de Janeiro - RJ, 21710-400</t>
   </si>
   <si>
-    <t>Ter/Sáb</t>
-  </si>
-  <si>
     <t>R. Maria Soares Sendas, 4200 - Venda Velha, São João de Meriti - RJ, 25575-825</t>
   </si>
   <si>
@@ -1045,36 +1042,36 @@
     <t>Ter</t>
   </si>
   <si>
+    <t>Seg</t>
+  </si>
+  <si>
+    <t>Av. Dom Hélder Câmara, 105 - Benfica, Rio de Janeiro - RJ, 20911-291</t>
+  </si>
+  <si>
+    <t>Qua</t>
+  </si>
+  <si>
+    <t>Sáb</t>
+  </si>
+  <si>
+    <t>R. Cândido Benício, 20 - Campinho, Rio de Janeiro - RJ, 21320-060</t>
+  </si>
+  <si>
     <t>Sex</t>
   </si>
   <si>
-    <t>Av. Dom Hélder Câmara, 105 - Benfica, Rio de Janeiro - RJ, 20911-291</t>
-  </si>
-  <si>
-    <t>Qua</t>
-  </si>
-  <si>
-    <t>Sáb</t>
-  </si>
-  <si>
-    <t>R. Cândido Benício, 20 - Campinho, Rio de Janeiro - RJ, 21320-060</t>
-  </si>
-  <si>
-    <t>Seg</t>
-  </si>
-  <si>
     <t>Est. do Cabuçu, 1654 - Campo Grande, Rio de Janeiro - RJ, 23052-230</t>
   </si>
   <si>
+    <t>Qui</t>
+  </si>
+  <si>
     <t>R. Dr. Manoel Reis, 175 - Vila Meriti, Duque de Caxias - RJ, 25025-010</t>
   </si>
   <si>
     <t>Estr. de Jacarepaguá, 7153 - Freguesia (Jacarepaguá), Rio de Janeiro - RJ, 22753-033</t>
   </si>
   <si>
-    <t>Qui</t>
-  </si>
-  <si>
     <t>Av. Rodolfo Amoedo, 347 - Barra da Tijuca, Rio de Janeiro - RJ, 22620-350</t>
   </si>
   <si>
@@ -1114,19 +1111,22 @@
     <t>Link (Casa → paradas → Casa)</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.769066,-43.410775%7C-22.775841,-43.308631%7C-22.781013,-43.286252%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.747852,-43.392257&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.761935,-43.445172%7C-22.804718,-43.418825%7C-22.799075,-43.357408%7C-22.798746,-43.354000%7C-22.754258,-43.433102&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.747852,-43.392257%7C-22.726211,-43.313020%7C-22.775841,-43.308631%7C-22.780278,-43.310000&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.726211,-43.313020%7C-22.641768,-43.277839%7C-22.781013,-43.286252%7C-22.775841,-43.308631&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.761935,-43.445172%7C-22.799075,-43.357408%7C-22.807575,-43.416172%7C-22.804718,-43.418825&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.747852,-43.392257%7C-22.726211,-43.313020%7C-22.775841,-43.308631%7C-22.780278,-43.310000%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.761935,-43.445172%7C-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.804718,-43.418825&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.799075,-43.357408%7C-22.775841,-43.308631%7C-22.781013,-43.286252%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.747852,-43.392257&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.807575,-43.416172%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.726211,-43.313020%7C-22.641768,-43.277839%7C-22.781013,-43.286252%7C-22.775841,-43.308631%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
   </si>
   <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.881347,-43.342096%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
@@ -1135,34 +1135,34 @@
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.914747,-43.241269%7C-22.871506,-43.277717&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.834535,-43.318511%7C-22.881347,-43.342096%7C-22.883440,-43.343393%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358%7C-22.827684,-43.338882&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.834535,-43.318511%7C-22.881347,-43.342096%7C-22.905431,-43.291154%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358%7C-22.827684,-43.338882&amp;travelmode=driving</t>
   </si>
   <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.930622,-43.242526%7C-22.919957,-43.244485%7C-22.871506,-43.277717&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.881347,-43.342096%7C-22.905431,-43.291154%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.881347,-43.342096%7C-22.883440,-43.343393%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
   </si>
   <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.892195,-43.241108&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-23.008411,-43.316903%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.941113,-43.343251%7C-22.945679,-43.340096%7C-22.935560,-43.372767&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.879019,-43.465396%7C-22.877465,-43.422793%7C-22.858758,-43.460071%7C-22.856798,-43.477684%7C-22.863251,-43.549364%7C-22.891011,-43.676538%7C-22.915624,-43.682502%7C-22.950972,-43.652551%7C-22.906919,-43.564898&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.935560,-43.372767%7C-22.959146,-43.356197%7C-23.000610,-43.356417%7C-23.008411,-43.316903%7C-23.001891,-43.323279&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.915624,-43.682502%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396&amp;travelmode=driving</t>
   </si>
   <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.941113,-43.343251%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.882288,-43.488152%7C-22.893845,-43.534011&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-23.000610,-43.356417%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.913861,-43.544483%7C-22.893845,-43.534011%7C-22.879019,-43.465396%7C-22.877465,-43.422793%7C-22.856798,-43.477684%7C-22.863251,-43.549364%7C-22.884020,-43.575133%7C-22.906919,-43.564898&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.884020,-43.575133%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.879019,-43.465396%7C-22.882288,-43.488152%7C-22.893845,-43.534011%7C-22.913861,-43.544483&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.941113,-43.343251%7C-22.945679,-43.340096%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.893845,-43.534011&amp;travelmode=driving</t>
   </si>
 </sst>
 </file>
@@ -1800,7 +1800,7 @@
         <v>35</v>
       </c>
       <c r="E14" s="6">
-        <v>391.4</v>
+        <v>376.7</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>20</v>
@@ -1846,7 +1846,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="6">
-        <v>541.6</v>
+        <v>541.7</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -1892,13 +1892,13 @@
         <v>42</v>
       </c>
       <c r="E18" s="6">
-        <v>480.9</v>
+        <v>461.5</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="6">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2765,7 +2765,7 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>94.7</v>
+        <v>41.3</v>
       </c>
       <c r="H5" t="s">
         <v>102</v>
@@ -2791,7 +2791,7 @@
         <v>6</v>
       </c>
       <c r="G6">
-        <v>47.4</v>
+        <v>64.3</v>
       </c>
       <c r="H6" t="s">
         <v>105</v>
@@ -2814,10 +2814,10 @@
         <v>101</v>
       </c>
       <c r="F7" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G7">
-        <v>64.6</v>
+        <v>36.9</v>
       </c>
       <c r="H7" t="s">
         <v>108</v>
@@ -2843,15 +2843,15 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>47.4</v>
+        <v>95</v>
       </c>
       <c r="H8" t="s">
-        <v>105</v>
+        <v>110</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2860,7 +2860,7 @@
         <v>98.7</v>
       </c>
       <c r="D9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="E9" t="s">
         <v>101</v>
@@ -2869,15 +2869,15 @@
         <v>6</v>
       </c>
       <c r="G9">
-        <v>92.9</v>
+        <v>41.1</v>
       </c>
       <c r="H9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B10" s="5">
         <v>8</v>
@@ -2886,24 +2886,24 @@
         <v>49.1</v>
       </c>
       <c r="D10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="E10" t="s">
         <v>101</v>
       </c>
       <c r="F10" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G10">
-        <v>44.4</v>
+        <v>98.1</v>
       </c>
       <c r="H10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B11" s="13">
         <v>37</v>
@@ -2921,7 +2921,7 @@
         <v>35</v>
       </c>
       <c r="G11" s="13">
-        <v>391.4</v>
+        <v>376.7</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>20</v>
@@ -2929,7 +2929,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2976,7 +2976,7 @@
         <v>90.6</v>
       </c>
       <c r="D15" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="E15" t="s">
         <v>101</v>
@@ -2988,7 +2988,7 @@
         <v>83</v>
       </c>
       <c r="H15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3002,7 +3002,7 @@
         <v>103.8</v>
       </c>
       <c r="D16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="E16" t="s">
         <v>101</v>
@@ -3014,7 +3014,7 @@
         <v>96.9</v>
       </c>
       <c r="H16" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
@@ -3028,7 +3028,7 @@
         <v>88.4</v>
       </c>
       <c r="D17" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="E17" t="s">
         <v>101</v>
@@ -3037,10 +3037,10 @@
         <v>7</v>
       </c>
       <c r="G17">
-        <v>85.3</v>
+        <v>82.9</v>
       </c>
       <c r="H17" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
@@ -3054,7 +3054,7 @@
         <v>105</v>
       </c>
       <c r="D18" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E18" t="s">
         <v>101</v>
@@ -3066,12 +3066,12 @@
         <v>97.8</v>
       </c>
       <c r="H18" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -3080,7 +3080,7 @@
         <v>88.1</v>
       </c>
       <c r="D19" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E19" t="s">
         <v>101</v>
@@ -3089,15 +3089,15 @@
         <v>6</v>
       </c>
       <c r="G19">
-        <v>82.6</v>
+        <v>85.1</v>
       </c>
       <c r="H19" t="s">
-        <v>119</v>
+        <v>128</v>
       </c>
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B20">
         <v>7</v>
@@ -3106,7 +3106,7 @@
         <v>105</v>
       </c>
       <c r="D20" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="E20" t="s">
         <v>101</v>
@@ -3118,12 +3118,12 @@
         <v>96</v>
       </c>
       <c r="H20" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B21" s="13">
         <v>43</v>
@@ -3141,7 +3141,7 @@
         <v>38</v>
       </c>
       <c r="G21" s="13">
-        <v>541.6</v>
+        <v>541.7</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>25</v>
@@ -3149,7 +3149,7 @@
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
@@ -3196,7 +3196,7 @@
         <v>79.6</v>
       </c>
       <c r="D25" t="s">
-        <v>123</v>
+        <v>131</v>
       </c>
       <c r="E25" t="s">
         <v>101</v>
@@ -3205,10 +3205,10 @@
         <v>6</v>
       </c>
       <c r="G25">
-        <v>97.5</v>
+        <v>91.8</v>
       </c>
       <c r="H25" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -3222,19 +3222,19 @@
         <v>95.1</v>
       </c>
       <c r="D26" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="E26" t="s">
         <v>101</v>
       </c>
       <c r="F26" s="11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G26">
-        <v>79.4</v>
+        <v>73.2</v>
       </c>
       <c r="H26" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3248,7 +3248,7 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="E27" t="s">
         <v>101</v>
@@ -3260,7 +3260,7 @@
         <v>95</v>
       </c>
       <c r="H27" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3274,24 +3274,24 @@
         <v>98.4</v>
       </c>
       <c r="D28" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="E28" t="s">
         <v>101</v>
       </c>
       <c r="F28" s="11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G28">
-        <v>72.5</v>
+        <v>37.7</v>
       </c>
       <c r="H28" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B29" s="5">
         <v>9</v>
@@ -3300,24 +3300,24 @@
         <v>77.4</v>
       </c>
       <c r="D29" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E29" t="s">
         <v>101</v>
       </c>
       <c r="F29" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G29">
-        <v>89.6</v>
+        <v>91.4</v>
       </c>
       <c r="H29" t="s">
-        <v>127</v>
+        <v>138</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B30" s="5">
         <v>8</v>
@@ -3326,7 +3326,7 @@
         <v>110.6</v>
       </c>
       <c r="D30" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="E30" t="s">
         <v>101</v>
@@ -3335,15 +3335,15 @@
         <v>8</v>
       </c>
       <c r="G30">
-        <v>46.9</v>
+        <v>72.4</v>
       </c>
       <c r="H30" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B31" s="13">
         <v>50</v>
@@ -3361,7 +3361,7 @@
         <v>42</v>
       </c>
       <c r="G31" s="13">
-        <v>480.9</v>
+        <v>461.5</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>29</v>
@@ -3393,7 +3393,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3403,7 +3403,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3413,7 +3413,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -3423,33 +3423,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -3466,19 +3466,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="15">
-        <v>13</v>
+        <v>7.9</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3486,19 +3486,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>49</v>
+        <v>88</v>
       </c>
       <c r="C8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="D8" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E8">
-        <v>16.7</v>
+        <v>5.5</v>
       </c>
       <c r="F8" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3506,19 +3506,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>153</v>
+        <v>158</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E9" s="15">
-        <v>4.8</v>
+        <v>3.5</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>154</v>
+        <v>159</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3526,19 +3526,19 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>59</v>
+        <v>87</v>
       </c>
       <c r="C10" t="s">
-        <v>155</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
         <v>58</v>
       </c>
       <c r="E10">
-        <v>17.9</v>
+        <v>0.9</v>
       </c>
       <c r="F10" t="s">
-        <v>156</v>
+        <v>161</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3546,19 +3546,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>54</v>
+        <v>162</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E11" s="15">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3566,27 +3566,27 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>85</v>
+        <v>165</v>
       </c>
       <c r="C12" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D12" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E12">
-        <v>12</v>
+        <v>7.1</v>
       </c>
       <c r="F12" t="s">
-        <v>160</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>31</v>
@@ -3595,15 +3595,15 @@
         <v>31</v>
       </c>
       <c r="E13" s="15">
-        <v>15.9</v>
+        <v>8.5</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -3613,33 +3613,33 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -3656,19 +3656,19 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>164</v>
+        <v>169</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E18" s="15">
-        <v>7.9</v>
+        <v>16.3</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>150</v>
+        <v>170</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,19 +3676,19 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>165</v>
+        <v>54</v>
       </c>
       <c r="C19" t="s">
-        <v>166</v>
+        <v>171</v>
       </c>
       <c r="D19" t="s">
         <v>50</v>
       </c>
       <c r="E19">
-        <v>2</v>
+        <v>11.4</v>
       </c>
       <c r="F19" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,19 +3696,19 @@
         <v>3</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>168</v>
+        <v>49</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>166</v>
+        <v>173</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="15">
-        <v>6.7</v>
+        <v>6.3</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>169</v>
+        <v>174</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3716,19 +3716,19 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>55</v>
+        <v>61</v>
       </c>
       <c r="C21" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="D21" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E21">
-        <v>9.2</v>
+        <v>1.3</v>
       </c>
       <c r="F21" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3739,16 +3739,16 @@
         <v>60</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>58</v>
       </c>
       <c r="E22" s="15">
-        <v>0.9</v>
+        <v>7.2</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3756,27 +3756,27 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="D23" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E23">
-        <v>9.9</v>
+        <v>0.9</v>
       </c>
       <c r="F23" t="s">
-        <v>174</v>
+        <v>179</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>31</v>
@@ -3785,15 +3785,15 @@
         <v>31</v>
       </c>
       <c r="E24" s="15">
-        <v>10.8</v>
+        <v>20.9</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>175</v>
+        <v>180</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>176</v>
+        <v>181</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -3803,33 +3803,33 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
@@ -3846,19 +3846,19 @@
         <v>1</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E29" s="15">
-        <v>13</v>
+        <v>7.9</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3866,19 +3866,19 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="C30" t="s">
-        <v>177</v>
+        <v>163</v>
       </c>
       <c r="D30" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E30">
-        <v>0.9</v>
+        <v>2</v>
       </c>
       <c r="F30" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3886,19 +3886,19 @@
         <v>3</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>85</v>
+        <v>157</v>
       </c>
       <c r="C31" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>159</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E31" s="15">
-        <v>5.1</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3906,19 +3906,19 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>54</v>
+        <v>87</v>
       </c>
       <c r="C32" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E32">
-        <v>11.4</v>
+        <v>0.9</v>
       </c>
       <c r="F32" t="s">
-        <v>180</v>
+        <v>161</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3926,609 +3926,609 @@
         <v>5</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>49</v>
+        <v>162</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>151</v>
+        <v>163</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E33" s="15">
-        <v>6.3</v>
+        <v>8</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>181</v>
+        <v>164</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>6</v>
+      <c r="A34" t="s">
+        <v>149</v>
       </c>
       <c r="B34" t="s">
-        <v>61</v>
+        <v>166</v>
       </c>
       <c r="C34" t="s">
-        <v>182</v>
+        <v>31</v>
       </c>
       <c r="D34" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="E34">
-        <v>1.3</v>
+        <v>14</v>
       </c>
       <c r="F34" t="s">
         <v>183</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
+    <row r="36" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>184</v>
+      </c>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="B35" s="15" t="s">
+      <c r="C37" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>149</v>
+      </c>
+      <c r="B38" t="s">
+        <v>150</v>
+      </c>
+      <c r="C38" t="s">
+        <v>151</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
+        <v>1</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>55</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="15">
+        <v>19.5</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>49</v>
+      </c>
+      <c r="C40" t="s">
+        <v>173</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40">
+        <v>10.5</v>
+      </c>
+      <c r="F40" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
+        <v>3</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E41" s="15">
+        <v>4.8</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>59</v>
+      </c>
+      <c r="C42" t="s">
+        <v>188</v>
+      </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42">
+        <v>17.9</v>
+      </c>
+      <c r="F42" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15">
+        <v>5</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="15">
+        <v>14.5</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>85</v>
+      </c>
+      <c r="C44" t="s">
+        <v>169</v>
+      </c>
+      <c r="D44" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44">
+        <v>12</v>
+      </c>
+      <c r="F44" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="15">
+        <v>15.9</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>189</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" t="s">
+        <v>150</v>
+      </c>
+      <c r="C49" t="s">
+        <v>151</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="15">
+        <v>1</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="C50" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50" s="15">
+        <v>7.9</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>88</v>
+      </c>
+      <c r="C51" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51">
+        <v>5.5</v>
+      </c>
+      <c r="F51" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
+        <v>3</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>158</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>190</v>
+      </c>
+      <c r="C53" t="s">
+        <v>163</v>
+      </c>
+      <c r="D53" t="s">
+        <v>62</v>
+      </c>
+      <c r="E53">
+        <v>8.2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>5</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="F54" s="15" t="s">
         <v>161</v>
       </c>
-      <c r="C35" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="15">
-        <v>26.7</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>185</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D38" s="4" t="s">
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>6</v>
+      </c>
+      <c r="B55" t="s">
+        <v>165</v>
+      </c>
+      <c r="C55" t="s">
+        <v>163</v>
+      </c>
+      <c r="D55" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55">
+        <v>7.1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" s="15">
+        <v>8.5</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="58" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="B58" s="14"/>
+      <c r="C58" s="14"/>
+      <c r="D58" s="14"/>
+      <c r="E58" s="14"/>
+      <c r="F58" s="14"/>
+    </row>
+    <row r="59" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D59" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="E38" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>145</v>
-      </c>
-      <c r="B39" t="s">
-        <v>146</v>
-      </c>
-      <c r="C39" t="s">
+      <c r="E59" s="4" t="s">
         <v>147</v>
       </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="15">
+      <c r="F59" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>149</v>
+      </c>
+      <c r="B60" t="s">
+        <v>150</v>
+      </c>
+      <c r="C60" t="s">
+        <v>151</v>
+      </c>
+      <c r="D60" t="s">
+        <v>31</v>
+      </c>
+      <c r="E60" t="s">
+        <v>31</v>
+      </c>
+      <c r="F60" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="15">
         <v>1</v>
       </c>
-      <c r="B40" s="15" t="s">
+      <c r="B61" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>171</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E61" s="15">
+        <v>30.7</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>2</v>
+      </c>
+      <c r="B62" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" t="s">
+        <v>188</v>
+      </c>
+      <c r="D62" t="s">
+        <v>58</v>
+      </c>
+      <c r="E62">
+        <v>16.9</v>
+      </c>
+      <c r="F62" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="15">
+        <v>3</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>186</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="15">
+        <v>17.1</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64">
+        <v>4</v>
+      </c>
+      <c r="B64" t="s">
+        <v>49</v>
+      </c>
+      <c r="C64" t="s">
+        <v>173</v>
+      </c>
+      <c r="D64" t="s">
+        <v>50</v>
+      </c>
+      <c r="E64">
+        <v>4.2</v>
+      </c>
+      <c r="F64" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="15">
+        <v>5</v>
+      </c>
+      <c r="B65" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C65" s="15" t="s">
+        <v>177</v>
+      </c>
+      <c r="D65" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E65" s="15">
+        <v>7.4</v>
+      </c>
+      <c r="F65" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66">
+        <v>6</v>
+      </c>
+      <c r="B66" t="s">
+        <v>55</v>
+      </c>
+      <c r="C66" t="s">
         <v>163</v>
       </c>
-      <c r="C40" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40" s="15">
-        <v>7.9</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2</v>
-      </c>
-      <c r="B41" t="s">
-        <v>165</v>
-      </c>
-      <c r="C41" t="s">
+      <c r="D66" t="s">
+        <v>50</v>
+      </c>
+      <c r="E66">
+        <v>0.9</v>
+      </c>
+      <c r="F66" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B67" s="15" t="s">
         <v>166</v>
       </c>
-      <c r="D41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41">
-        <v>2</v>
-      </c>
-      <c r="F41" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
-        <v>3</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="15">
-        <v>6.7</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>55</v>
-      </c>
-      <c r="C43" t="s">
-        <v>166</v>
-      </c>
-      <c r="D43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43">
-        <v>9.2</v>
-      </c>
-      <c r="F43" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="15">
-        <v>5</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="15">
-        <v>0.9</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>88</v>
-      </c>
-      <c r="C45" t="s">
-        <v>173</v>
-      </c>
-      <c r="D45" t="s">
-        <v>58</v>
-      </c>
-      <c r="E45">
-        <v>9.9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E46" s="15">
-        <v>10.8</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-    </row>
-    <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>145</v>
-      </c>
-      <c r="B50" t="s">
-        <v>146</v>
-      </c>
-      <c r="C50" t="s">
-        <v>147</v>
-      </c>
-      <c r="D50" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="15">
-        <v>1</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E51" s="15">
-        <v>13</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>2</v>
-      </c>
-      <c r="B52" t="s">
-        <v>87</v>
-      </c>
-      <c r="C52" t="s">
-        <v>177</v>
-      </c>
-      <c r="D52" t="s">
-        <v>58</v>
-      </c>
-      <c r="E52">
-        <v>0.9</v>
-      </c>
-      <c r="F52" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="15">
-        <v>3</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E53" s="15">
-        <v>13.9</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>59</v>
-      </c>
-      <c r="C54" t="s">
-        <v>155</v>
-      </c>
-      <c r="D54" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54">
-        <v>16.9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="15">
-        <v>5</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E55" s="15">
-        <v>17.1</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>6</v>
-      </c>
-      <c r="B56" t="s">
-        <v>49</v>
-      </c>
-      <c r="C56" t="s">
-        <v>151</v>
-      </c>
-      <c r="D56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56">
-        <v>4.2</v>
-      </c>
-      <c r="F56" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="15" t="s">
-        <v>145</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E57" s="15">
-        <v>27</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="59" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="B59" s="14"/>
-      <c r="C59" s="14"/>
-      <c r="D59" s="14"/>
-      <c r="E59" s="14"/>
-      <c r="F59" s="14"/>
-    </row>
-    <row r="60" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D60" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E60" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F60" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>145</v>
-      </c>
-      <c r="B61" t="s">
-        <v>146</v>
-      </c>
-      <c r="C61" t="s">
-        <v>147</v>
-      </c>
-      <c r="D61" t="s">
-        <v>31</v>
-      </c>
-      <c r="E61" t="s">
-        <v>31</v>
-      </c>
-      <c r="F61" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A62" s="15">
-        <v>1</v>
-      </c>
-      <c r="B62" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="C62" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="D62" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62" s="15">
-        <v>7.9</v>
-      </c>
-      <c r="F62" s="15" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63">
-        <v>2</v>
-      </c>
-      <c r="B63" t="s">
-        <v>165</v>
-      </c>
-      <c r="C63" t="s">
-        <v>166</v>
-      </c>
-      <c r="D63" t="s">
-        <v>50</v>
-      </c>
-      <c r="E63">
-        <v>2</v>
-      </c>
-      <c r="F63" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="15">
-        <v>3</v>
-      </c>
-      <c r="B64" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C64" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D64" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E64" s="15">
-        <v>10.7</v>
-      </c>
-      <c r="F64" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65">
-        <v>4</v>
-      </c>
-      <c r="B65" t="s">
-        <v>190</v>
-      </c>
-      <c r="C65" t="s">
-        <v>166</v>
-      </c>
-      <c r="D65" t="s">
-        <v>62</v>
-      </c>
-      <c r="E65">
-        <v>9.4</v>
-      </c>
-      <c r="F65" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="15">
-        <v>5</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>168</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E66" s="15">
-        <v>0.4</v>
-      </c>
-      <c r="F66" s="15" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" t="s">
-        <v>145</v>
-      </c>
-      <c r="B67" t="s">
-        <v>161</v>
-      </c>
-      <c r="C67" t="s">
-        <v>31</v>
-      </c>
-      <c r="D67" t="s">
-        <v>31</v>
-      </c>
-      <c r="E67">
-        <v>14</v>
-      </c>
-      <c r="F67" t="s">
-        <v>192</v>
+      <c r="C67" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D67" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" s="15">
+        <v>20.9</v>
+      </c>
+      <c r="F67" s="15" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -4538,9 +4538,9 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A48:F48"/>
-    <mergeCell ref="A59:F59"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A58:F58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -4591,33 +4591,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -4666,7 +4666,7 @@
         <v>8.2</v>
       </c>
       <c r="F8" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4674,10 +4674,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>202</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>203</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>50</v>
@@ -4686,7 +4686,7 @@
         <v>8</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4694,10 +4694,10 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
+        <v>203</v>
+      </c>
+      <c r="C10" t="s">
         <v>204</v>
-      </c>
-      <c r="C10" t="s">
-        <v>205</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -4706,7 +4706,7 @@
         <v>3.3</v>
       </c>
       <c r="F10" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4714,10 +4714,10 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>207</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>208</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>50</v>
@@ -4726,15 +4726,15 @@
         <v>6.7</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B12" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C12" t="s">
         <v>31</v>
@@ -4746,12 +4746,12 @@
         <v>29.4</v>
       </c>
       <c r="F12" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="14" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B14" s="14"/>
       <c r="C14" s="14"/>
@@ -4761,33 +4761,33 @@
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F15" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B16" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C16" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D16" t="s">
         <v>31</v>
@@ -4804,10 +4804,10 @@
         <v>1</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D17" s="15" t="s">
         <v>50</v>
@@ -4816,7 +4816,7 @@
         <v>28.4</v>
       </c>
       <c r="F17" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -4827,7 +4827,7 @@
         <v>67</v>
       </c>
       <c r="C18" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D18" t="s">
         <v>50</v>
@@ -4836,7 +4836,7 @@
         <v>11.3</v>
       </c>
       <c r="F18" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -4847,7 +4847,7 @@
         <v>66</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>50</v>
@@ -4856,7 +4856,7 @@
         <v>6.9</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4867,7 +4867,7 @@
         <v>65</v>
       </c>
       <c r="C20" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D20" t="s">
         <v>50</v>
@@ -4876,7 +4876,7 @@
         <v>2.8</v>
       </c>
       <c r="F20" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4887,7 +4887,7 @@
         <v>63</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D21" s="15" t="s">
         <v>50</v>
@@ -4896,7 +4896,7 @@
         <v>1.8</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4907,7 +4907,7 @@
         <v>70</v>
       </c>
       <c r="C22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s">
         <v>62</v>
@@ -4916,7 +4916,7 @@
         <v>1.4</v>
       </c>
       <c r="F22" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4927,7 +4927,7 @@
         <v>86</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D23" s="15" t="s">
         <v>58</v>
@@ -4936,15 +4936,15 @@
         <v>9.4</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>152</v>
+        <v>216</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B24" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
@@ -4956,12 +4956,12 @@
         <v>34.8</v>
       </c>
       <c r="F24" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -4971,33 +4971,33 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F27" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B28" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C28" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
@@ -5014,10 +5014,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>220</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>221</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>62</v>
@@ -5026,7 +5026,7 @@
         <v>25.5</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -5046,7 +5046,7 @@
         <v>6.8</v>
       </c>
       <c r="F30" t="s">
-        <v>170</v>
+        <v>222</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -5057,16 +5057,16 @@
         <v>223</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="D31" s="15" t="s">
         <v>62</v>
       </c>
       <c r="E31" s="15">
-        <v>0.4</v>
+        <v>7.5</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>224</v>
+        <v>154</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,19 +5074,19 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
+        <v>201</v>
+      </c>
+      <c r="C32" t="s">
         <v>202</v>
       </c>
-      <c r="C32" t="s">
-        <v>203</v>
-      </c>
       <c r="D32" t="s">
         <v>50</v>
       </c>
       <c r="E32">
-        <v>10.1</v>
+        <v>0.5</v>
       </c>
       <c r="F32" t="s">
-        <v>225</v>
+        <v>179</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -5094,10 +5094,10 @@
         <v>5</v>
       </c>
       <c r="B33" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C33" s="15" t="s">
         <v>204</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>205</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>50</v>
@@ -5106,7 +5106,7 @@
         <v>3.2</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -5114,10 +5114,10 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
+        <v>206</v>
+      </c>
+      <c r="C34" t="s">
         <v>207</v>
-      </c>
-      <c r="C34" t="s">
-        <v>208</v>
       </c>
       <c r="D34" t="s">
         <v>50</v>
@@ -5126,7 +5126,7 @@
         <v>6.4</v>
       </c>
       <c r="F34" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5146,15 +5146,15 @@
         <v>5.9</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B36" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
@@ -5171,7 +5171,7 @@
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="14" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="B38" s="14"/>
       <c r="C38" s="14"/>
@@ -5181,33 +5181,33 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F39" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B40" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C40" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D40" t="s">
         <v>31</v>
@@ -5224,10 +5224,10 @@
         <v>1</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>50</v>
@@ -5236,7 +5236,7 @@
         <v>28.4</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -5247,7 +5247,7 @@
         <v>67</v>
       </c>
       <c r="C42" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D42" t="s">
         <v>50</v>
@@ -5256,7 +5256,7 @@
         <v>11.3</v>
       </c>
       <c r="F42" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -5267,7 +5267,7 @@
         <v>66</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D43" s="15" t="s">
         <v>50</v>
@@ -5276,7 +5276,7 @@
         <v>6.9</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -5287,7 +5287,7 @@
         <v>65</v>
       </c>
       <c r="C44" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D44" t="s">
         <v>50</v>
@@ -5296,7 +5296,7 @@
         <v>2.8</v>
       </c>
       <c r="F44" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -5307,7 +5307,7 @@
         <v>69</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>62</v>
@@ -5316,7 +5316,7 @@
         <v>0.9</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -5327,7 +5327,7 @@
         <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D46" t="s">
         <v>50</v>
@@ -5336,7 +5336,7 @@
         <v>2.5</v>
       </c>
       <c r="F46" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
@@ -5347,7 +5347,7 @@
         <v>86</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D47" s="15" t="s">
         <v>58</v>
@@ -5356,15 +5356,15 @@
         <v>10.1</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>225</v>
+        <v>180</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B48" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C48" t="s">
         <v>31</v>
@@ -5376,12 +5376,12 @@
         <v>34.8</v>
       </c>
       <c r="F48" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="14" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="B50" s="14"/>
       <c r="C50" s="14"/>
@@ -5391,33 +5391,33 @@
     </row>
     <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C51" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D51" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E51" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F51" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B52" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C52" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D52" t="s">
         <v>31</v>
@@ -5466,7 +5466,7 @@
         <v>8.2</v>
       </c>
       <c r="F54" t="s">
-        <v>201</v>
+        <v>167</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -5474,19 +5474,19 @@
         <v>3</v>
       </c>
       <c r="B55" s="15" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="C55" s="15" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="D55" s="15" t="s">
         <v>62</v>
       </c>
       <c r="E55" s="15">
-        <v>7.5</v>
+        <v>0.4</v>
       </c>
       <c r="F55" s="15" t="s">
-        <v>150</v>
+        <v>179</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -5494,19 +5494,19 @@
         <v>4</v>
       </c>
       <c r="B56" t="s">
+        <v>201</v>
+      </c>
+      <c r="C56" t="s">
         <v>202</v>
       </c>
-      <c r="C56" t="s">
-        <v>203</v>
-      </c>
       <c r="D56" t="s">
         <v>50</v>
       </c>
       <c r="E56">
-        <v>0.5</v>
+        <v>10.1</v>
       </c>
       <c r="F56" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -5514,10 +5514,10 @@
         <v>5</v>
       </c>
       <c r="B57" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C57" s="15" t="s">
         <v>204</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>205</v>
       </c>
       <c r="D57" s="15" t="s">
         <v>50</v>
@@ -5526,7 +5526,7 @@
         <v>3.2</v>
       </c>
       <c r="F57" s="15" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -5534,10 +5534,10 @@
         <v>6</v>
       </c>
       <c r="B58" t="s">
+        <v>206</v>
+      </c>
+      <c r="C58" t="s">
         <v>207</v>
-      </c>
-      <c r="C58" t="s">
-        <v>208</v>
       </c>
       <c r="D58" t="s">
         <v>50</v>
@@ -5546,15 +5546,15 @@
         <v>6.4</v>
       </c>
       <c r="F58" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C59" s="15" t="s">
         <v>31</v>
@@ -5566,12 +5566,12 @@
         <v>29.4</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -5581,33 +5581,33 @@
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C62" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B63" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C63" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D63" t="s">
         <v>31</v>
@@ -5624,10 +5624,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>50</v>
@@ -5636,7 +5636,7 @@
         <v>28.4</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -5647,7 +5647,7 @@
         <v>67</v>
       </c>
       <c r="C65" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="D65" t="s">
         <v>50</v>
@@ -5656,7 +5656,7 @@
         <v>11.3</v>
       </c>
       <c r="F65" t="s">
-        <v>175</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -5667,7 +5667,7 @@
         <v>66</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>50</v>
@@ -5676,7 +5676,7 @@
         <v>6.9</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5687,7 +5687,7 @@
         <v>65</v>
       </c>
       <c r="C67" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D67" t="s">
         <v>50</v>
@@ -5696,7 +5696,7 @@
         <v>2.8</v>
       </c>
       <c r="F67" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5707,7 +5707,7 @@
         <v>63</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>50</v>
@@ -5716,7 +5716,7 @@
         <v>1.8</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5727,7 +5727,7 @@
         <v>68</v>
       </c>
       <c r="C69" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="D69" t="s">
         <v>62</v>
@@ -5736,15 +5736,15 @@
         <v>5.1</v>
       </c>
       <c r="F69" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>31</v>
@@ -5756,7 +5756,7 @@
         <v>39.8</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
     </row>
   </sheetData>
@@ -5789,7 +5789,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5799,7 +5799,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5809,7 +5809,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -5819,33 +5819,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B6" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5862,19 +5862,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>238</v>
+        <v>89</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E7" s="15">
-        <v>44.2</v>
+        <v>14.8</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>240</v>
+        <v>183</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5882,19 +5882,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
       </c>
       <c r="E8">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="F8" t="s">
-        <v>228</v>
+        <v>180</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5902,19 +5902,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="15">
-        <v>9.2</v>
+        <v>6.3</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5922,19 +5922,19 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D10" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>3.1</v>
+        <v>8.3</v>
       </c>
       <c r="F10" t="s">
-        <v>228</v>
+        <v>243</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5942,19 +5942,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>62</v>
       </c>
       <c r="E11" s="15">
-        <v>0.9</v>
+        <v>5.6</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5962,27 +5962,27 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>
       </c>
       <c r="E12">
-        <v>6.1</v>
+        <v>3</v>
       </c>
       <c r="F12" t="s">
-        <v>175</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>31</v>
@@ -5991,15 +5991,15 @@
         <v>31</v>
       </c>
       <c r="E13" s="15">
-        <v>30.8</v>
+        <v>41.8</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -6009,33 +6009,33 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B17" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C17" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -6052,19 +6052,19 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>251</v>
+        <v>81</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>252</v>
+        <v>235</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E18" s="15">
-        <v>10.3</v>
+        <v>3.1</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>152</v>
+        <v>205</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6072,19 +6072,19 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="C19" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D19" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E19">
-        <v>4.6</v>
+        <v>14.9</v>
       </c>
       <c r="F19" t="s">
-        <v>206</v>
+        <v>249</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6092,19 +6092,19 @@
         <v>3</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>84</v>
+        <v>250</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E20" s="15">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>169</v>
+        <v>222</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6112,19 +6112,19 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>79</v>
+        <v>251</v>
       </c>
       <c r="C21" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
       </c>
       <c r="E21">
-        <v>2.3</v>
+        <v>6.5</v>
       </c>
       <c r="F21" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6135,16 +6135,16 @@
         <v>82</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="15">
-        <v>9.5</v>
+        <v>15.1</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>154</v>
+        <v>216</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6152,19 +6152,19 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>254</v>
+        <v>79</v>
       </c>
       <c r="C23" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
       </c>
       <c r="E23">
-        <v>14.6</v>
+        <v>7.6</v>
       </c>
       <c r="F23" t="s">
-        <v>158</v>
+        <v>174</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6172,19 +6172,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>256</v>
+        <v>84</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E24" s="15">
-        <v>6.7</v>
+        <v>3.6</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>175</v>
+        <v>182</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6192,546 +6192,546 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>83</v>
+        <v>253</v>
       </c>
       <c r="C25" t="s">
+        <v>252</v>
+      </c>
+      <c r="D25" t="s">
+        <v>50</v>
+      </c>
+      <c r="E25">
+        <v>4.4</v>
+      </c>
+      <c r="F25" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26" s="15">
+        <v>11.4</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>254</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F29" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>149</v>
+      </c>
+      <c r="B30" t="s">
+        <v>150</v>
+      </c>
+      <c r="C30" t="s">
+        <v>235</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="15">
+        <v>1</v>
+      </c>
+      <c r="B31" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="15">
+        <v>43.9</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>255</v>
       </c>
-      <c r="D25" t="s">
-        <v>50</v>
-      </c>
-      <c r="E25">
-        <v>5.9</v>
-      </c>
-      <c r="F25" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
-        <v>9</v>
-      </c>
-      <c r="B26" s="15" t="s">
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
+        <v>2</v>
+      </c>
+      <c r="B32" t="s">
+        <v>239</v>
+      </c>
+      <c r="C32" t="s">
+        <v>240</v>
+      </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32">
+        <v>9.2</v>
+      </c>
+      <c r="F32" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33" s="15">
+        <v>3</v>
+      </c>
+      <c r="B33" s="15" t="s">
+        <v>256</v>
+      </c>
+      <c r="C33" s="15" t="s">
+        <v>257</v>
+      </c>
+      <c r="D33" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="F33" s="15" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>4</v>
+      </c>
+      <c r="B34" t="s">
+        <v>237</v>
+      </c>
+      <c r="C34" t="s">
+        <v>238</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34">
+        <v>7</v>
+      </c>
+      <c r="F34" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="15">
+        <v>5</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>238</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E35" s="15">
+        <v>1.9</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>149</v>
+      </c>
+      <c r="B36" t="s">
+        <v>166</v>
+      </c>
+      <c r="C36" t="s">
+        <v>31</v>
+      </c>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36">
+        <v>29.8</v>
+      </c>
+      <c r="F36" t="s">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B38" s="14"/>
+      <c r="C38" s="14"/>
+      <c r="D38" s="14"/>
+      <c r="E38" s="14"/>
+      <c r="F38" s="14"/>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E39" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F39" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>149</v>
+      </c>
+      <c r="B40" t="s">
+        <v>150</v>
+      </c>
+      <c r="C40" t="s">
+        <v>235</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F40" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
+        <v>1</v>
+      </c>
+      <c r="B41" s="15" t="s">
         <v>81</v>
       </c>
-      <c r="C26" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E26" s="15">
-        <v>15.2</v>
-      </c>
-      <c r="F26" s="15" t="s">
+      <c r="C41" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>2</v>
+      </c>
+      <c r="B42" t="s">
+        <v>260</v>
+      </c>
+      <c r="C42" t="s">
+        <v>235</v>
+      </c>
+      <c r="D42" t="s">
+        <v>62</v>
+      </c>
+      <c r="E42">
+        <v>3.8</v>
+      </c>
+      <c r="F42" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15">
+        <v>3</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43" s="15">
+        <v>6.6</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>4</v>
+      </c>
+      <c r="B44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C44" t="s">
+        <v>252</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44">
+        <v>7.6</v>
+      </c>
+      <c r="F44" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="15">
+        <v>5</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45" s="15">
+        <v>4.4</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46">
+        <v>6</v>
+      </c>
+      <c r="B46" t="s">
+        <v>261</v>
+      </c>
+      <c r="C46" t="s">
+        <v>262</v>
+      </c>
+      <c r="D46" t="s">
+        <v>62</v>
+      </c>
+      <c r="E46">
+        <v>3.5</v>
+      </c>
+      <c r="F46" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="15">
+        <v>7</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>235</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E47" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48">
+        <v>8</v>
+      </c>
+      <c r="B48" t="s">
+        <v>264</v>
+      </c>
+      <c r="C48" t="s">
+        <v>235</v>
+      </c>
+      <c r="D48" t="s">
+        <v>62</v>
+      </c>
+      <c r="E48">
+        <v>3</v>
+      </c>
+      <c r="F48" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>166</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B51" s="14"/>
+      <c r="C51" s="14"/>
+      <c r="D51" s="14"/>
+      <c r="E51" s="14"/>
+      <c r="F51" s="14"/>
+    </row>
+    <row r="52" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="D52" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E52" s="4" t="s">
+        <v>147</v>
+      </c>
+      <c r="F52" s="4" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>149</v>
+      </c>
+      <c r="B53" t="s">
+        <v>150</v>
+      </c>
+      <c r="C53" t="s">
+        <v>235</v>
+      </c>
+      <c r="D53" t="s">
+        <v>31</v>
+      </c>
+      <c r="E53" t="s">
+        <v>31</v>
+      </c>
+      <c r="F53" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>1</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>236</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="15">
+        <v>14.8</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>2</v>
+      </c>
+      <c r="B55" t="s">
+        <v>256</v>
+      </c>
+      <c r="C55" t="s">
         <v>257</v>
       </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" t="s">
-        <v>145</v>
-      </c>
-      <c r="B27" t="s">
-        <v>161</v>
-      </c>
-      <c r="C27" t="s">
-        <v>31</v>
-      </c>
-      <c r="D27" t="s">
-        <v>31</v>
-      </c>
-      <c r="E27">
-        <v>2.8</v>
-      </c>
-      <c r="F27" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="14" t="s">
-        <v>258</v>
-      </c>
-      <c r="B29" s="14"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="14"/>
-      <c r="E29" s="14"/>
-      <c r="F29" s="14"/>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E30" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F30" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>145</v>
-      </c>
-      <c r="B31" t="s">
-        <v>146</v>
-      </c>
-      <c r="C31" t="s">
-        <v>237</v>
-      </c>
-      <c r="D31" t="s">
-        <v>31</v>
-      </c>
-      <c r="E31" t="s">
-        <v>31</v>
-      </c>
-      <c r="F31" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="15">
-        <v>1</v>
-      </c>
-      <c r="B32" s="15" t="s">
-        <v>241</v>
-      </c>
-      <c r="C32" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="D32" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32" s="15">
-        <v>43.9</v>
-      </c>
-      <c r="F32" s="15" t="s">
-        <v>240</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33">
-        <v>2</v>
-      </c>
-      <c r="B33" t="s">
-        <v>242</v>
-      </c>
-      <c r="C33" t="s">
-        <v>243</v>
-      </c>
-      <c r="D33" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33">
-        <v>9.2</v>
-      </c>
-      <c r="F33" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" s="15">
-        <v>3</v>
-      </c>
-      <c r="B34" s="15" t="s">
-        <v>244</v>
-      </c>
-      <c r="C34" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="D34" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34" s="15">
-        <v>3.1</v>
-      </c>
-      <c r="F34" s="15" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35">
-        <v>4</v>
-      </c>
-      <c r="B35" t="s">
-        <v>247</v>
-      </c>
-      <c r="C35" t="s">
-        <v>248</v>
-      </c>
-      <c r="D35" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35">
-        <v>7</v>
-      </c>
-      <c r="F35" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="15">
-        <v>5</v>
-      </c>
-      <c r="B36" s="15" t="s">
-        <v>259</v>
-      </c>
-      <c r="C36" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="D36" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E36" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="F36" s="15" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" t="s">
-        <v>145</v>
-      </c>
-      <c r="B37" t="s">
-        <v>161</v>
-      </c>
-      <c r="C37" t="s">
-        <v>31</v>
-      </c>
-      <c r="D37" t="s">
-        <v>31</v>
-      </c>
-      <c r="E37">
-        <v>29.8</v>
-      </c>
-      <c r="F37" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="14" t="s">
-        <v>261</v>
-      </c>
-      <c r="B39" s="14"/>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14"/>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14"/>
-    </row>
-    <row r="40" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D40" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E40" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F40" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" t="s">
-        <v>145</v>
-      </c>
-      <c r="B41" t="s">
-        <v>146</v>
-      </c>
-      <c r="C41" t="s">
-        <v>237</v>
-      </c>
-      <c r="D41" t="s">
-        <v>31</v>
-      </c>
-      <c r="E41" t="s">
-        <v>31</v>
-      </c>
-      <c r="F41" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
-        <v>1</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E42" s="15">
-        <v>3.1</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>206</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>2</v>
-      </c>
-      <c r="B43" t="s">
-        <v>83</v>
-      </c>
-      <c r="C43" t="s">
-        <v>255</v>
-      </c>
-      <c r="D43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43">
-        <v>14.9</v>
-      </c>
-      <c r="F43" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="15">
-        <v>3</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>254</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E44" s="15">
-        <v>12.3</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>263</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>4</v>
-      </c>
-      <c r="B45" t="s">
-        <v>82</v>
-      </c>
-      <c r="C45" t="s">
-        <v>237</v>
-      </c>
-      <c r="D45" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45">
+      <c r="D55" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55">
         <v>15.1</v>
       </c>
-      <c r="F45" t="s">
-        <v>152</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="15">
-        <v>5</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46" s="15">
-        <v>7.6</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47">
-        <v>6</v>
-      </c>
-      <c r="B47" t="s">
-        <v>84</v>
-      </c>
-      <c r="C47" t="s">
-        <v>252</v>
-      </c>
-      <c r="D47" t="s">
-        <v>58</v>
-      </c>
-      <c r="E47">
-        <v>3.6</v>
-      </c>
-      <c r="F47" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="15">
-        <v>7</v>
-      </c>
-      <c r="B48" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="C48" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="D48" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E48" s="15">
-        <v>4.4</v>
-      </c>
-      <c r="F48" s="15" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49">
-        <v>8</v>
-      </c>
-      <c r="B49" t="s">
-        <v>264</v>
-      </c>
-      <c r="C49" t="s">
-        <v>265</v>
-      </c>
-      <c r="D49" t="s">
-        <v>62</v>
-      </c>
-      <c r="E49">
-        <v>3.5</v>
-      </c>
-      <c r="F49" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
-        <v>9</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E50" s="15">
-        <v>5.5</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" t="s">
-        <v>145</v>
-      </c>
-      <c r="B51" t="s">
-        <v>161</v>
-      </c>
-      <c r="C51" t="s">
-        <v>31</v>
-      </c>
-      <c r="D51" t="s">
-        <v>31</v>
-      </c>
-      <c r="E51">
-        <v>2.5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>260</v>
-      </c>
-    </row>
-    <row r="53" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="14" t="s">
+      <c r="F55" t="s">
         <v>266</v>
-      </c>
-      <c r="B53" s="14"/>
-      <c r="C53" s="14"/>
-      <c r="D53" s="14"/>
-      <c r="E53" s="14"/>
-      <c r="F53" s="14"/>
-    </row>
-    <row r="54" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="4" t="s">
-        <v>140</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>142</v>
-      </c>
-      <c r="D54" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="F54" s="4" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" t="s">
-        <v>145</v>
-      </c>
-      <c r="B55" t="s">
-        <v>146</v>
-      </c>
-      <c r="C55" t="s">
-        <v>237</v>
-      </c>
-      <c r="D55" t="s">
-        <v>31</v>
-      </c>
-      <c r="E55" t="s">
-        <v>31</v>
-      </c>
-      <c r="F55" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A56" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B56" s="15" t="s">
         <v>267</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>239</v>
+        <v>257</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>62</v>
       </c>
       <c r="E56" s="15">
-        <v>38.8</v>
+        <v>0.9</v>
       </c>
       <c r="F56" s="15" t="s">
         <v>268</v>
@@ -6739,33 +6739,33 @@
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A57">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B57" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="C57" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="D57" t="s">
         <v>50</v>
       </c>
       <c r="E57">
-        <v>5.3</v>
+        <v>15</v>
       </c>
       <c r="F57" t="s">
-        <v>206</v>
+        <v>170</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D58" s="15" t="s">
         <v>50</v>
@@ -6774,18 +6774,18 @@
         <v>9.2</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B59" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="C59" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D59" t="s">
         <v>50</v>
@@ -6794,18 +6794,18 @@
         <v>4.7</v>
       </c>
       <c r="F59" t="s">
-        <v>179</v>
+        <v>243</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B60" s="15" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="C60" s="15" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="D60" s="15" t="s">
         <v>58</v>
@@ -6814,15 +6814,15 @@
         <v>1.9</v>
       </c>
       <c r="F60" s="15" t="s">
-        <v>260</v>
+        <v>159</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B61" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C61" t="s">
         <v>31</v>
@@ -6834,7 +6834,7 @@
         <v>29.8</v>
       </c>
       <c r="F61" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
     </row>
     <row r="63" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -6849,33 +6849,33 @@
     </row>
     <row r="64" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A64" s="4" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C64" s="4" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D64" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E64" s="4" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="F64" s="4" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B65" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="C65" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D65" t="s">
         <v>31</v>
@@ -6892,19 +6892,19 @@
         <v>1</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>270</v>
+        <v>81</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E66" s="15">
-        <v>0.6</v>
+        <v>3.1</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>172</v>
+        <v>205</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -6912,19 +6912,19 @@
         <v>2</v>
       </c>
       <c r="B67" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="C67" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D67" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E67">
-        <v>3.2</v>
+        <v>14.9</v>
       </c>
       <c r="F67" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -6935,16 +6935,16 @@
         <v>251</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E68" s="15">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>154</v>
+        <v>270</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -6952,19 +6952,19 @@
         <v>4</v>
       </c>
       <c r="B69" t="s">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="C69" t="s">
-        <v>253</v>
+        <v>235</v>
       </c>
       <c r="D69" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E69">
-        <v>4.6</v>
+        <v>15.1</v>
       </c>
       <c r="F69" t="s">
-        <v>206</v>
+        <v>216</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
@@ -6981,10 +6981,10 @@
         <v>50</v>
       </c>
       <c r="E70" s="15">
-        <v>9.8</v>
+        <v>7.6</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>150</v>
+        <v>174</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.25">
@@ -6992,19 +6992,19 @@
         <v>6</v>
       </c>
       <c r="B71" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C71" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="D71" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E71">
-        <v>9.5</v>
+        <v>3.6</v>
       </c>
       <c r="F71" t="s">
-        <v>154</v>
+        <v>182</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.25">
@@ -7012,19 +7012,19 @@
         <v>7</v>
       </c>
       <c r="B72" s="15" t="s">
-        <v>271</v>
+        <v>253</v>
       </c>
       <c r="C72" s="15" t="s">
-        <v>237</v>
+        <v>252</v>
       </c>
       <c r="D72" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E72" s="15">
-        <v>4.8</v>
+        <v>4.4</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.25">
@@ -7032,27 +7032,27 @@
         <v>8</v>
       </c>
       <c r="B73" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="C73" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="D73" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E73">
-        <v>3.7</v>
+        <v>8.9</v>
       </c>
       <c r="F73" t="s">
-        <v>206</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A74" s="15" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="B74" s="15" t="s">
-        <v>161</v>
+        <v>166</v>
       </c>
       <c r="C74" s="15" t="s">
         <v>31</v>
@@ -7061,10 +7061,10 @@
         <v>31</v>
       </c>
       <c r="E74" s="15">
-        <v>2.8</v>
+        <v>2.5</v>
       </c>
       <c r="F74" s="15" t="s">
-        <v>174</v>
+        <v>159</v>
       </c>
     </row>
   </sheetData>
@@ -7073,9 +7073,9 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A29:F29"/>
-    <mergeCell ref="A39:F39"/>
-    <mergeCell ref="A53:F53"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A51:F51"/>
     <mergeCell ref="A63:F63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7102,7 +7102,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7122,57 +7122,57 @@
         <v>45</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="D3" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="E3" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="F3" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>278</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>279</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>280</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" t="s">
+        <v>240</v>
+      </c>
+      <c r="E4" t="s">
         <v>281</v>
-      </c>
-      <c r="D4" t="s">
-        <v>243</v>
-      </c>
-      <c r="E4" t="s">
-        <v>282</v>
       </c>
       <c r="F4" t="s">
         <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H4" t="s">
         <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J4" t="s">
         <v>76</v>
@@ -7180,31 +7180,31 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="B5" t="s">
         <v>50</v>
       </c>
       <c r="C5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D5" t="s">
         <v>252</v>
       </c>
       <c r="E5" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="F5" t="s">
         <v>80</v>
       </c>
       <c r="G5" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H5" t="s">
         <v>80</v>
       </c>
       <c r="I5" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J5" t="s">
         <v>76</v>
@@ -7218,25 +7218,25 @@
         <v>50</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D6" s="11" t="s">
         <v>252</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>76</v>
@@ -7244,31 +7244,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
       </c>
       <c r="C7" t="s">
+        <v>288</v>
+      </c>
+      <c r="D7" t="s">
+        <v>242</v>
+      </c>
+      <c r="E7" t="s">
         <v>289</v>
-      </c>
-      <c r="D7" t="s">
-        <v>239</v>
-      </c>
-      <c r="E7" t="s">
-        <v>290</v>
       </c>
       <c r="F7" t="s">
         <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H7" t="s">
         <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J7" t="s">
         <v>76</v>
@@ -7282,28 +7282,28 @@
         <v>50</v>
       </c>
       <c r="C8" s="9" t="s">
+        <v>290</v>
+      </c>
+      <c r="D8" s="9" t="s">
+        <v>214</v>
+      </c>
+      <c r="E8" s="9" t="s">
         <v>291</v>
-      </c>
-      <c r="D8" s="9" t="s">
-        <v>216</v>
-      </c>
-      <c r="E8" s="9" t="s">
-        <v>292</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
@@ -7314,25 +7314,25 @@
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D9" t="s">
         <v>200</v>
       </c>
       <c r="E9" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="F9" t="s">
         <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H9" t="s">
         <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J9" t="s">
         <v>51</v>
@@ -7340,31 +7340,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
+        <v>206</v>
+      </c>
+      <c r="B10" t="s">
+        <v>50</v>
+      </c>
+      <c r="C10" t="s">
+        <v>293</v>
+      </c>
+      <c r="D10" t="s">
         <v>207</v>
       </c>
-      <c r="B10" t="s">
-        <v>50</v>
-      </c>
-      <c r="C10" t="s">
-        <v>294</v>
-      </c>
-      <c r="D10" t="s">
-        <v>208</v>
-      </c>
       <c r="E10" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="F10" t="s">
         <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H10" t="s">
         <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J10" t="s">
         <v>51</v>
@@ -7378,25 +7378,25 @@
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D11" t="s">
         <v>197</v>
       </c>
       <c r="E11" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="F11" t="s">
         <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H11" t="s">
         <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J11" t="s">
         <v>51</v>
@@ -7410,25 +7410,25 @@
         <v>50</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>76</v>
@@ -7436,31 +7436,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D13" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="E13" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="F13" t="s">
         <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H13" t="s">
         <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J13" t="s">
         <v>51</v>
@@ -7474,28 +7474,28 @@
         <v>50</v>
       </c>
       <c r="C14" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D14" s="9" t="s">
+        <v>173</v>
+      </c>
+      <c r="E14" s="9" t="s">
         <v>300</v>
-      </c>
-      <c r="D14" s="9" t="s">
-        <v>151</v>
-      </c>
-      <c r="E14" s="9" t="s">
-        <v>301</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -7506,57 +7506,57 @@
         <v>50</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>157</v>
+        <v>171</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>244</v>
+        <v>256</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D16" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E16" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="F16" t="s">
         <v>78</v>
       </c>
       <c r="G16" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H16" t="s">
         <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="J16" t="s">
         <v>76</v>
@@ -7564,31 +7564,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D17" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E17" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="F17" t="s">
         <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H17" t="s">
         <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J17" t="s">
         <v>76</v>
@@ -7602,28 +7602,28 @@
         <v>50</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7634,28 +7634,28 @@
         <v>50</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -7666,25 +7666,25 @@
         <v>50</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>76</v>
@@ -7692,31 +7692,31 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>201</v>
+      </c>
+      <c r="B21" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" t="s">
+        <v>293</v>
+      </c>
+      <c r="D21" t="s">
         <v>202</v>
       </c>
-      <c r="B21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" t="s">
-        <v>294</v>
-      </c>
-      <c r="D21" t="s">
-        <v>203</v>
-      </c>
       <c r="E21" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F21" t="s">
         <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H21" t="s">
         <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J21" t="s">
         <v>51</v>
@@ -7724,31 +7724,31 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>148</v>
+        <v>157</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
       <c r="C22" t="s">
+        <v>311</v>
+      </c>
+      <c r="D22" t="s">
+        <v>158</v>
+      </c>
+      <c r="E22" t="s">
         <v>312</v>
-      </c>
-      <c r="D22" t="s">
-        <v>149</v>
-      </c>
-      <c r="E22" t="s">
-        <v>313</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H22" t="s">
         <v>80</v>
       </c>
       <c r="I22" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J22" t="s">
         <v>52</v>
@@ -7756,25 +7756,25 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>168</v>
+        <v>162</v>
       </c>
       <c r="B23" t="s">
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D23" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E23" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F23" t="s">
         <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H23" t="s">
         <v>80</v>
@@ -7794,19 +7794,19 @@
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D24" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E24" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="F24" t="s">
         <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H24" t="s">
         <v>80</v>
@@ -7820,25 +7820,25 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>163</v>
+        <v>152</v>
       </c>
       <c r="B25" t="s">
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D25" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="E25" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="F25" t="s">
         <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H25" t="s">
         <v>80</v>
@@ -7852,31 +7852,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
+        <v>203</v>
+      </c>
+      <c r="B26" t="s">
+        <v>50</v>
+      </c>
+      <c r="C26" t="s">
+        <v>293</v>
+      </c>
+      <c r="D26" t="s">
         <v>204</v>
       </c>
-      <c r="B26" t="s">
-        <v>50</v>
-      </c>
-      <c r="C26" t="s">
-        <v>294</v>
-      </c>
-      <c r="D26" t="s">
-        <v>205</v>
-      </c>
       <c r="E26" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="F26" t="s">
         <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H26" t="s">
         <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J26" t="s">
         <v>51</v>
@@ -7890,57 +7890,57 @@
         <v>50</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D28" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E28" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="F28" t="s">
         <v>78</v>
       </c>
       <c r="G28" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H28" t="s">
         <v>78</v>
       </c>
       <c r="I28" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="J28" t="s">
         <v>76</v>
@@ -7954,10 +7954,10 @@
         <v>50</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E29" s="11" t="s">
         <v>321</v>
@@ -7972,7 +7972,7 @@
         <v>78</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>76</v>
@@ -7989,7 +7989,7 @@
         <v>323</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E30" s="9" t="s">
         <v>324</v>
@@ -7998,16 +7998,16 @@
         <v>80</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -8018,7 +8018,7 @@
         <v>58</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D31" s="11" t="s">
         <v>252</v>
@@ -8030,13 +8030,13 @@
         <v>80</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>76</v>
@@ -8050,10 +8050,10 @@
         <v>58</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>159</v>
+        <v>169</v>
       </c>
       <c r="E32" s="11" t="s">
         <v>326</v>
@@ -8062,13 +8062,13 @@
         <v>80</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>52</v>
@@ -8082,10 +8082,10 @@
         <v>58</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E33" s="11" t="s">
         <v>327</v>
@@ -8094,7 +8094,7 @@
         <v>77</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>78</v>
@@ -8114,10 +8114,10 @@
         <v>58</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>153</v>
+        <v>186</v>
       </c>
       <c r="E34" s="9" t="s">
         <v>329</v>
@@ -8126,16 +8126,16 @@
         <v>80</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -8146,10 +8146,10 @@
         <v>58</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>155</v>
+        <v>188</v>
       </c>
       <c r="E35" s="9" t="s">
         <v>330</v>
@@ -8158,16 +8158,16 @@
         <v>80</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -8178,10 +8178,10 @@
         <v>58</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="E36" s="11" t="s">
         <v>331</v>
@@ -8190,13 +8190,13 @@
         <v>80</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>51</v>
@@ -8210,10 +8210,10 @@
         <v>58</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>177</v>
+        <v>160</v>
       </c>
       <c r="E37" s="11" t="s">
         <v>332</v>
@@ -8222,7 +8222,7 @@
         <v>80</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>78</v>
@@ -8242,10 +8242,10 @@
         <v>58</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>173</v>
+        <v>155</v>
       </c>
       <c r="E38" s="11" t="s">
         <v>334</v>
@@ -8254,13 +8254,13 @@
         <v>80</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>305</v>
+        <v>319</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>52</v>
@@ -8274,10 +8274,10 @@
         <v>58</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>253</v>
+        <v>236</v>
       </c>
       <c r="E39" s="11" t="s">
         <v>335</v>
@@ -8286,13 +8286,13 @@
         <v>80</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>336</v>
+        <v>319</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>76</v>
@@ -8309,54 +8309,54 @@
         <v>323</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>305</v>
+        <v>320</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D41" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="E41" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="F41" t="s">
         <v>78</v>
       </c>
       <c r="G41" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H41" t="s">
         <v>78</v>
       </c>
       <c r="I41" t="s">
-        <v>333</v>
+        <v>305</v>
       </c>
       <c r="J41" t="s">
         <v>76</v>
@@ -8364,31 +8364,31 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>267</v>
+        <v>241</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D42" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E42" t="s">
+        <v>338</v>
+      </c>
+      <c r="F42" t="s">
         <v>339</v>
       </c>
-      <c r="F42" t="s">
+      <c r="G42" t="s">
         <v>340</v>
       </c>
-      <c r="G42" t="s">
+      <c r="H42" t="s">
+        <v>339</v>
+      </c>
+      <c r="I42" t="s">
         <v>341</v>
-      </c>
-      <c r="H42" t="s">
-        <v>340</v>
-      </c>
-      <c r="I42" t="s">
-        <v>342</v>
       </c>
       <c r="J42" t="s">
         <v>76</v>
@@ -8402,57 +8402,57 @@
         <v>62</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E43" s="9" t="s">
+        <v>342</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="G43" s="9" t="s">
         <v>343</v>
       </c>
-      <c r="F43" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="G43" s="9" t="s">
+      <c r="H43" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I43" s="9" t="s">
         <v>344</v>
       </c>
-      <c r="H43" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="I43" s="9" t="s">
-        <v>345</v>
-      </c>
       <c r="J43" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="B44" t="s">
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D44" t="s">
         <v>200</v>
       </c>
       <c r="E44" t="s">
+        <v>345</v>
+      </c>
+      <c r="F44" t="s">
+        <v>339</v>
+      </c>
+      <c r="G44" t="s">
+        <v>341</v>
+      </c>
+      <c r="H44" t="s">
+        <v>339</v>
+      </c>
+      <c r="I44" t="s">
         <v>346</v>
-      </c>
-      <c r="F44" t="s">
-        <v>340</v>
-      </c>
-      <c r="G44" t="s">
-        <v>347</v>
-      </c>
-      <c r="H44" t="s">
-        <v>340</v>
-      </c>
-      <c r="I44" t="s">
-        <v>344</v>
       </c>
       <c r="J44" t="s">
         <v>51</v>
@@ -8460,31 +8460,31 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D45" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E45" t="s">
+        <v>347</v>
+      </c>
+      <c r="F45" t="s">
+        <v>339</v>
+      </c>
+      <c r="G45" t="s">
+        <v>343</v>
+      </c>
+      <c r="H45" t="s">
+        <v>339</v>
+      </c>
+      <c r="I45" t="s">
         <v>348</v>
-      </c>
-      <c r="F45" t="s">
-        <v>340</v>
-      </c>
-      <c r="G45" t="s">
-        <v>344</v>
-      </c>
-      <c r="H45" t="s">
-        <v>340</v>
-      </c>
-      <c r="I45" t="s">
-        <v>345</v>
       </c>
       <c r="J45" t="s">
         <v>76</v>
@@ -8498,57 +8498,57 @@
         <v>62</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E46" s="9" t="s">
         <v>349</v>
       </c>
       <c r="F46" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="G46" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="G46" s="9" t="s">
-        <v>341</v>
-      </c>
       <c r="H46" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I46" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="I46" s="9" t="s">
-        <v>344</v>
-      </c>
       <c r="J46" s="9" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>246</v>
+        <v>267</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D47" t="s">
-        <v>245</v>
+        <v>257</v>
       </c>
       <c r="E47" t="s">
         <v>350</v>
       </c>
       <c r="F47" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G47" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H47" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I47" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="J47" t="s">
         <v>76</v>
@@ -8556,31 +8556,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="D48" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="E48" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="F48" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G48" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="H48" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I48" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="J48" t="s">
         <v>76</v>
@@ -8588,31 +8588,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>230</v>
+        <v>223</v>
       </c>
       <c r="B49" t="s">
         <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D49" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="E49" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="F49" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G49" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="H49" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I49" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="J49" t="s">
         <v>51</v>
@@ -8626,25 +8626,25 @@
         <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="D50" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="E50" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="F50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G50" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H50" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I50" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="J50" t="s">
         <v>52</v>
@@ -8652,31 +8652,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="B51" t="s">
         <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D51" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E51" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="F51" t="s">
+        <v>339</v>
+      </c>
+      <c r="G51" t="s">
+        <v>341</v>
+      </c>
+      <c r="H51" t="s">
+        <v>339</v>
+      </c>
+      <c r="I51" t="s">
         <v>340</v>
-      </c>
-      <c r="G51" t="s">
-        <v>347</v>
-      </c>
-      <c r="H51" t="s">
-        <v>340</v>
-      </c>
-      <c r="I51" t="s">
-        <v>341</v>
       </c>
       <c r="J51" t="s">
         <v>76</v>
@@ -8684,31 +8684,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D52" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E52" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="F52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G52" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H52" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I52" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="J52" t="s">
         <v>76</v>
@@ -8722,57 +8722,57 @@
         <v>62</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E54" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="F54" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G54" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H54" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I54" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="J54" t="s">
         <v>76</v>
@@ -8786,57 +8786,57 @@
         <v>62</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="F55" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="G55" s="9" t="s">
+        <v>346</v>
+      </c>
+      <c r="H55" s="9" t="s">
+        <v>339</v>
+      </c>
+      <c r="I55" s="9" t="s">
         <v>340</v>
       </c>
-      <c r="G55" s="9" t="s">
-        <v>342</v>
-      </c>
-      <c r="H55" s="9" t="s">
-        <v>340</v>
-      </c>
-      <c r="I55" s="9" t="s">
-        <v>341</v>
-      </c>
       <c r="J55" s="9" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D56" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="E56" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="F56" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H56" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="I56" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="J56" t="s">
         <v>51</v>
@@ -8844,7 +8844,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -8878,7 +8878,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8886,7 +8886,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8903,7 +8903,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -8917,7 +8917,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -8931,7 +8931,7 @@
         <v>6</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -8942,10 +8942,10 @@
         <v>106</v>
       </c>
       <c r="C7">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -8959,7 +8959,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -8967,7 +8967,7 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9">
         <v>6</v>
@@ -8981,10 +8981,10 @@
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
         <v>369</v>
@@ -9051,7 +9051,7 @@
         <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16">
         <v>6</v>
@@ -9065,7 +9065,7 @@
         <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C17">
         <v>6</v>
@@ -9096,7 +9096,7 @@
         <v>103</v>
       </c>
       <c r="C20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D20" s="16" t="s">
         <v>377</v>
@@ -9124,7 +9124,7 @@
         <v>109</v>
       </c>
       <c r="C22">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="D22" s="16" t="s">
         <v>379</v>
@@ -9135,10 +9135,10 @@
         <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D23" s="16" t="s">
         <v>380</v>
@@ -9149,7 +9149,7 @@
         <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="C24">
         <v>8</v>

--- a/Estudo-Rotas-RJ-Eficiencia.xlsx
+++ b/Estudo-Rotas-RJ-Eficiencia.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="384">
   <si>
     <t>ESTUDO 2 — EFICIÊNCIA MÁXIMA · ROTAS RJ (Cleide · Lucas · Anderson)</t>
   </si>
@@ -79,7 +79,7 @@
     <t>Cleide — PROPOSTA</t>
   </si>
   <si>
-    <t>10h45</t>
+    <t>10h46</t>
   </si>
   <si>
     <t>Lucas — HOJE</t>
@@ -94,7 +94,7 @@
     <t>Lucas — PROPOSTA</t>
   </si>
   <si>
-    <t>15h25</t>
+    <t>15h59</t>
   </si>
   <si>
     <t>Anderson — HOJE</t>
@@ -106,7 +106,7 @@
     <t>Anderson — PROPOSTA</t>
   </si>
   <si>
-    <t>14h10</t>
+    <t>14h26</t>
   </si>
   <si>
     <t>TOTAL (3 promotores)</t>
@@ -118,10 +118,10 @@
     <t>53 lojas</t>
   </si>
   <si>
-    <t>130 → 115</t>
-  </si>
-  <si>
-    <t>1524 → 1380 km</t>
+    <t>130 → 114</t>
+  </si>
+  <si>
+    <t>1524 → 1407 km</t>
   </si>
   <si>
     <t>10 → 8 (1 dia)</t>
@@ -130,7 +130,7 @@
     <t>O QUE MUDA (resumo executivo)</t>
   </si>
   <si>
-    <t>• TODO MUNDO roda menos: Cleide 434 → 377 km (-57), Anderson 509 → 462 (-48), Lucas 581 → 542 (-39). Total -144 km/sem (-7%).</t>
+    <t>• TODO MUNDO roda menos: Cleide 434 → 379 km (-56), Anderson 509 → 475 (-35), Lucas 581 → 554 (-27). Total -117 km/sem (-7%).</t>
   </si>
   <si>
     <t>• Cleide (ônibus): seg/qua/sex viram loops LOCAIS de Nova Iguaçu/Mesquita/Nilópolis (37-42 km); ter/qui/sáb = corredor Meriti→Caxias (ônibus direto Via Light/Dutra). Nunca mais de 6 lojas/dia. Adeus Tijuca.</t>
@@ -142,7 +142,7 @@
     <t>• Anderson: semana 7/7/8/7/7/7 com o dia de 8 na QUARTA densa de Bangu/CG (8 lojas, ~46 km) — mesmo formato aceito no estudo 1. Território 100% dele no Oeste+Barra+Jacarepaguá, sem NENHUMA loja de outro no meio.</t>
   </si>
   <si>
-    <t>• Pior dia geral: 10 lojas → 8 (um único dia). Visitas: 35/38/42 (hoje 37/43/50). Sábados: 6/5/7.</t>
+    <t>• Pior dia geral: 10 lojas → 8 (um único dia). Visitas: 35/38/41 (hoje 37/43/50). Sábados: 6/5/7.</t>
   </si>
   <si>
     <t>• Custo do desenho: 14 transferências de loja (Caxias+Meriti inteiros pra Cleide, Tijuca inteira pro Lucas) — mais mudança operacional que o estudo 1 (4 transferências), em troca de −100 km/sem a mais.</t>
@@ -232,7 +232,7 @@
     <t>PREZUNIC VILA ISABEL</t>
   </si>
   <si>
-    <t>MUDANÇAS DE FREQUÊNCIA (14 lojas — padronização por rede)</t>
+    <t>MUDANÇAS DE FREQUÊNCIA (15 lojas — padronização por rede)</t>
   </si>
   <si>
     <t>Freq. hoje</t>
@@ -256,12 +256,15 @@
     <t>2x</t>
   </si>
   <si>
+    <t>ASSAÍ BANGU - 55 - RJ</t>
+  </si>
+  <si>
+    <t>3x</t>
+  </si>
+  <si>
     <t>ASSAÍ BANGU VK - 332 - RJ</t>
   </si>
   <si>
-    <t>3x</t>
-  </si>
-  <si>
     <t>ASSAÍ CESARIO DE MELO - 202 - RJ</t>
   </si>
   <si>
@@ -325,49 +328,49 @@
     <t>→</t>
   </si>
   <si>
+    <t>1h31</t>
+  </si>
+  <si>
+    <t>Terça</t>
+  </si>
+  <si>
+    <t>1h29</t>
+  </si>
+  <si>
+    <t>2h19</t>
+  </si>
+  <si>
+    <t>Quarta</t>
+  </si>
+  <si>
+    <t>2h06</t>
+  </si>
+  <si>
     <t>1h33</t>
   </si>
   <si>
-    <t>Terça</t>
-  </si>
-  <si>
-    <t>1h29</t>
-  </si>
-  <si>
-    <t>1h43</t>
-  </si>
-  <si>
-    <t>Quarta</t>
-  </si>
-  <si>
-    <t>2h06</t>
+    <t>Quinta</t>
+  </si>
+  <si>
+    <t>1h55</t>
+  </si>
+  <si>
+    <t>Sexta</t>
+  </si>
+  <si>
+    <t>2h02</t>
   </si>
   <si>
     <t>1h17</t>
   </si>
   <si>
-    <t>Quinta</t>
-  </si>
-  <si>
-    <t>2h20</t>
-  </si>
-  <si>
-    <t>Sexta</t>
-  </si>
-  <si>
-    <t>2h02</t>
-  </si>
-  <si>
-    <t>1h31</t>
-  </si>
-  <si>
     <t>Sábado</t>
   </si>
   <si>
     <t>1h53</t>
   </si>
   <si>
-    <t>2h21</t>
+    <t>2h11</t>
   </si>
   <si>
     <t>SEMANA</t>
@@ -379,76 +382,70 @@
     <t>2h44</t>
   </si>
   <si>
+    <t>2h47</t>
+  </si>
+  <si>
+    <t>2h18</t>
+  </si>
+  <si>
+    <t>2h38</t>
+  </si>
+  <si>
+    <t>2h50</t>
+  </si>
+  <si>
+    <t>2h40</t>
+  </si>
+  <si>
+    <t>2h41</t>
+  </si>
+  <si>
+    <t>2h36</t>
+  </si>
+  <si>
+    <t>2h52</t>
+  </si>
+  <si>
+    <t>2h31</t>
+  </si>
+  <si>
+    <t>Anderson (Moto)</t>
+  </si>
+  <si>
+    <t>2h35</t>
+  </si>
+  <si>
+    <t>2h46</t>
+  </si>
+  <si>
+    <t>1h57</t>
+  </si>
+  <si>
+    <t>1h41</t>
+  </si>
+  <si>
+    <t>2h45</t>
+  </si>
+  <si>
+    <t>2h53</t>
+  </si>
+  <si>
     <t>2h26</t>
   </si>
   <si>
-    <t>2h47</t>
-  </si>
-  <si>
-    <t>2h42</t>
-  </si>
-  <si>
-    <t>2h38</t>
-  </si>
-  <si>
-    <t>2h27</t>
-  </si>
-  <si>
-    <t>2h40</t>
-  </si>
-  <si>
-    <t>2h45</t>
-  </si>
-  <si>
-    <t>2h36</t>
-  </si>
-  <si>
-    <t>2h33</t>
-  </si>
-  <si>
-    <t>2h32</t>
-  </si>
-  <si>
-    <t>Anderson (Moto)</t>
-  </si>
-  <si>
-    <t>2h35</t>
-  </si>
-  <si>
     <t>2h39</t>
   </si>
   <si>
-    <t>2h46</t>
-  </si>
-  <si>
-    <t>2h18</t>
-  </si>
-  <si>
-    <t>1h41</t>
-  </si>
-  <si>
-    <t>2h53</t>
-  </si>
-  <si>
-    <t>1h21</t>
-  </si>
-  <si>
-    <t>2h52</t>
-  </si>
-  <si>
     <t>3h07</t>
   </si>
   <si>
-    <t>2h15</t>
-  </si>
-  <si>
     <t>Cleide de Oliveira Lira — ROTA PROPOSTA (Ônibus)</t>
   </si>
   <si>
     <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (carro, referência — ela roda de ônibus)</t>
   </si>
   <si>
-    <t>SEGUNDA — 6 lojas · 41.3 km · 1h33</t>
+    <t>SEGUNDA — 6 lojas · 41.1 km · 1h31</t>
   </si>
   <si>
     <t>#</t>
@@ -499,229 +496,238 @@
     <t>7 min</t>
   </si>
   <si>
+    <t>PREZUNIC NILÓPOLIS</t>
+  </si>
+  <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>ASSAÍ NILÓPOLIS - 36 - RJ</t>
+  </si>
+  <si>
+    <t>1 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ NOVA IGUAÇU - 30 - RJ</t>
+  </si>
+  <si>
+    <t>CASA (volta)</t>
+  </si>
+  <si>
+    <t>19 min</t>
+  </si>
+  <si>
+    <t>TERÇA — 6 lojas · 91 km · 2h19</t>
+  </si>
+  <si>
+    <t>Piam</t>
+  </si>
+  <si>
+    <t>25 min</t>
+  </si>
+  <si>
+    <t>Santa Cruz da Serra</t>
+  </si>
+  <si>
+    <t>41 min</t>
+  </si>
+  <si>
+    <t>São Bento</t>
+  </si>
+  <si>
+    <t>22 min</t>
+  </si>
+  <si>
+    <t>Vila Centenario</t>
+  </si>
+  <si>
+    <t>11 min</t>
+  </si>
+  <si>
+    <t>Venda Velha</t>
+  </si>
+  <si>
+    <t>2 min</t>
+  </si>
+  <si>
+    <t>24 min</t>
+  </si>
+  <si>
+    <t>QUARTA — 6 lojas · 41.3 km · 1h33</t>
+  </si>
+  <si>
     <t>Bairro Industrial</t>
   </si>
   <si>
-    <t>1 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ NILÓPOLIS - 36 - RJ</t>
-  </si>
-  <si>
-    <t>Centro</t>
-  </si>
-  <si>
     <t>18 min</t>
   </si>
   <si>
-    <t>ASSAÍ NOVA IGUAÇU - 30 - RJ</t>
-  </si>
-  <si>
-    <t>CASA (volta)</t>
-  </si>
-  <si>
-    <t>19 min</t>
-  </si>
-  <si>
-    <t>TERÇA — 6 lojas · 64.3 km · 1h43</t>
-  </si>
-  <si>
-    <t>Piam</t>
-  </si>
-  <si>
-    <t>25 min</t>
-  </si>
-  <si>
-    <t>São Bento</t>
+    <t>QUINTA — 6 lojas · 69.4 km · 1h55</t>
   </si>
   <si>
     <t>23 min</t>
   </si>
   <si>
-    <t>Vila Centenario</t>
-  </si>
-  <si>
-    <t>11 min</t>
+    <t>Vila São Luis</t>
+  </si>
+  <si>
+    <t>14 min</t>
+  </si>
+  <si>
+    <t>13 min</t>
+  </si>
+  <si>
+    <t>SEXTA — 5 lojas · 36.9 km · 1h17</t>
+  </si>
+  <si>
+    <t>6 min</t>
+  </si>
+  <si>
+    <t>29 min</t>
+  </si>
+  <si>
+    <t>SÁBADO — 6 lojas · 98.8 km · 2h11</t>
   </si>
   <si>
     <t>Vila Meriti</t>
   </si>
   <si>
-    <t>5 min</t>
-  </si>
-  <si>
-    <t>Venda Velha</t>
-  </si>
-  <si>
-    <t>13 min</t>
-  </si>
-  <si>
-    <t>2 min</t>
-  </si>
-  <si>
-    <t>24 min</t>
-  </si>
-  <si>
-    <t>QUARTA — 5 lojas · 36.9 km · 1h17</t>
-  </si>
-  <si>
-    <t>6 min</t>
-  </si>
-  <si>
-    <t>29 min</t>
-  </si>
-  <si>
-    <t>QUINTA — 6 lojas · 95 km · 2h20</t>
-  </si>
-  <si>
-    <t>22 min</t>
-  </si>
-  <si>
-    <t>Vila São Luis</t>
-  </si>
-  <si>
-    <t>14 min</t>
-  </si>
-  <si>
-    <t>Santa Cruz da Serra</t>
-  </si>
-  <si>
-    <t>SEXTA — 6 lojas · 41.1 km · 1h31</t>
-  </si>
-  <si>
-    <t>PREZUNIC NILÓPOLIS</t>
-  </si>
-  <si>
-    <t>SÁBADO — 6 lojas · 98.1 km · 2h21</t>
+    <t>35 min</t>
+  </si>
+  <si>
+    <t>Lucas Braz Monassa Vidal de Negreiros — ROTA PROPOSTA (Moto)</t>
+  </si>
+  <si>
+    <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (moto)</t>
+  </si>
+  <si>
+    <t>SEGUNDA — 7 lojas · 98.6 km · 2h47</t>
+  </si>
+  <si>
+    <t>ASSAÍ CORDOVIL - 231 - RJ</t>
+  </si>
+  <si>
+    <t>Cordovil</t>
+  </si>
+  <si>
+    <t>38 min</t>
+  </si>
+  <si>
+    <t>Vasco da Gama</t>
+  </si>
+  <si>
+    <t>Tijuca</t>
+  </si>
+  <si>
+    <t>10 min</t>
+  </si>
+  <si>
+    <t>Vila Isabel</t>
+  </si>
+  <si>
+    <t>ASSAÍ CAMPINHO - 37 - RJ</t>
+  </si>
+  <si>
+    <t>Campinho</t>
+  </si>
+  <si>
+    <t>51 min</t>
+  </si>
+  <si>
+    <t>TERÇA — 5 lojas · 83.3 km · 2h18</t>
+  </si>
+  <si>
+    <t>PREZUNIC VISTA ALEGRE</t>
+  </si>
+  <si>
+    <t>Vista Alegre</t>
+  </si>
+  <si>
+    <t>36 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ CARIOCA - 316 - RJ</t>
+  </si>
+  <si>
+    <t>Vila da Penha</t>
+  </si>
+  <si>
+    <t>8 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ MEIER - 160 - RJ</t>
+  </si>
+  <si>
+    <t>Méier</t>
+  </si>
+  <si>
+    <t>27 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ PILARES - 128 - RJ</t>
+  </si>
+  <si>
+    <t>Pilares</t>
+  </si>
+  <si>
+    <t>ASSAÍ CEASA - 42 - RJ</t>
+  </si>
+  <si>
+    <t>Irajá</t>
+  </si>
+  <si>
+    <t>20 min</t>
+  </si>
+  <si>
+    <t>37 min</t>
+  </si>
+  <si>
+    <t>QUARTA — 7 lojas · 99.6 km · 2h50</t>
+  </si>
+  <si>
+    <t>4 min</t>
+  </si>
+  <si>
+    <t>28 min</t>
+  </si>
+  <si>
+    <t>QUINTA — 6 lojas · 90.1 km · 2h41</t>
+  </si>
+  <si>
+    <t>Inhaúma</t>
+  </si>
+  <si>
+    <t>Benfica</t>
   </si>
   <si>
     <t>45 min</t>
   </si>
   <si>
-    <t>Lucas Braz Monassa Vidal de Negreiros — ROTA PROPOSTA (Moto)</t>
-  </si>
-  <si>
-    <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (moto)</t>
-  </si>
-  <si>
-    <t>SEGUNDA — 5 lojas · 83 km · 2h26</t>
-  </si>
-  <si>
-    <t>ASSAÍ CEASA - 42 - RJ</t>
-  </si>
-  <si>
-    <t>Irajá</t>
-  </si>
-  <si>
-    <t>37 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ CAMPINHO - 37 - RJ</t>
-  </si>
-  <si>
-    <t>Campinho</t>
-  </si>
-  <si>
-    <t>ASSAÍ MEIER - 160 - RJ</t>
-  </si>
-  <si>
-    <t>Méier</t>
-  </si>
-  <si>
-    <t>ASSAÍ PILARES - 128 - RJ</t>
-  </si>
-  <si>
-    <t>Pilares</t>
-  </si>
-  <si>
-    <t>10 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ CARIOCA - 316 - RJ</t>
-  </si>
-  <si>
-    <t>Vila da Penha</t>
-  </si>
-  <si>
-    <t>TERÇA — 7 lojas · 96.9 km · 2h42</t>
-  </si>
-  <si>
-    <t>ASSAÍ CORDOVIL - 231 - RJ</t>
-  </si>
-  <si>
-    <t>Cordovil</t>
-  </si>
-  <si>
-    <t>38 min</t>
-  </si>
-  <si>
-    <t>Vasco da Gama</t>
-  </si>
-  <si>
-    <t>Tijuca</t>
-  </si>
-  <si>
-    <t>Vila Isabel</t>
-  </si>
-  <si>
-    <t>Inhaúma</t>
-  </si>
-  <si>
-    <t>20 min</t>
-  </si>
-  <si>
-    <t>51 min</t>
-  </si>
-  <si>
-    <t>QUARTA — 7 lojas · 82.9 km · 2h27</t>
-  </si>
-  <si>
-    <t>PREZUNIC VISTA ALEGRE</t>
-  </si>
-  <si>
-    <t>Vista Alegre</t>
-  </si>
-  <si>
-    <t>36 min</t>
+    <t>SEXTA — 7 lojas · 95.6 km · 2h52</t>
+  </si>
+  <si>
+    <t>PREZUNIC CAMPINHO</t>
+  </si>
+  <si>
+    <t>58 min</t>
+  </si>
+  <si>
+    <t>SÁBADO — 6 lojas · 86.7 km · 2h31</t>
+  </si>
+  <si>
+    <t>PREZUNIC MÉIER</t>
   </si>
   <si>
     <t>17 min</t>
   </si>
   <si>
-    <t>PREZUNIC MÉIER</t>
-  </si>
-  <si>
-    <t>QUINTA — 7 lojas · 97.8 km · 2h45</t>
-  </si>
-  <si>
-    <t>4 min</t>
-  </si>
-  <si>
-    <t>8 min</t>
-  </si>
-  <si>
-    <t>SEXTA — 6 lojas · 85.1 km · 2h33</t>
-  </si>
-  <si>
-    <t>PREZUNIC CAMPINHO</t>
-  </si>
-  <si>
-    <t>SÁBADO — 6 lojas · 96 km · 2h32</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>53 min</t>
-  </si>
-  <si>
     <t>Anderson Camilo Supeleto — ROTA PROPOSTA (Moto)</t>
   </si>
   <si>
     <t>Saída: Est. do Pré, 674 - Campo Grande, Rio de Janeiro - RJ, 23013-550 · km/tempo por trecho = Google (moto)</t>
   </si>
   <si>
-    <t>SEGUNDA — 6 lojas · 91.8 km · 2h39</t>
+    <t>SEGUNDA — 6 lojas · 91.4 km · 2h52</t>
   </si>
   <si>
     <t>Campo Grande</t>
@@ -730,106 +736,106 @@
     <t>Realengo</t>
   </si>
   <si>
+    <t>ASSAÍ FREGUESIA 28 - RJ</t>
+  </si>
+  <si>
+    <t>Freguesia (Jacarepaguá)</t>
+  </si>
+  <si>
+    <t>33 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ BARRA DA TIJUCA - 245 - RJ</t>
+  </si>
+  <si>
+    <t>Barra da Tijuca</t>
+  </si>
+  <si>
+    <t>ASSAÍ AYRTON SENNA - 133 - RJ</t>
+  </si>
+  <si>
+    <t>Jacarepaguá</t>
+  </si>
+  <si>
     <t>ASSAÍ JACAREPAGUÁ MERCADÃO - 340 - RJ</t>
   </si>
   <si>
     <t>Taquara</t>
   </si>
   <si>
-    <t>ASSAÍ AYRTON SENNA - 133 - RJ</t>
-  </si>
-  <si>
-    <t>Jacarepaguá</t>
+    <t>12 min</t>
+  </si>
+  <si>
+    <t>DOM TAQUARA</t>
+  </si>
+  <si>
+    <t>TERÇA — 10 lojas · 62.8 km · 1h57</t>
+  </si>
+  <si>
+    <t>PREZUNIC TINGUÍ</t>
+  </si>
+  <si>
+    <t>ASSAÍ SANTA CRUZ - 201 - RJ</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
+  </si>
+  <si>
+    <t>21 min</t>
+  </si>
+  <si>
+    <t>Bangu</t>
+  </si>
+  <si>
+    <t>PREZUNIC SENADOR CAMARÁ</t>
+  </si>
+  <si>
+    <t>Senador Camará</t>
+  </si>
+  <si>
+    <t>9 min</t>
+  </si>
+  <si>
+    <t>PREZUNIC CAMPO GRANDE</t>
+  </si>
+  <si>
+    <t>QUARTA — 7 lojas · 93.9 km · 2h45</t>
+  </si>
+  <si>
+    <t>PREZUNIC FREGUESIA</t>
+  </si>
+  <si>
+    <t>3 min</t>
   </si>
   <si>
     <t>PREZUNIC BARRA MARAPENDI</t>
   </si>
   <si>
-    <t>Barra da Tijuca</t>
-  </si>
-  <si>
-    <t>12 min</t>
+    <t>63 min</t>
+  </si>
+  <si>
+    <t>QUINTA — 9 lojas · 73.2 km · 2h18</t>
+  </si>
+  <si>
+    <t>PREZUNIC SANTA CRUZ</t>
+  </si>
+  <si>
+    <t>SEXTA — 5 lojas · 92.9 km · 2h39</t>
   </si>
   <si>
     <t>PREZUNIC JARDIM OCEÂNICO</t>
   </si>
   <si>
-    <t>ASSAÍ BARRA DA TIJUCA - 245 - RJ</t>
-  </si>
-  <si>
-    <t>63 min</t>
-  </si>
-  <si>
-    <t>TERÇA — 8 lojas · 73.2 km · 2h18</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
-    <t>28 min</t>
-  </si>
-  <si>
-    <t>PREZUNIC SANTA CRUZ</t>
-  </si>
-  <si>
-    <t>ASSAÍ SANTA CRUZ - 201 - RJ</t>
-  </si>
-  <si>
-    <t>Bangu</t>
-  </si>
-  <si>
-    <t>ASSAÍ BANGU - 55 - RJ</t>
-  </si>
-  <si>
-    <t>QUARTA — 5 lojas · 95 km · 2h45</t>
-  </si>
-  <si>
     <t>68 min</t>
   </si>
   <si>
-    <t>ASSAÍ FREGUESIA 28 - RJ</t>
-  </si>
-  <si>
-    <t>Freguesia (Jacarepaguá)</t>
-  </si>
-  <si>
-    <t>DOM TAQUARA</t>
-  </si>
-  <si>
-    <t>QUINTA — 8 lojas · 37.7 km · 1h21</t>
-  </si>
-  <si>
-    <t>PREZUNIC TINGUÍ</t>
-  </si>
-  <si>
-    <t>PREZUNIC SENADOR CAMARÁ</t>
-  </si>
-  <si>
-    <t>Senador Camará</t>
-  </si>
-  <si>
-    <t>9 min</t>
-  </si>
-  <si>
-    <t>PREZUNIC CAMPO GRANDE</t>
-  </si>
-  <si>
-    <t>SEXTA — 7 lojas · 91.4 km · 2h52</t>
-  </si>
-  <si>
-    <t>33 min</t>
-  </si>
-  <si>
-    <t>PREZUNIC FREGUESIA</t>
-  </si>
-  <si>
-    <t>3 min</t>
-  </si>
-  <si>
-    <t>SÁBADO — 8 lojas · 72.4 km · 2h15</t>
-  </si>
-  <si>
-    <t>27 min</t>
+    <t>SÁBADO — 4 lojas · 60.4 km · 1h55</t>
+  </si>
+  <si>
+    <t>34 min</t>
+  </si>
+  <si>
+    <t>32 min</t>
   </si>
   <si>
     <t>TODAS AS LOJAS — DE/PARA (promotor, frequência e dias)</t>
@@ -877,6 +883,9 @@
     <t>R. Francisco Real, 2050 - Bangu, Rio de Janeiro - RJ, 21810-042</t>
   </si>
   <si>
+    <t>Ter/Qui</t>
+  </si>
+  <si>
     <t>Av. Brasil, 33809 - Bangu, Rio de Janeiro - RJ, 21852-002</t>
   </si>
   <si>
@@ -931,96 +940,93 @@
     <t>Estr. de Jacarepaguá, 7753 - Freguesia (Jacarepaguá), Rio de Janeiro - RJ, 22755-158</t>
   </si>
   <si>
-    <t>Ter/Qui</t>
+    <t>Seg/Qua</t>
+  </si>
+  <si>
+    <t>Estr. dos Bandeirantes, 1430 - Taquara, Rio de Janeiro - RJ, 22710-310</t>
+  </si>
+  <si>
+    <t>Av. Maracanã, 1188 - Tijuca, Rio de Janeiro - RJ, 20511-001</t>
+  </si>
+  <si>
+    <t>R. Mariz e Barros, 975 - Tijuca, Rio de Janeiro - RJ, 20270-004</t>
+  </si>
+  <si>
+    <t>Estr. do Mendanha, 3457 - Campo Grande, Rio de Janeiro - RJ, 23092-001</t>
+  </si>
+  <si>
+    <t>R. Dias da Cruz, 371 - Méier, Rio de Janeiro - RJ, 20720-010</t>
+  </si>
+  <si>
+    <t>BAIXADA</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 10521 - Jacutinga, Mesquita - RJ, 26574-751</t>
+  </si>
+  <si>
+    <t>Av. Getúlio de Moura, 1983 - Centro, Nilópolis - RJ, 26525-002</t>
+  </si>
+  <si>
+    <t>Av. Mal. Floriano Peixoto, 1448 - Centro, Nova Iguaçu - RJ, 26220-060</t>
+  </si>
+  <si>
+    <t>Av. Tancredo Neves, 3424 - Santa Eugenia, Nova Iguaçu - RJ, 26285-002</t>
+  </si>
+  <si>
+    <t>Av. Dom Hélder Câmara, 6350 - Pilares, Rio de Janeiro - RJ, 20771-001</t>
+  </si>
+  <si>
+    <t>Av. Brasil, 2251 - Vasco da Gama, Rio de Janeiro - RJ, 20930-041</t>
+  </si>
+  <si>
+    <t>Av. Padre Guilherme Decaminada, 2385 - Santa Cruz, Rio de Janeiro - RJ, 23575-000</t>
+  </si>
+  <si>
+    <t>Seg/Sex</t>
+  </si>
+  <si>
+    <t>Estr. da Pedra, 2.500 - Santa Cruz, Rio de Janeiro - RJ, 23520-241</t>
+  </si>
+  <si>
+    <t>Seg/Sex/Sáb</t>
+  </si>
+  <si>
+    <t>Qui/Sáb</t>
+  </si>
+  <si>
+    <t>MERITI</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 4301 - Centro, São João de Meriti - RJ, 25515-230</t>
+  </si>
+  <si>
+    <t>Av. Brasil, 32238 - Bangu, Rio de Janeiro - RJ, 21863-000</t>
+  </si>
+  <si>
+    <t>Av. Joaquim da Costa Lima, 2009 - Piam, Belford Roxo - RJ, 26183-000</t>
+  </si>
+  <si>
+    <t>Av. de Santa Cruz, Avenue, 12,516 - Campo Grande, Rio de Janeiro - RJ, 23010-002</t>
+  </si>
+  <si>
+    <t>Rod. Washington Luiz, 3853 - Vila São Luis, Duque de Caxias - RJ, 25065-135</t>
+  </si>
+  <si>
+    <t>Avenida Automóvel Clube QUADRA37L - LOTE 489 - Santa Cruz da Serra, Duque de Caxias - RJ, 25267-135</t>
+  </si>
+  <si>
+    <t>Ter/Sáb</t>
+  </si>
+  <si>
+    <t>Av. Itaóca, 2650 - Inhaúma, Rio de Janeiro - RJ, 21061-770</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 10201B - Bairro Industrial, Mesquita - RJ, 26574-751</t>
   </si>
   <si>
     <t>Qua/Sex</t>
   </si>
   <si>
-    <t>Estr. dos Bandeirantes, 1430 - Taquara, Rio de Janeiro - RJ, 22710-310</t>
-  </si>
-  <si>
-    <t>Av. Maracanã, 1188 - Tijuca, Rio de Janeiro - RJ, 20511-001</t>
-  </si>
-  <si>
-    <t>R. Mariz e Barros, 975 - Tijuca, Rio de Janeiro - RJ, 20270-004</t>
-  </si>
-  <si>
-    <t>Estr. do Mendanha, 3457 - Campo Grande, Rio de Janeiro - RJ, 23092-001</t>
-  </si>
-  <si>
-    <t>R. Dias da Cruz, 371 - Méier, Rio de Janeiro - RJ, 20720-010</t>
-  </si>
-  <si>
-    <t>BAIXADA</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 10521 - Jacutinga, Mesquita - RJ, 26574-751</t>
-  </si>
-  <si>
-    <t>Av. Getúlio de Moura, 1983 - Centro, Nilópolis - RJ, 26525-002</t>
-  </si>
-  <si>
-    <t>Av. Mal. Floriano Peixoto, 1448 - Centro, Nova Iguaçu - RJ, 26220-060</t>
-  </si>
-  <si>
-    <t>Av. Tancredo Neves, 3424 - Santa Eugenia, Nova Iguaçu - RJ, 26285-002</t>
-  </si>
-  <si>
-    <t>Av. Dom Hélder Câmara, 6350 - Pilares, Rio de Janeiro - RJ, 20771-001</t>
-  </si>
-  <si>
-    <t>Av. Brasil, 2251 - Vasco da Gama, Rio de Janeiro - RJ, 20930-041</t>
-  </si>
-  <si>
-    <t>Av. Padre Guilherme Decaminada, 2385 - Santa Cruz, Rio de Janeiro - RJ, 23575-000</t>
-  </si>
-  <si>
-    <t>Seg/Sex</t>
-  </si>
-  <si>
-    <t>Ter/Sáb</t>
-  </si>
-  <si>
-    <t>Estr. da Pedra, 2.500 - Santa Cruz, Rio de Janeiro - RJ, 23520-241</t>
-  </si>
-  <si>
-    <t>Seg/Sex/Sáb</t>
-  </si>
-  <si>
-    <t>MERITI</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 4301 - Centro, São João de Meriti - RJ, 25515-230</t>
-  </si>
-  <si>
-    <t>Av. Brasil, 32238 - Bangu, Rio de Janeiro - RJ, 21863-000</t>
-  </si>
-  <si>
-    <t>Av. Joaquim da Costa Lima, 2009 - Piam, Belford Roxo - RJ, 26183-000</t>
-  </si>
-  <si>
-    <t>Av. de Santa Cruz, Avenue, 12,516 - Campo Grande, Rio de Janeiro - RJ, 23010-002</t>
-  </si>
-  <si>
-    <t>Qui/Sáb</t>
-  </si>
-  <si>
-    <t>Rod. Washington Luiz, 3853 - Vila São Luis, Duque de Caxias - RJ, 25065-135</t>
-  </si>
-  <si>
-    <t>Avenida Automóvel Clube QUADRA37L - LOTE 489 - Santa Cruz da Serra, Duque de Caxias - RJ, 25267-135</t>
-  </si>
-  <si>
-    <t>Av. Itaóca, 2650 - Inhaúma, Rio de Janeiro - RJ, 21061-770</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 10201B - Bairro Industrial, Mesquita - RJ, 26574-751</t>
-  </si>
-  <si>
-    <t>Seg/Qua</t>
-  </si>
-  <si>
     <t>Rod. Pres. Dutra, 13900 - Jardim Tropical, Nova Iguaçu - RJ, 26015-005</t>
   </si>
   <si>
@@ -1042,33 +1048,33 @@
     <t>Ter</t>
   </si>
   <si>
+    <t>Qua</t>
+  </si>
+  <si>
+    <t>Av. Dom Hélder Câmara, 105 - Benfica, Rio de Janeiro - RJ, 20911-291</t>
+  </si>
+  <si>
+    <t>Qui</t>
+  </si>
+  <si>
+    <t>R. Cândido Benício, 20 - Campinho, Rio de Janeiro - RJ, 21320-060</t>
+  </si>
+  <si>
     <t>Seg</t>
   </si>
   <si>
-    <t>Av. Dom Hélder Câmara, 105 - Benfica, Rio de Janeiro - RJ, 20911-291</t>
-  </si>
-  <si>
-    <t>Qua</t>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Est. do Cabuçu, 1654 - Campo Grande, Rio de Janeiro - RJ, 23052-230</t>
+  </si>
+  <si>
+    <t>R. Dr. Manoel Reis, 175 - Vila Meriti, Duque de Caxias - RJ, 25025-010</t>
   </si>
   <si>
     <t>Sáb</t>
   </si>
   <si>
-    <t>R. Cândido Benício, 20 - Campinho, Rio de Janeiro - RJ, 21320-060</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>Est. do Cabuçu, 1654 - Campo Grande, Rio de Janeiro - RJ, 23052-230</t>
-  </si>
-  <si>
-    <t>Qui</t>
-  </si>
-  <si>
-    <t>R. Dr. Manoel Reis, 175 - Vila Meriti, Duque de Caxias - RJ, 25025-010</t>
-  </si>
-  <si>
     <t>Estr. de Jacarepaguá, 7153 - Freguesia (Jacarepaguá), Rio de Janeiro - RJ, 22753-033</t>
   </si>
   <si>
@@ -1111,58 +1117,58 @@
     <t>Link (Casa → paradas → Casa)</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.807575,-43.416172%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.747852,-43.392257%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.775841,-43.308631%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
+  </si>
+  <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.747852,-43.392257%7C-22.726211,-43.313020%7C-22.775841,-43.308631%7C-22.780278,-43.310000%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.747852,-43.392257%7C-22.726211,-43.313020%7C-22.781013,-43.286252%7C-22.775841,-43.308631%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
   </si>
   <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.761935,-43.445172%7C-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.804718,-43.418825&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.799075,-43.357408%7C-22.775841,-43.308631%7C-22.781013,-43.286252%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.747852,-43.392257&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.807575,-43.416172%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.726211,-43.313020%7C-22.641768,-43.277839%7C-22.781013,-43.286252%7C-22.775841,-43.308631%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.881347,-43.342096%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.914747,-43.241269%7C-22.871506,-43.277717&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.834535,-43.318511%7C-22.881347,-43.342096%7C-22.905431,-43.291154%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358%7C-22.827684,-43.338882&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.930622,-43.242526%7C-22.919957,-43.244485%7C-22.871506,-43.277717&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.881347,-43.342096%7C-22.883440,-43.343393%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.892195,-43.241108&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.935560,-43.372767%7C-22.959146,-43.356197%7C-23.000610,-43.356417%7C-23.008411,-43.316903%7C-23.001891,-43.323279&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.915624,-43.682502%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.941113,-43.343251%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.884020,-43.575133%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.879019,-43.465396%7C-22.882288,-43.488152%7C-22.893845,-43.534011%7C-22.913861,-43.544483&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.941113,-43.343251%7C-22.945679,-43.340096%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.893845,-43.534011&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.799075,-43.357408%7C-22.780278,-43.310000%7C-22.781013,-43.286252%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.775841,-43.308631&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.914747,-43.241269%7C-22.881347,-43.342096&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.834535,-43.318511%7C-22.849155,-43.311358%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.827684,-43.338882&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.930622,-43.242526%7C-22.919957,-43.244485%7C-22.881347,-43.342096&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.871506,-43.277717%7C-22.892195,-43.241108%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.881347,-43.342096%7C-22.883440,-43.343393&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.871506,-43.277717%7C-22.905431,-43.291154%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.941113,-43.343251%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.884020,-43.575133%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.882288,-43.488152%7C-22.893845,-43.534011%7C-22.913861,-43.544483&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.935560,-43.372767%7C-22.959146,-43.356197%7C-22.941113,-43.343251%7C-22.945679,-43.340096%7C-23.000610,-43.356417%7C-23.001891,-43.323279&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.915624,-43.682502%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.893845,-43.534011&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-23.008411,-43.316903%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.950972,-43.652551%7C-22.906919,-43.564898%7C-22.863251,-43.549364%7C-22.856798,-43.477684&amp;travelmode=driving</t>
   </si>
 </sst>
 </file>
@@ -1634,7 +1640,7 @@
   <sheetPr>
     <tabColor rgb="FFC19A2F"/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G63"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -1800,7 +1806,7 @@
         <v>35</v>
       </c>
       <c r="E14" s="6">
-        <v>376.7</v>
+        <v>378.5</v>
       </c>
       <c r="F14" s="6" t="s">
         <v>20</v>
@@ -1846,7 +1852,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="6">
-        <v>541.7</v>
+        <v>553.9</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -1889,16 +1895,16 @@
         <v>21</v>
       </c>
       <c r="D18" s="6">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" s="6">
-        <v>461.5</v>
+        <v>474.6</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="6">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2367,10 +2373,10 @@
         <v>76</v>
       </c>
       <c r="D50" s="11" t="s">
-        <v>77</v>
+        <v>80</v>
       </c>
       <c r="E50" s="11" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>31</v>
@@ -2430,10 +2436,10 @@
         <v>76</v>
       </c>
       <c r="D53" s="11" t="s">
+        <v>77</v>
+      </c>
+      <c r="E53" s="11" t="s">
         <v>80</v>
-      </c>
-      <c r="E53" s="11" t="s">
-        <v>78</v>
       </c>
       <c r="F53" s="12" t="s">
         <v>31</v>
@@ -2445,7 +2451,7 @@
         <v>84</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="C54" s="11" t="s">
         <v>76</v>
@@ -2469,7 +2475,7 @@
         <v>58</v>
       </c>
       <c r="C55" s="11" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D55" s="11" t="s">
         <v>80</v>
@@ -2484,7 +2490,7 @@
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="11" t="s">
-        <v>57</v>
+        <v>86</v>
       </c>
       <c r="B56" s="11" t="s">
         <v>58</v>
@@ -2505,7 +2511,7 @@
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B57" s="11" t="s">
         <v>58</v>
@@ -2526,13 +2532,13 @@
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="11" t="s">
-        <v>86</v>
+        <v>59</v>
       </c>
       <c r="B58" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C58" s="11" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D58" s="11" t="s">
         <v>80</v>
@@ -2553,7 +2559,7 @@
         <v>58</v>
       </c>
       <c r="C59" s="11" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="D59" s="11" t="s">
         <v>80</v>
@@ -2595,7 +2601,7 @@
         <v>58</v>
       </c>
       <c r="C61" s="11" t="s">
-        <v>76</v>
+        <v>52</v>
       </c>
       <c r="D61" s="11" t="s">
         <v>80</v>
@@ -2610,13 +2616,13 @@
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="11" t="s">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C62" s="11" t="s">
-        <v>52</v>
+        <v>76</v>
       </c>
       <c r="D62" s="11" t="s">
         <v>80</v>
@@ -2629,8 +2635,29 @@
       </c>
       <c r="G62" s="12"/>
     </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A63" s="11" t="s">
+        <v>60</v>
+      </c>
+      <c r="B63" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C63" s="11" t="s">
+        <v>52</v>
+      </c>
+      <c r="D63" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="E63" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="F63" s="12" t="s">
+        <v>31</v>
+      </c>
+      <c r="G63" s="12"/>
+    </row>
   </sheetData>
-  <mergeCells count="46">
+  <mergeCells count="47">
     <mergeCell ref="A1:G1"/>
     <mergeCell ref="A2:G2"/>
     <mergeCell ref="A4:G4"/>
@@ -2677,6 +2704,7 @@
     <mergeCell ref="F60:G60"/>
     <mergeCell ref="F61:G61"/>
     <mergeCell ref="F62:G62"/>
+    <mergeCell ref="F63:G63"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -2697,7 +2725,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -2709,7 +2737,7 @@
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -2721,33 +2749,33 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E4" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F4" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H4" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B5">
         <v>5</v>
@@ -2756,24 +2784,24 @@
         <v>98.3</v>
       </c>
       <c r="D5" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F5" s="11">
         <v>6</v>
       </c>
       <c r="G5">
-        <v>41.3</v>
+        <v>41.1</v>
       </c>
       <c r="H5" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B6">
         <v>7</v>
@@ -2782,24 +2810,24 @@
         <v>46.5</v>
       </c>
       <c r="D6" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F6" s="11">
         <v>6</v>
       </c>
       <c r="G6">
-        <v>64.3</v>
+        <v>91</v>
       </c>
       <c r="H6" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B7">
         <v>5</v>
@@ -2808,24 +2836,24 @@
         <v>94.9</v>
       </c>
       <c r="D7" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="E7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F7" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G7">
-        <v>36.9</v>
+        <v>41.3</v>
       </c>
       <c r="H7" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B8">
         <v>7</v>
@@ -2834,24 +2862,24 @@
         <v>46.5</v>
       </c>
       <c r="D8" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="E8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F8" s="11">
         <v>6</v>
       </c>
       <c r="G8">
-        <v>95</v>
+        <v>69.4</v>
       </c>
       <c r="H8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -2860,24 +2888,24 @@
         <v>98.7</v>
       </c>
       <c r="D9" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="E9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F9" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G9">
-        <v>41.1</v>
+        <v>36.9</v>
       </c>
       <c r="H9" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B10" s="5">
         <v>8</v>
@@ -2886,24 +2914,24 @@
         <v>49.1</v>
       </c>
       <c r="D10" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="E10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F10" s="11">
         <v>6</v>
       </c>
       <c r="G10">
-        <v>98.1</v>
+        <v>98.8</v>
       </c>
       <c r="H10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B11" s="13">
         <v>37</v>
@@ -2915,13 +2943,13 @@
         <v>18</v>
       </c>
       <c r="E11" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F11" s="13">
         <v>35</v>
       </c>
       <c r="G11" s="13">
-        <v>376.7</v>
+        <v>378.5</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>20</v>
@@ -2929,7 +2957,7 @@
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B13" s="3"/>
       <c r="C13" s="3"/>
@@ -2941,33 +2969,33 @@
     </row>
     <row r="14" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F14" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G14" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H14" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B15" s="5">
         <v>8</v>
@@ -2976,24 +3004,24 @@
         <v>90.6</v>
       </c>
       <c r="D15" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="E15" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F15" s="11">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G15">
-        <v>83</v>
+        <v>98.6</v>
       </c>
       <c r="H15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B16" s="5">
         <v>8</v>
@@ -3005,13 +3033,13 @@
         <v>121</v>
       </c>
       <c r="E16" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F16" s="11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G16">
-        <v>96.9</v>
+        <v>83.3</v>
       </c>
       <c r="H16" t="s">
         <v>122</v>
@@ -3019,7 +3047,7 @@
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B17">
         <v>7</v>
@@ -3031,13 +3059,13 @@
         <v>123</v>
       </c>
       <c r="E17" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F17" s="11">
         <v>7</v>
       </c>
       <c r="G17">
-        <v>82.9</v>
+        <v>99.6</v>
       </c>
       <c r="H17" t="s">
         <v>124</v>
@@ -3045,7 +3073,7 @@
     </row>
     <row r="18" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B18">
         <v>7</v>
@@ -3057,13 +3085,13 @@
         <v>125</v>
       </c>
       <c r="E18" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F18" s="11">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G18">
-        <v>97.8</v>
+        <v>90.1</v>
       </c>
       <c r="H18" t="s">
         <v>126</v>
@@ -3071,7 +3099,7 @@
     </row>
     <row r="19" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B19">
         <v>6</v>
@@ -3083,13 +3111,13 @@
         <v>127</v>
       </c>
       <c r="E19" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F19" s="11">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G19">
-        <v>85.1</v>
+        <v>95.6</v>
       </c>
       <c r="H19" t="s">
         <v>128</v>
@@ -3097,7 +3125,7 @@
     </row>
     <row r="20" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B20">
         <v>7</v>
@@ -3109,13 +3137,13 @@
         <v>125</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F20" s="11">
         <v>6</v>
       </c>
       <c r="G20">
-        <v>96</v>
+        <v>86.7</v>
       </c>
       <c r="H20" t="s">
         <v>129</v>
@@ -3123,7 +3151,7 @@
     </row>
     <row r="21" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A21" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B21" s="13">
         <v>43</v>
@@ -3135,13 +3163,13 @@
         <v>23</v>
       </c>
       <c r="E21" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F21" s="13">
         <v>38</v>
       </c>
       <c r="G21" s="13">
-        <v>541.7</v>
+        <v>553.9</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>25</v>
@@ -3161,33 +3189,33 @@
     </row>
     <row r="24" ht="20" customHeight="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>31</v>
       </c>
       <c r="F24" s="4" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="G24" s="4" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="H24" s="4" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="B25" s="5">
         <v>10</v>
@@ -3199,21 +3227,21 @@
         <v>131</v>
       </c>
       <c r="E25" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F25" s="11">
         <v>6</v>
       </c>
       <c r="G25">
-        <v>91.8</v>
+        <v>91.4</v>
       </c>
       <c r="H25" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B26">
         <v>6</v>
@@ -3222,24 +3250,24 @@
         <v>95.1</v>
       </c>
       <c r="D26" t="s">
+        <v>132</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" s="11">
+        <v>10</v>
+      </c>
+      <c r="G26">
+        <v>62.8</v>
+      </c>
+      <c r="H26" t="s">
         <v>133</v>
-      </c>
-      <c r="E26" t="s">
-        <v>101</v>
-      </c>
-      <c r="F26" s="11">
-        <v>8</v>
-      </c>
-      <c r="G26">
-        <v>73.2</v>
-      </c>
-      <c r="H26" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="5">
         <v>10</v>
@@ -3248,24 +3276,24 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
+        <v>134</v>
+      </c>
+      <c r="E27" t="s">
+        <v>102</v>
+      </c>
+      <c r="F27" s="11">
+        <v>7</v>
+      </c>
+      <c r="G27">
+        <v>93.9</v>
+      </c>
+      <c r="H27" t="s">
         <v>135</v>
-      </c>
-      <c r="E27" t="s">
-        <v>101</v>
-      </c>
-      <c r="F27" s="11">
-        <v>5</v>
-      </c>
-      <c r="G27">
-        <v>95</v>
-      </c>
-      <c r="H27" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B28">
         <v>7</v>
@@ -3277,21 +3305,21 @@
         <v>136</v>
       </c>
       <c r="E28" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F28" s="11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G28">
-        <v>37.7</v>
+        <v>73.2</v>
       </c>
       <c r="H28" t="s">
-        <v>137</v>
+        <v>122</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B29" s="5">
         <v>9</v>
@@ -3300,16 +3328,16 @@
         <v>77.4</v>
       </c>
       <c r="D29" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E29" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F29" s="11">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G29">
-        <v>91.4</v>
+        <v>92.9</v>
       </c>
       <c r="H29" t="s">
         <v>138</v>
@@ -3317,7 +3345,7 @@
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B30" s="5">
         <v>8</v>
@@ -3329,21 +3357,21 @@
         <v>139</v>
       </c>
       <c r="E30" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F30" s="11">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G30">
-        <v>72.4</v>
+        <v>60.4</v>
       </c>
       <c r="H30" t="s">
-        <v>140</v>
+        <v>111</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A31" s="13" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="B31" s="13">
         <v>50</v>
@@ -3355,13 +3383,13 @@
         <v>27</v>
       </c>
       <c r="E31" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="F31" s="13">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G31" s="13">
-        <v>461.5</v>
+        <v>474.6</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>29</v>
@@ -3393,7 +3421,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3403,7 +3431,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3413,7 +3441,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -3423,33 +3451,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" t="s">
         <v>149</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>150</v>
-      </c>
-      <c r="C6" t="s">
-        <v>151</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -3466,10 +3494,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>152</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>153</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>50</v>
@@ -3478,7 +3506,7 @@
         <v>7.9</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3486,10 +3514,10 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C8" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D8" t="s">
         <v>58</v>
@@ -3498,7 +3526,7 @@
         <v>5.5</v>
       </c>
       <c r="F8" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3506,10 +3534,10 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>157</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>158</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>50</v>
@@ -3518,7 +3546,7 @@
         <v>3.5</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3526,19 +3554,19 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>87</v>
+        <v>159</v>
       </c>
       <c r="C10" t="s">
         <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E10">
-        <v>0.9</v>
+        <v>8.2</v>
       </c>
       <c r="F10" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3546,19 +3574,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E11" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="F11" s="15" t="s">
         <v>162</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="15">
-        <v>8</v>
-      </c>
-      <c r="F11" s="15" t="s">
-        <v>164</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3566,10 +3594,10 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C12" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>
@@ -3578,15 +3606,15 @@
         <v>7.1</v>
       </c>
       <c r="F12" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>31</v>
@@ -3598,12 +3626,12 @@
         <v>8.5</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -3613,33 +3641,33 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" t="s">
         <v>149</v>
       </c>
-      <c r="B17" t="s">
+      <c r="C17" t="s">
         <v>150</v>
-      </c>
-      <c r="C17" t="s">
-        <v>151</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -3656,10 +3684,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>58</v>
@@ -3668,7 +3696,7 @@
         <v>16.3</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3676,19 +3704,19 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>59</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E19">
-        <v>11.4</v>
+        <v>24.8</v>
       </c>
       <c r="F19" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3696,19 +3724,19 @@
         <v>3</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>49</v>
+        <v>54</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="15">
-        <v>6.3</v>
+        <v>14.5</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3716,19 +3744,19 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>61</v>
+        <v>49</v>
       </c>
       <c r="C21" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D21" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E21">
-        <v>1.3</v>
+        <v>6.3</v>
       </c>
       <c r="F21" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3739,16 +3767,16 @@
         <v>60</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>58</v>
       </c>
       <c r="E22" s="15">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>178</v>
+        <v>155</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -3759,7 +3787,7 @@
         <v>55</v>
       </c>
       <c r="C23" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D23" t="s">
         <v>50</v>
@@ -3768,15 +3796,15 @@
         <v>0.9</v>
       </c>
       <c r="F23" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C24" s="15" t="s">
         <v>31</v>
@@ -3788,12 +3816,12 @@
         <v>20.9</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -3803,33 +3831,33 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
         <v>149</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>150</v>
-      </c>
-      <c r="C28" t="s">
-        <v>151</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
@@ -3846,10 +3874,10 @@
         <v>1</v>
       </c>
       <c r="B29" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C29" s="15" t="s">
         <v>152</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>153</v>
       </c>
       <c r="D29" s="15" t="s">
         <v>50</v>
@@ -3858,7 +3886,7 @@
         <v>7.9</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -3866,19 +3894,19 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>165</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>163</v>
+        <v>154</v>
       </c>
       <c r="D30" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E30">
-        <v>2</v>
+        <v>5.5</v>
       </c>
       <c r="F30" t="s">
-        <v>182</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -3886,19 +3914,19 @@
         <v>3</v>
       </c>
       <c r="B31" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="15" t="s">
         <v>157</v>
       </c>
-      <c r="C31" s="15" t="s">
+      <c r="D31" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="F31" s="15" t="s">
         <v>158</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -3906,10 +3934,10 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C32" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="D32" t="s">
         <v>58</v>
@@ -3918,7 +3946,7 @@
         <v>0.9</v>
       </c>
       <c r="F32" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -3926,10 +3954,10 @@
         <v>5</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="D33" s="15" t="s">
         <v>50</v>
@@ -3938,412 +3966,412 @@
         <v>8</v>
       </c>
       <c r="F33" s="15" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34">
+        <v>6</v>
+      </c>
+      <c r="B34" t="s">
+        <v>163</v>
+      </c>
+      <c r="C34" t="s">
+        <v>160</v>
+      </c>
+      <c r="D34" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34">
+        <v>7.1</v>
+      </c>
+      <c r="F34" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B35" s="15" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34" t="s">
+      <c r="C35" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E35" s="15">
+        <v>8.5</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B37" s="14"/>
+      <c r="C37" s="14"/>
+      <c r="D37" s="14"/>
+      <c r="E37" s="14"/>
+      <c r="F37" s="14"/>
+    </row>
+    <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F38" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>148</v>
+      </c>
+      <c r="B39" t="s">
         <v>149</v>
       </c>
-      <c r="B34" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" t="s">
-        <v>31</v>
-      </c>
-      <c r="D34" t="s">
-        <v>31</v>
-      </c>
-      <c r="E34">
+      <c r="C39" t="s">
+        <v>150</v>
+      </c>
+      <c r="D39" t="s">
+        <v>31</v>
+      </c>
+      <c r="E39" t="s">
+        <v>31</v>
+      </c>
+      <c r="F39" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="15">
+        <v>1</v>
+      </c>
+      <c r="B40" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C40" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="D40" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E40" s="15">
+        <v>16.3</v>
+      </c>
+      <c r="F40" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41">
+        <v>2</v>
+      </c>
+      <c r="B41" t="s">
+        <v>54</v>
+      </c>
+      <c r="C41" t="s">
+        <v>171</v>
+      </c>
+      <c r="D41" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41">
+        <v>11.4</v>
+      </c>
+      <c r="F41" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="15">
+        <v>3</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42" s="15">
+        <v>8.3</v>
+      </c>
+      <c r="F42" s="15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
+        <v>49</v>
+      </c>
+      <c r="C43" t="s">
+        <v>173</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43">
+        <v>4.2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="15">
+        <v>5</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E44" s="15">
+        <v>7.4</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>6</v>
+      </c>
+      <c r="B45" t="s">
+        <v>55</v>
+      </c>
+      <c r="C45" t="s">
+        <v>160</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45">
+        <v>0.9</v>
+      </c>
+      <c r="F45" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E46" s="15">
+        <v>20.9</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="14" t="s">
+        <v>186</v>
+      </c>
+      <c r="B48" s="14"/>
+      <c r="C48" s="14"/>
+      <c r="D48" s="14"/>
+      <c r="E48" s="14"/>
+      <c r="F48" s="14"/>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D49" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E49" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F49" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>148</v>
+      </c>
+      <c r="B50" t="s">
+        <v>149</v>
+      </c>
+      <c r="C50" t="s">
+        <v>150</v>
+      </c>
+      <c r="D50" t="s">
+        <v>31</v>
+      </c>
+      <c r="E50" t="s">
+        <v>31</v>
+      </c>
+      <c r="F50" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="15">
+        <v>1</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>151</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>152</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51" s="15">
+        <v>7.9</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
+        <v>2</v>
+      </c>
+      <c r="B52" t="s">
+        <v>163</v>
+      </c>
+      <c r="C52" t="s">
+        <v>160</v>
+      </c>
+      <c r="D52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52">
+        <v>2</v>
+      </c>
+      <c r="F52" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
+        <v>3</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>156</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E53" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54">
+        <v>4</v>
+      </c>
+      <c r="B54" t="s">
+        <v>88</v>
+      </c>
+      <c r="C54" t="s">
+        <v>179</v>
+      </c>
+      <c r="D54" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54">
+        <v>0.9</v>
+      </c>
+      <c r="F54" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="15">
+        <v>5</v>
+      </c>
+      <c r="B55" s="15" t="s">
+        <v>161</v>
+      </c>
+      <c r="C55" s="15" t="s">
+        <v>160</v>
+      </c>
+      <c r="D55" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55" s="15">
+        <v>8</v>
+      </c>
+      <c r="F55" s="15" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>148</v>
+      </c>
+      <c r="B56" t="s">
+        <v>164</v>
+      </c>
+      <c r="C56" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56">
         <v>14</v>
       </c>
-      <c r="F34" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="36" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" s="14" t="s">
-        <v>184</v>
-      </c>
-      <c r="B36" s="14"/>
-      <c r="C36" s="14"/>
-      <c r="D36" s="14"/>
-      <c r="E36" s="14"/>
-      <c r="F36" s="14"/>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D37" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E37" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F37" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>149</v>
-      </c>
-      <c r="B38" t="s">
-        <v>150</v>
-      </c>
-      <c r="C38" t="s">
-        <v>151</v>
-      </c>
-      <c r="D38" t="s">
-        <v>31</v>
-      </c>
-      <c r="E38" t="s">
-        <v>31</v>
-      </c>
-      <c r="F38" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="15">
-        <v>1</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>55</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="15">
-        <v>19.5</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40">
-        <v>2</v>
-      </c>
-      <c r="B40" t="s">
-        <v>49</v>
-      </c>
-      <c r="C40" t="s">
-        <v>173</v>
-      </c>
-      <c r="D40" t="s">
-        <v>50</v>
-      </c>
-      <c r="E40">
-        <v>10.5</v>
-      </c>
-      <c r="F40" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
-        <v>3</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>186</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E41" s="15">
-        <v>4.8</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>4</v>
-      </c>
-      <c r="B42" t="s">
-        <v>59</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="F56" t="s">
         <v>188</v>
-      </c>
-      <c r="D42" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42">
-        <v>17.9</v>
-      </c>
-      <c r="F42" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15">
-        <v>5</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>54</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>171</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="15">
-        <v>14.5</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>6</v>
-      </c>
-      <c r="B44" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" t="s">
-        <v>169</v>
-      </c>
-      <c r="D44" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44">
-        <v>12</v>
-      </c>
-      <c r="F44" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E45" s="15">
-        <v>15.9</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="47" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="14" t="s">
-        <v>189</v>
-      </c>
-      <c r="B47" s="14"/>
-      <c r="C47" s="14"/>
-      <c r="D47" s="14"/>
-      <c r="E47" s="14"/>
-      <c r="F47" s="14"/>
-    </row>
-    <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D48" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E48" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F48" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" t="s">
-        <v>149</v>
-      </c>
-      <c r="B49" t="s">
-        <v>150</v>
-      </c>
-      <c r="C49" t="s">
-        <v>151</v>
-      </c>
-      <c r="D49" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" t="s">
-        <v>31</v>
-      </c>
-      <c r="F49" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="15">
-        <v>1</v>
-      </c>
-      <c r="B50" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="C50" s="15" t="s">
-        <v>153</v>
-      </c>
-      <c r="D50" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E50" s="15">
-        <v>7.9</v>
-      </c>
-      <c r="F50" s="15" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51">
-        <v>2</v>
-      </c>
-      <c r="B51" t="s">
-        <v>88</v>
-      </c>
-      <c r="C51" t="s">
-        <v>155</v>
-      </c>
-      <c r="D51" t="s">
-        <v>58</v>
-      </c>
-      <c r="E51">
-        <v>5.5</v>
-      </c>
-      <c r="F51" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="15">
-        <v>3</v>
-      </c>
-      <c r="B52" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="D52" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52" s="15">
-        <v>3.5</v>
-      </c>
-      <c r="F52" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53">
-        <v>4</v>
-      </c>
-      <c r="B53" t="s">
-        <v>190</v>
-      </c>
-      <c r="C53" t="s">
-        <v>163</v>
-      </c>
-      <c r="D53" t="s">
-        <v>62</v>
-      </c>
-      <c r="E53">
-        <v>8.2</v>
-      </c>
-      <c r="F53" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="15">
-        <v>5</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>162</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>163</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="15">
-        <v>0.4</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>6</v>
-      </c>
-      <c r="B55" t="s">
-        <v>165</v>
-      </c>
-      <c r="C55" t="s">
-        <v>163</v>
-      </c>
-      <c r="D55" t="s">
-        <v>50</v>
-      </c>
-      <c r="E55">
-        <v>7.1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E56" s="15">
-        <v>8.5</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -4353,33 +4381,33 @@
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B59" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B59" s="4" t="s">
+      <c r="C59" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F59" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F59" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>148</v>
+      </c>
+      <c r="B60" t="s">
         <v>149</v>
       </c>
-      <c r="B60" t="s">
+      <c r="C60" t="s">
         <v>150</v>
-      </c>
-      <c r="C60" t="s">
-        <v>151</v>
       </c>
       <c r="D60" t="s">
         <v>31</v>
@@ -4396,19 +4424,19 @@
         <v>1</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="D61" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E61" s="15">
-        <v>30.7</v>
+        <v>19.5</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>192</v>
+        <v>172</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4416,19 +4444,19 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C62" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="D62" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E62">
-        <v>16.9</v>
+        <v>10</v>
       </c>
       <c r="F62" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4439,16 +4467,16 @@
         <v>57</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="D63" s="15" t="s">
         <v>58</v>
       </c>
       <c r="E63" s="15">
-        <v>17.1</v>
+        <v>3.7</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>164</v>
+        <v>174</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4456,19 +4484,19 @@
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>49</v>
+        <v>59</v>
       </c>
       <c r="C64" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="D64" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E64">
-        <v>4.2</v>
+        <v>17.9</v>
       </c>
       <c r="F64" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4476,19 +4504,19 @@
         <v>5</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>177</v>
+        <v>171</v>
       </c>
       <c r="D65" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E65" s="15">
-        <v>7.4</v>
+        <v>14.5</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>156</v>
+        <v>172</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4496,27 +4524,27 @@
         <v>6</v>
       </c>
       <c r="B66" t="s">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="C66" t="s">
-        <v>163</v>
+        <v>173</v>
       </c>
       <c r="D66" t="s">
         <v>50</v>
       </c>
       <c r="E66">
-        <v>0.9</v>
+        <v>6.3</v>
       </c>
       <c r="F66" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>31</v>
@@ -4525,10 +4553,10 @@
         <v>31</v>
       </c>
       <c r="E67" s="15">
-        <v>20.9</v>
+        <v>27</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>180</v>
+        <v>191</v>
       </c>
     </row>
   </sheetData>
@@ -4538,8 +4566,8 @@
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A36:F36"/>
-    <mergeCell ref="A47:F47"/>
+    <mergeCell ref="A37:F37"/>
+    <mergeCell ref="A48:F48"/>
     <mergeCell ref="A58:F58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4561,7 +4589,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4571,7 +4599,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4581,7 +4609,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -4591,33 +4619,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" t="s">
         <v>149</v>
       </c>
-      <c r="B6" t="s">
+      <c r="C6" t="s">
         <v>150</v>
-      </c>
-      <c r="C6" t="s">
-        <v>151</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -4634,19 +4662,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>196</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="D7" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E7" s="15">
+        <v>28.4</v>
+      </c>
+      <c r="F7" s="15" t="s">
         <v>197</v>
-      </c>
-      <c r="D7" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E7" s="15">
-        <v>27.4</v>
-      </c>
-      <c r="F7" s="15" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4654,19 +4682,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
       </c>
       <c r="E8">
-        <v>8.2</v>
+        <v>11.3</v>
       </c>
       <c r="F8" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4674,19 +4702,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>201</v>
+        <v>66</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="15">
-        <v>8</v>
+        <v>6.9</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4694,19 +4722,19 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>203</v>
+        <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
       </c>
       <c r="E10">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="F10" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4714,237 +4742,237 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E11" s="15">
-        <v>6.7</v>
+        <v>1.8</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>154</v>
+        <v>187</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" t="s">
+      <c r="A12">
+        <v>6</v>
+      </c>
+      <c r="B12" t="s">
+        <v>70</v>
+      </c>
+      <c r="C12" t="s">
+        <v>201</v>
+      </c>
+      <c r="D12" t="s">
+        <v>62</v>
+      </c>
+      <c r="E12">
+        <v>1.4</v>
+      </c>
+      <c r="F12" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A13" s="15">
+        <v>7</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>202</v>
+      </c>
+      <c r="C13" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E13" s="15">
+        <v>12.6</v>
+      </c>
+      <c r="F13" s="15" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>148</v>
+      </c>
+      <c r="B14" t="s">
+        <v>164</v>
+      </c>
+      <c r="C14" t="s">
+        <v>31</v>
+      </c>
+      <c r="D14" t="s">
+        <v>31</v>
+      </c>
+      <c r="E14">
+        <v>33.4</v>
+      </c>
+      <c r="F14" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" s="14" t="s">
+        <v>205</v>
+      </c>
+      <c r="B16" s="14"/>
+      <c r="C16" s="14"/>
+      <c r="D16" s="14"/>
+      <c r="E16" s="14"/>
+      <c r="F16" s="14"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>148</v>
+      </c>
+      <c r="B18" t="s">
         <v>149</v>
       </c>
-      <c r="B12" t="s">
-        <v>166</v>
-      </c>
-      <c r="C12" t="s">
-        <v>31</v>
-      </c>
-      <c r="D12" t="s">
-        <v>31</v>
-      </c>
-      <c r="E12">
-        <v>29.4</v>
-      </c>
-      <c r="F12" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="14" t="s">
-        <v>208</v>
-      </c>
-      <c r="B14" s="14"/>
-      <c r="C14" s="14"/>
-      <c r="D14" s="14"/>
-      <c r="E14" s="14"/>
-      <c r="F14" s="14"/>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F15" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" t="s">
-        <v>149</v>
-      </c>
-      <c r="B16" t="s">
+      <c r="C18" t="s">
         <v>150</v>
       </c>
-      <c r="C16" t="s">
-        <v>151</v>
-      </c>
-      <c r="D16" t="s">
-        <v>31</v>
-      </c>
-      <c r="E16" t="s">
-        <v>31</v>
-      </c>
-      <c r="F16" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="15">
-        <v>1</v>
-      </c>
-      <c r="B17" s="15" t="s">
-        <v>209</v>
-      </c>
-      <c r="C17" s="15" t="s">
-        <v>210</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E17" s="15">
-        <v>28.4</v>
-      </c>
-      <c r="F17" s="15" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18">
-        <v>2</v>
-      </c>
-      <c r="B18" t="s">
-        <v>67</v>
-      </c>
-      <c r="C18" t="s">
-        <v>212</v>
-      </c>
       <c r="D18" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18">
-        <v>11.3</v>
+        <v>31</v>
+      </c>
+      <c r="E18" t="s">
+        <v>31</v>
       </c>
       <c r="F18" t="s">
-        <v>156</v>
+        <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>66</v>
+        <v>206</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E19" s="15">
-        <v>6.9</v>
+        <v>25.5</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>154</v>
+        <v>208</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>65</v>
+        <v>209</v>
       </c>
       <c r="C20" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="D20" t="s">
         <v>50</v>
       </c>
       <c r="E20">
-        <v>2.8</v>
+        <v>2.6</v>
       </c>
       <c r="F20" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="15">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>63</v>
+        <v>212</v>
       </c>
       <c r="C21" s="15" t="s">
+        <v>213</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E21" s="15">
+        <v>14.4</v>
+      </c>
+      <c r="F21" s="15" t="s">
         <v>214</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21" s="15">
-        <v>1.8</v>
-      </c>
-      <c r="F21" s="15" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B22" t="s">
-        <v>70</v>
+        <v>215</v>
       </c>
       <c r="C22" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D22" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E22">
-        <v>1.4</v>
+        <v>3.3</v>
       </c>
       <c r="F22" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="15">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>86</v>
+        <v>217</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>215</v>
+        <v>218</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E23" s="15">
-        <v>9.4</v>
+        <v>10.4</v>
       </c>
       <c r="F23" s="15" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B24" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C24" t="s">
         <v>31</v>
@@ -4953,15 +4981,15 @@
         <v>31</v>
       </c>
       <c r="E24">
-        <v>34.8</v>
+        <v>27</v>
       </c>
       <c r="F24" t="s">
-        <v>217</v>
+        <v>220</v>
       </c>
     </row>
     <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="14" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="B26" s="14"/>
       <c r="C26" s="14"/>
@@ -4971,33 +4999,33 @@
     </row>
     <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B27" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B27" s="4" t="s">
+      <c r="C27" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D27" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E27" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F27" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" t="s">
         <v>149</v>
       </c>
-      <c r="B28" t="s">
+      <c r="C28" t="s">
         <v>150</v>
-      </c>
-      <c r="C28" t="s">
-        <v>151</v>
       </c>
       <c r="D28" t="s">
         <v>31</v>
@@ -5014,19 +5042,19 @@
         <v>1</v>
       </c>
       <c r="B29" s="15" t="s">
-        <v>219</v>
+        <v>195</v>
       </c>
       <c r="C29" s="15" t="s">
-        <v>220</v>
+        <v>196</v>
       </c>
       <c r="D29" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E29" s="15">
-        <v>25.5</v>
+        <v>28.4</v>
       </c>
       <c r="F29" s="15" t="s">
-        <v>221</v>
+        <v>197</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
@@ -5034,19 +5062,19 @@
         <v>2</v>
       </c>
       <c r="B30" t="s">
-        <v>199</v>
+        <v>67</v>
       </c>
       <c r="C30" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="D30" t="s">
         <v>50</v>
       </c>
       <c r="E30">
-        <v>6.8</v>
+        <v>11.3</v>
       </c>
       <c r="F30" t="s">
-        <v>222</v>
+        <v>155</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
@@ -5054,19 +5082,19 @@
         <v>3</v>
       </c>
       <c r="B31" s="15" t="s">
-        <v>223</v>
+        <v>66</v>
       </c>
       <c r="C31" s="15" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D31" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E31" s="15">
-        <v>7.5</v>
+        <v>6.9</v>
       </c>
       <c r="F31" s="15" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.25">
@@ -5074,19 +5102,19 @@
         <v>4</v>
       </c>
       <c r="B32" t="s">
-        <v>201</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="D32" t="s">
         <v>50</v>
       </c>
       <c r="E32">
-        <v>0.5</v>
+        <v>2.8</v>
       </c>
       <c r="F32" t="s">
-        <v>179</v>
+        <v>200</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
@@ -5094,19 +5122,19 @@
         <v>5</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>203</v>
+        <v>69</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E33" s="15">
-        <v>3.2</v>
+        <v>0.9</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>205</v>
+        <v>222</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
@@ -5114,19 +5142,19 @@
         <v>6</v>
       </c>
       <c r="B34" t="s">
-        <v>206</v>
+        <v>63</v>
       </c>
       <c r="C34" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="D34" t="s">
         <v>50</v>
       </c>
       <c r="E34">
-        <v>6.4</v>
+        <v>2.5</v>
       </c>
       <c r="F34" t="s">
-        <v>154</v>
+        <v>211</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
@@ -5134,27 +5162,27 @@
         <v>7</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E35" s="15">
-        <v>5.9</v>
+        <v>13.3</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C36" t="s">
         <v>31</v>
@@ -5163,10 +5191,10 @@
         <v>31</v>
       </c>
       <c r="E36">
-        <v>27</v>
+        <v>33.4</v>
       </c>
       <c r="F36" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
@@ -5181,33 +5209,33 @@
     </row>
     <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B39" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="C39" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D39" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E39" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F39" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" t="s">
         <v>149</v>
       </c>
-      <c r="B40" t="s">
+      <c r="C40" t="s">
         <v>150</v>
-      </c>
-      <c r="C40" t="s">
-        <v>151</v>
       </c>
       <c r="D40" t="s">
         <v>31</v>
@@ -5224,19 +5252,19 @@
         <v>1</v>
       </c>
       <c r="B41" s="15" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C41" s="15" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D41" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E41" s="15">
-        <v>28.4</v>
+        <v>27.4</v>
       </c>
       <c r="F41" s="15" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.25">
@@ -5244,19 +5272,19 @@
         <v>2</v>
       </c>
       <c r="B42" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C42" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D42" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E42">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="F42" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.25">
@@ -5264,19 +5292,19 @@
         <v>3</v>
       </c>
       <c r="B43" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C43" s="15" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="D43" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E43" s="15">
-        <v>6.9</v>
+        <v>6.6</v>
       </c>
       <c r="F43" s="15" t="s">
-        <v>154</v>
+        <v>184</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
@@ -5284,7 +5312,7 @@
         <v>4</v>
       </c>
       <c r="B44" t="s">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="C44" t="s">
         <v>213</v>
@@ -5293,10 +5321,10 @@
         <v>50</v>
       </c>
       <c r="E44">
-        <v>2.8</v>
+        <v>6.9</v>
       </c>
       <c r="F44" t="s">
-        <v>205</v>
+        <v>155</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
@@ -5304,19 +5332,19 @@
         <v>5</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>69</v>
+        <v>215</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>213</v>
+        <v>216</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E45" s="15">
-        <v>0.9</v>
+        <v>3.2</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>225</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
@@ -5324,254 +5352,254 @@
         <v>6</v>
       </c>
       <c r="B46" t="s">
+        <v>209</v>
+      </c>
+      <c r="C46" t="s">
+        <v>210</v>
+      </c>
+      <c r="D46" t="s">
+        <v>50</v>
+      </c>
+      <c r="E46">
+        <v>6.4</v>
+      </c>
+      <c r="F46" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B47" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C47" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47" s="15">
+        <v>29.4</v>
+      </c>
+      <c r="F47" s="15" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="14" t="s">
+        <v>228</v>
+      </c>
+      <c r="B49" s="14"/>
+      <c r="C49" s="14"/>
+      <c r="D49" s="14"/>
+      <c r="E49" s="14"/>
+      <c r="F49" s="14"/>
+    </row>
+    <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E50" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F50" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>148</v>
+      </c>
+      <c r="B51" t="s">
+        <v>149</v>
+      </c>
+      <c r="C51" t="s">
+        <v>150</v>
+      </c>
+      <c r="D51" t="s">
+        <v>31</v>
+      </c>
+      <c r="E51" t="s">
+        <v>31</v>
+      </c>
+      <c r="F51" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
+        <v>1</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52" s="15">
+        <v>28.4</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>2</v>
+      </c>
+      <c r="B53" t="s">
+        <v>67</v>
+      </c>
+      <c r="C53" t="s">
+        <v>198</v>
+      </c>
+      <c r="D53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E53">
+        <v>11.3</v>
+      </c>
+      <c r="F53" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>3</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>199</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E54" s="15">
+        <v>6.9</v>
+      </c>
+      <c r="F54" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
+        <v>4</v>
+      </c>
+      <c r="B55" t="s">
+        <v>65</v>
+      </c>
+      <c r="C55" t="s">
+        <v>199</v>
+      </c>
+      <c r="D55" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55">
+        <v>2.8</v>
+      </c>
+      <c r="F55" t="s">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="15">
+        <v>5</v>
+      </c>
+      <c r="B56" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="C46" t="s">
-        <v>214</v>
-      </c>
-      <c r="D46" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46">
-        <v>2.5</v>
-      </c>
-      <c r="F46" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="15">
+      <c r="C56" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E56" s="15">
+        <v>1.8</v>
+      </c>
+      <c r="F56" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57">
+        <v>6</v>
+      </c>
+      <c r="B57" t="s">
+        <v>202</v>
+      </c>
+      <c r="C57" t="s">
+        <v>203</v>
+      </c>
+      <c r="D57" t="s">
+        <v>50</v>
+      </c>
+      <c r="E57">
+        <v>13.3</v>
+      </c>
+      <c r="F57" t="s">
+        <v>223</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" s="15">
         <v>7</v>
       </c>
-      <c r="B47" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E47" s="15">
-        <v>10.1</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" t="s">
-        <v>149</v>
-      </c>
-      <c r="B48" t="s">
-        <v>166</v>
-      </c>
-      <c r="C48" t="s">
-        <v>31</v>
-      </c>
-      <c r="D48" t="s">
-        <v>31</v>
-      </c>
-      <c r="E48">
-        <v>34.8</v>
-      </c>
-      <c r="F48" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" s="14" t="s">
-        <v>227</v>
-      </c>
-      <c r="B50" s="14"/>
-      <c r="C50" s="14"/>
-      <c r="D50" s="14"/>
-      <c r="E50" s="14"/>
-      <c r="F50" s="14"/>
-    </row>
-    <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D51" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E51" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F51" s="4" t="s">
+      <c r="B58" s="15" t="s">
+        <v>229</v>
+      </c>
+      <c r="C58" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="D58" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E58" s="15">
+        <v>0.4</v>
+      </c>
+      <c r="F58" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" t="s">
-        <v>149</v>
-      </c>
-      <c r="B52" t="s">
-        <v>150</v>
-      </c>
-      <c r="C52" t="s">
-        <v>151</v>
-      </c>
-      <c r="D52" t="s">
-        <v>31</v>
-      </c>
-      <c r="E52" t="s">
-        <v>31</v>
-      </c>
-      <c r="F52" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="15">
-        <v>1</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>197</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E53" s="15">
-        <v>27.4</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>198</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>2</v>
-      </c>
-      <c r="B54" t="s">
-        <v>199</v>
-      </c>
-      <c r="C54" t="s">
-        <v>200</v>
-      </c>
-      <c r="D54" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54">
-        <v>8.2</v>
-      </c>
-      <c r="F54" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="15">
-        <v>3</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>228</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>200</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E55" s="15">
-        <v>0.4</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56">
-        <v>4</v>
-      </c>
-      <c r="B56" t="s">
-        <v>201</v>
-      </c>
-      <c r="C56" t="s">
-        <v>202</v>
-      </c>
-      <c r="D56" t="s">
-        <v>50</v>
-      </c>
-      <c r="E56">
-        <v>10.1</v>
-      </c>
-      <c r="F56" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="15">
-        <v>5</v>
-      </c>
-      <c r="B57" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="C57" s="15" t="s">
-        <v>204</v>
-      </c>
-      <c r="D57" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E57" s="15">
-        <v>3.2</v>
-      </c>
-      <c r="F57" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58">
-        <v>6</v>
-      </c>
-      <c r="B58" t="s">
-        <v>206</v>
-      </c>
-      <c r="C58" t="s">
-        <v>207</v>
-      </c>
-      <c r="D58" t="s">
-        <v>50</v>
-      </c>
-      <c r="E58">
-        <v>6.4</v>
-      </c>
-      <c r="F58" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B59" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C59" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D59" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E59" s="15">
-        <v>29.4</v>
-      </c>
-      <c r="F59" s="15" t="s">
-        <v>192</v>
+      <c r="B59" t="s">
+        <v>164</v>
+      </c>
+      <c r="C59" t="s">
+        <v>31</v>
+      </c>
+      <c r="D59" t="s">
+        <v>31</v>
+      </c>
+      <c r="E59">
+        <v>30.7</v>
+      </c>
+      <c r="F59" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -5581,33 +5609,33 @@
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B62" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B62" s="4" t="s">
+      <c r="C62" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E62" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F62" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F62" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>148</v>
+      </c>
+      <c r="B63" t="s">
         <v>149</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>150</v>
-      </c>
-      <c r="C63" t="s">
-        <v>151</v>
       </c>
       <c r="D63" t="s">
         <v>31</v>
@@ -5624,19 +5652,19 @@
         <v>1</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E64" s="15">
-        <v>28.4</v>
+        <v>27.4</v>
       </c>
       <c r="F64" s="15" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -5644,19 +5672,19 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>67</v>
+        <v>87</v>
       </c>
       <c r="C65" t="s">
-        <v>212</v>
+        <v>225</v>
       </c>
       <c r="D65" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E65">
-        <v>11.3</v>
+        <v>10.2</v>
       </c>
       <c r="F65" t="s">
-        <v>156</v>
+        <v>177</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -5664,19 +5692,19 @@
         <v>3</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>66</v>
+        <v>232</v>
       </c>
       <c r="C66" s="15" t="s">
         <v>213</v>
       </c>
       <c r="D66" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E66" s="15">
-        <v>6.9</v>
+        <v>9.6</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>154</v>
+        <v>233</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5684,7 +5712,7 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>65</v>
+        <v>212</v>
       </c>
       <c r="C67" t="s">
         <v>213</v>
@@ -5693,10 +5721,10 @@
         <v>50</v>
       </c>
       <c r="E67">
-        <v>2.8</v>
+        <v>0.5</v>
       </c>
       <c r="F67" t="s">
-        <v>205</v>
+        <v>176</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5704,19 +5732,19 @@
         <v>5</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>63</v>
+        <v>215</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E68" s="15">
-        <v>1.8</v>
+        <v>3.2</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>182</v>
+        <v>200</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5724,27 +5752,27 @@
         <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>68</v>
+        <v>209</v>
       </c>
       <c r="C69" t="s">
-        <v>230</v>
+        <v>210</v>
       </c>
       <c r="D69" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E69">
-        <v>5.1</v>
+        <v>6.4</v>
       </c>
       <c r="F69" t="s">
-        <v>187</v>
+        <v>153</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>31</v>
@@ -5753,10 +5781,10 @@
         <v>31</v>
       </c>
       <c r="E70" s="15">
-        <v>39.8</v>
+        <v>29.4</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
   </sheetData>
@@ -5764,10 +5792,10 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A26:F26"/>
     <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A50:F50"/>
+    <mergeCell ref="A49:F49"/>
     <mergeCell ref="A61:F61"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5777,7 +5805,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F74"/>
+  <dimension ref="A1:F73"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="6" customWidth="1"/>
@@ -5789,7 +5817,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5799,7 +5827,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5809,7 +5837,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -5819,33 +5847,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B5" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="C5" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F5" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F5" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>148</v>
+      </c>
+      <c r="B6" t="s">
         <v>149</v>
       </c>
-      <c r="B6" t="s">
-        <v>150</v>
-      </c>
       <c r="C6" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5862,10 +5890,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>58</v>
@@ -5874,7 +5902,7 @@
         <v>14.8</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>183</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5882,19 +5910,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C8" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
       </c>
       <c r="E8">
-        <v>12</v>
+        <v>15.1</v>
       </c>
       <c r="F8" t="s">
-        <v>180</v>
+        <v>241</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5902,19 +5930,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="15">
-        <v>6.3</v>
+        <v>15.9</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>187</v>
+        <v>223</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5922,19 +5950,19 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="C10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E10">
-        <v>8.3</v>
+        <v>9.2</v>
       </c>
       <c r="F10" t="s">
-        <v>243</v>
+        <v>184</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5942,19 +5970,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E11" s="15">
-        <v>5.6</v>
+        <v>4.7</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>205</v>
+        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -5962,27 +5990,27 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>247</v>
       </c>
       <c r="D12" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E12">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="F12" t="s">
-        <v>226</v>
+        <v>158</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>31</v>
@@ -5991,15 +6019,15 @@
         <v>31</v>
       </c>
       <c r="E13" s="15">
-        <v>41.8</v>
+        <v>29.8</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>246</v>
+        <v>204</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -6009,33 +6037,33 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B16" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="C16" s="4" t="s">
         <v>145</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>146</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F16" s="4" t="s">
         <v>147</v>
-      </c>
-      <c r="F16" s="4" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>148</v>
+      </c>
+      <c r="B17" t="s">
         <v>149</v>
       </c>
-      <c r="B17" t="s">
-        <v>150</v>
-      </c>
       <c r="C17" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -6052,10 +6080,10 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="D18" s="15" t="s">
         <v>50</v>
@@ -6064,7 +6092,7 @@
         <v>3.1</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -6072,19 +6100,19 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>83</v>
+        <v>251</v>
       </c>
       <c r="C19" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D19" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E19">
-        <v>14.9</v>
+        <v>3.8</v>
       </c>
       <c r="F19" t="s">
-        <v>249</v>
+        <v>174</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -6092,19 +6120,19 @@
         <v>3</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E20" s="15">
-        <v>6.6</v>
+        <v>13</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>222</v>
+        <v>254</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -6112,19 +6140,19 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>251</v>
+        <v>83</v>
       </c>
       <c r="C21" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
       </c>
       <c r="E21">
-        <v>6.5</v>
+        <v>15.1</v>
       </c>
       <c r="F21" t="s">
-        <v>187</v>
+        <v>219</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -6132,19 +6160,19 @@
         <v>5</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="D22" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E22" s="15">
-        <v>15.1</v>
+        <v>7.6</v>
       </c>
       <c r="F22" s="15" t="s">
-        <v>216</v>
+        <v>174</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -6152,19 +6180,19 @@
         <v>6</v>
       </c>
       <c r="B23" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="C23" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D23" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E23">
-        <v>7.6</v>
+        <v>3.6</v>
       </c>
       <c r="F23" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -6172,19 +6200,19 @@
         <v>7</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E24" s="15">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="F24" s="15" t="s">
-        <v>182</v>
+        <v>174</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -6192,879 +6220,859 @@
         <v>8</v>
       </c>
       <c r="B25" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="C25" t="s">
-        <v>252</v>
+        <v>257</v>
       </c>
       <c r="D25" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E25">
-        <v>4.4</v>
+        <v>3.5</v>
       </c>
       <c r="F25" t="s">
-        <v>174</v>
+        <v>258</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="15" t="s">
+      <c r="A26" s="15">
+        <v>9</v>
+      </c>
+      <c r="B26" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E26" s="15">
+        <v>5.5</v>
+      </c>
+      <c r="F26" s="15" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27">
+        <v>10</v>
+      </c>
+      <c r="B27" t="s">
+        <v>259</v>
+      </c>
+      <c r="C27" t="s">
+        <v>237</v>
+      </c>
+      <c r="D27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E27">
+        <v>3</v>
+      </c>
+      <c r="F27" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="15" t="s">
+        <v>148</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E28" s="15">
+        <v>0.3</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="14" t="s">
+        <v>260</v>
+      </c>
+      <c r="B30" s="14"/>
+      <c r="C30" s="14"/>
+      <c r="D30" s="14"/>
+      <c r="E30" s="14"/>
+      <c r="F30" s="14"/>
+    </row>
+    <row r="31" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F31" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>148</v>
+      </c>
+      <c r="B32" t="s">
         <v>149</v>
       </c>
-      <c r="B26" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E26" s="15">
-        <v>11.4</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="14" t="s">
-        <v>254</v>
-      </c>
-      <c r="B28" s="14"/>
-      <c r="C28" s="14"/>
-      <c r="D28" s="14"/>
-      <c r="E28" s="14"/>
-      <c r="F28" s="14"/>
-    </row>
-    <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E29" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F29" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>149</v>
-      </c>
-      <c r="B30" t="s">
-        <v>150</v>
-      </c>
-      <c r="C30" t="s">
-        <v>235</v>
-      </c>
-      <c r="D30" t="s">
-        <v>31</v>
-      </c>
-      <c r="E30" t="s">
-        <v>31</v>
-      </c>
-      <c r="F30" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="15">
-        <v>1</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>245</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="15">
-        <v>43.9</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>255</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>2</v>
-      </c>
-      <c r="B32" t="s">
-        <v>239</v>
-      </c>
       <c r="C32" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32">
-        <v>9.2</v>
+        <v>31</v>
+      </c>
+      <c r="E32" t="s">
+        <v>31</v>
       </c>
       <c r="F32" t="s">
-        <v>187</v>
+        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>256</v>
+        <v>90</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>257</v>
+        <v>238</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E33" s="15">
-        <v>3.1</v>
+        <v>14.8</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="B34" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="C34" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D34" t="s">
         <v>50</v>
       </c>
       <c r="E34">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="F34" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
+        <v>3</v>
+      </c>
+      <c r="B35" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C35" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D35" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E35" s="15">
+        <v>6.3</v>
+      </c>
+      <c r="F35" s="15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36">
+        <v>4</v>
+      </c>
+      <c r="B36" t="s">
+        <v>239</v>
+      </c>
+      <c r="C36" t="s">
+        <v>240</v>
+      </c>
+      <c r="D36" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36">
+        <v>3.1</v>
+      </c>
+      <c r="F36" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="15">
         <v>5</v>
       </c>
-      <c r="B35" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E35" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>149</v>
-      </c>
-      <c r="B36" t="s">
-        <v>166</v>
-      </c>
-      <c r="C36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36">
-        <v>29.8</v>
-      </c>
-      <c r="F36" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>259</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>148</v>
+      <c r="B37" s="15" t="s">
+        <v>261</v>
+      </c>
+      <c r="C37" s="15" t="s">
+        <v>240</v>
+      </c>
+      <c r="D37" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E37" s="15">
+        <v>0.9</v>
+      </c>
+      <c r="F37" s="15" t="s">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38">
+        <v>6</v>
+      </c>
+      <c r="B38" t="s">
+        <v>263</v>
+      </c>
+      <c r="C38" t="s">
+        <v>243</v>
+      </c>
+      <c r="D38" t="s">
+        <v>62</v>
+      </c>
+      <c r="E38">
+        <v>9.8</v>
+      </c>
+      <c r="F38" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
+        <v>7</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="15">
+        <v>5.3</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>200</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
+        <v>148</v>
+      </c>
+      <c r="B40" t="s">
+        <v>164</v>
+      </c>
+      <c r="C40" t="s">
+        <v>31</v>
+      </c>
+      <c r="D40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E40">
+        <v>41.8</v>
+      </c>
+      <c r="F40" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="42" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="14" t="s">
+        <v>265</v>
+      </c>
+      <c r="B42" s="14"/>
+      <c r="C42" s="14"/>
+      <c r="D42" s="14"/>
+      <c r="E42" s="14"/>
+      <c r="F42" s="14"/>
+    </row>
+    <row r="43" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D43" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E43" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F43" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>148</v>
+      </c>
+      <c r="B44" t="s">
         <v>149</v>
       </c>
-      <c r="B40" t="s">
-        <v>150</v>
-      </c>
-      <c r="C40" t="s">
-        <v>235</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
-        <v>1</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="15">
-        <v>3.1</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>2</v>
-      </c>
-      <c r="B42" t="s">
-        <v>260</v>
-      </c>
-      <c r="C42" t="s">
-        <v>235</v>
-      </c>
-      <c r="D42" t="s">
-        <v>62</v>
-      </c>
-      <c r="E42">
-        <v>3.8</v>
-      </c>
-      <c r="F42" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15">
-        <v>3</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43" s="15">
-        <v>6.6</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>4</v>
-      </c>
-      <c r="B44" t="s">
-        <v>79</v>
-      </c>
       <c r="C44" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D44" t="s">
-        <v>50</v>
-      </c>
-      <c r="E44">
-        <v>7.6</v>
+        <v>31</v>
+      </c>
+      <c r="E44" t="s">
+        <v>31</v>
       </c>
       <c r="F44" t="s">
-        <v>174</v>
+        <v>31</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>253</v>
+        <v>82</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>252</v>
+        <v>237</v>
       </c>
       <c r="D45" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E45" s="15">
-        <v>4.4</v>
+        <v>3.1</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="B46" t="s">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="D46" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E46">
-        <v>3.5</v>
+        <v>14.9</v>
       </c>
       <c r="F46" t="s">
-        <v>263</v>
+        <v>223</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>75</v>
+        <v>266</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>235</v>
+        <v>253</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E47" s="15">
-        <v>5.5</v>
+        <v>6.6</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>263</v>
+        <v>233</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
+        <v>4</v>
+      </c>
+      <c r="B48" t="s">
+        <v>252</v>
+      </c>
+      <c r="C48" t="s">
+        <v>253</v>
+      </c>
+      <c r="D48" t="s">
+        <v>50</v>
+      </c>
+      <c r="E48">
+        <v>6.5</v>
+      </c>
+      <c r="F48" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" s="15">
+        <v>5</v>
+      </c>
+      <c r="B49" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C49" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D49" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E49" s="15">
+        <v>15.1</v>
+      </c>
+      <c r="F49" s="15" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50">
+        <v>6</v>
+      </c>
+      <c r="B50" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" t="s">
+        <v>255</v>
+      </c>
+      <c r="D50" t="s">
+        <v>50</v>
+      </c>
+      <c r="E50">
+        <v>7.6</v>
+      </c>
+      <c r="F50" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51" s="15">
+        <v>7</v>
+      </c>
+      <c r="B51" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C51" s="15" t="s">
+        <v>255</v>
+      </c>
+      <c r="D51" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E51" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52">
         <v>8</v>
       </c>
-      <c r="B48" t="s">
-        <v>264</v>
-      </c>
-      <c r="C48" t="s">
-        <v>235</v>
-      </c>
-      <c r="D48" t="s">
+      <c r="B52" t="s">
+        <v>79</v>
+      </c>
+      <c r="C52" t="s">
+        <v>255</v>
+      </c>
+      <c r="D52" t="s">
+        <v>50</v>
+      </c>
+      <c r="E52">
+        <v>4.4</v>
+      </c>
+      <c r="F52" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53" s="15">
+        <v>9</v>
+      </c>
+      <c r="B53" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C53" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D53" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E53" s="15">
+        <v>8.9</v>
+      </c>
+      <c r="F53" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>148</v>
+      </c>
+      <c r="B54" t="s">
+        <v>164</v>
+      </c>
+      <c r="C54" t="s">
+        <v>31</v>
+      </c>
+      <c r="D54" t="s">
+        <v>31</v>
+      </c>
+      <c r="E54">
+        <v>2.5</v>
+      </c>
+      <c r="F54" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="56" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="14" t="s">
+        <v>267</v>
+      </c>
+      <c r="B56" s="14"/>
+      <c r="C56" s="14"/>
+      <c r="D56" s="14"/>
+      <c r="E56" s="14"/>
+      <c r="F56" s="14"/>
+    </row>
+    <row r="57" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D57" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E57" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F57" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>148</v>
+      </c>
+      <c r="B58" t="s">
+        <v>149</v>
+      </c>
+      <c r="C58" t="s">
+        <v>237</v>
+      </c>
+      <c r="D58" t="s">
+        <v>31</v>
+      </c>
+      <c r="E58" t="s">
+        <v>31</v>
+      </c>
+      <c r="F58" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A59" s="15">
+        <v>1</v>
+      </c>
+      <c r="B59" s="15" t="s">
+        <v>268</v>
+      </c>
+      <c r="C59" s="15" t="s">
+        <v>243</v>
+      </c>
+      <c r="D59" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="E48">
+      <c r="E59" s="15">
+        <v>44.2</v>
+      </c>
+      <c r="F59" s="15" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A60">
+        <v>2</v>
+      </c>
+      <c r="B60" t="s">
+        <v>242</v>
+      </c>
+      <c r="C60" t="s">
+        <v>243</v>
+      </c>
+      <c r="D60" t="s">
+        <v>50</v>
+      </c>
+      <c r="E60">
         <v>3</v>
       </c>
-      <c r="F48" t="s">
-        <v>226</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="15" t="s">
+      <c r="F60" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A61" s="15">
+        <v>3</v>
+      </c>
+      <c r="B61" s="15" t="s">
+        <v>244</v>
+      </c>
+      <c r="C61" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D61" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E61" s="15">
+        <v>9.2</v>
+      </c>
+      <c r="F61" s="15" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A62">
+        <v>4</v>
+      </c>
+      <c r="B62" t="s">
+        <v>246</v>
+      </c>
+      <c r="C62" t="s">
+        <v>247</v>
+      </c>
+      <c r="D62" t="s">
+        <v>50</v>
+      </c>
+      <c r="E62">
+        <v>4.7</v>
+      </c>
+      <c r="F62" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="15">
+        <v>5</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>249</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>247</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E63" s="15">
+        <v>1.9</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>148</v>
+      </c>
+      <c r="B64" t="s">
+        <v>164</v>
+      </c>
+      <c r="C64" t="s">
+        <v>31</v>
+      </c>
+      <c r="D64" t="s">
+        <v>31</v>
+      </c>
+      <c r="E64">
+        <v>29.8</v>
+      </c>
+      <c r="F64" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="14" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" s="14"/>
+      <c r="C66" s="14"/>
+      <c r="D66" s="14"/>
+      <c r="E66" s="14"/>
+      <c r="F66" s="14"/>
+    </row>
+    <row r="67" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>145</v>
+      </c>
+      <c r="D67" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E67" s="4" t="s">
+        <v>146</v>
+      </c>
+      <c r="F67" s="4" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>148</v>
+      </c>
+      <c r="B68" t="s">
         <v>149</v>
       </c>
-      <c r="B49" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C49" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D49" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E49" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="F49" s="15" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="51" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B51" s="14"/>
-      <c r="C51" s="14"/>
-      <c r="D51" s="14"/>
-      <c r="E51" s="14"/>
-      <c r="F51" s="14"/>
-    </row>
-    <row r="52" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D52" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E52" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F52" s="4" t="s">
+      <c r="C68" t="s">
+        <v>237</v>
+      </c>
+      <c r="D68" t="s">
+        <v>31</v>
+      </c>
+      <c r="E68" t="s">
+        <v>31</v>
+      </c>
+      <c r="F68" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69" s="15">
+        <v>1</v>
+      </c>
+      <c r="B69" s="15" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" s="15" t="s">
+        <v>253</v>
+      </c>
+      <c r="D69" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69" s="15">
+        <v>17</v>
+      </c>
+      <c r="F69" s="15" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70">
+        <v>2</v>
+      </c>
+      <c r="B70" t="s">
+        <v>82</v>
+      </c>
+      <c r="C70" t="s">
+        <v>237</v>
+      </c>
+      <c r="D70" t="s">
+        <v>50</v>
+      </c>
+      <c r="E70">
+        <v>15.2</v>
+      </c>
+      <c r="F70" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71" s="15">
+        <v>3</v>
+      </c>
+      <c r="B71" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="D71" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E71" s="15">
+        <v>7.7</v>
+      </c>
+      <c r="F71" s="15" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72">
+        <v>4</v>
+      </c>
+      <c r="B72" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" t="s">
+        <v>255</v>
+      </c>
+      <c r="D72" t="s">
+        <v>50</v>
+      </c>
+      <c r="E72">
+        <v>7.6</v>
+      </c>
+      <c r="F72" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" s="15" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" t="s">
-        <v>149</v>
-      </c>
-      <c r="B53" t="s">
-        <v>150</v>
-      </c>
-      <c r="C53" t="s">
-        <v>235</v>
-      </c>
-      <c r="D53" t="s">
-        <v>31</v>
-      </c>
-      <c r="E53" t="s">
-        <v>31</v>
-      </c>
-      <c r="F53" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" s="15">
-        <v>1</v>
-      </c>
-      <c r="B54" s="15" t="s">
-        <v>89</v>
-      </c>
-      <c r="C54" s="15" t="s">
-        <v>236</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54" s="15">
-        <v>14.8</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55">
-        <v>2</v>
-      </c>
-      <c r="B55" t="s">
-        <v>256</v>
-      </c>
-      <c r="C55" t="s">
-        <v>257</v>
-      </c>
-      <c r="D55" t="s">
-        <v>50</v>
-      </c>
-      <c r="E55">
-        <v>15.1</v>
-      </c>
-      <c r="F55" t="s">
-        <v>266</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="15">
-        <v>3</v>
-      </c>
-      <c r="B56" s="15" t="s">
-        <v>267</v>
-      </c>
-      <c r="C56" s="15" t="s">
-        <v>257</v>
-      </c>
-      <c r="D56" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E56" s="15">
-        <v>0.9</v>
-      </c>
-      <c r="F56" s="15" t="s">
-        <v>268</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57">
-        <v>4</v>
-      </c>
-      <c r="B57" t="s">
-        <v>245</v>
-      </c>
-      <c r="C57" t="s">
-        <v>242</v>
-      </c>
-      <c r="D57" t="s">
-        <v>50</v>
-      </c>
-      <c r="E57">
-        <v>15</v>
-      </c>
-      <c r="F57" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" s="15">
-        <v>5</v>
-      </c>
-      <c r="B58" s="15" t="s">
-        <v>239</v>
-      </c>
-      <c r="C58" s="15" t="s">
-        <v>240</v>
-      </c>
-      <c r="D58" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E58" s="15">
-        <v>9.2</v>
-      </c>
-      <c r="F58" s="15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A59">
-        <v>6</v>
-      </c>
-      <c r="B59" t="s">
-        <v>237</v>
-      </c>
-      <c r="C59" t="s">
-        <v>238</v>
-      </c>
-      <c r="D59" t="s">
-        <v>50</v>
-      </c>
-      <c r="E59">
-        <v>4.7</v>
-      </c>
-      <c r="F59" t="s">
-        <v>243</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A60" s="15">
-        <v>7</v>
-      </c>
-      <c r="B60" s="15" t="s">
-        <v>258</v>
-      </c>
-      <c r="C60" s="15" t="s">
-        <v>238</v>
-      </c>
-      <c r="D60" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E60" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="F60" s="15" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A61" t="s">
-        <v>149</v>
-      </c>
-      <c r="B61" t="s">
-        <v>166</v>
-      </c>
-      <c r="C61" t="s">
-        <v>31</v>
-      </c>
-      <c r="D61" t="s">
-        <v>31</v>
-      </c>
-      <c r="E61">
-        <v>29.8</v>
-      </c>
-      <c r="F61" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="63" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="14" t="s">
-        <v>269</v>
-      </c>
-      <c r="B63" s="14"/>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
-    </row>
-    <row r="64" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="D64" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E64" s="4" t="s">
-        <v>147</v>
-      </c>
-      <c r="F64" s="4" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A65" t="s">
-        <v>149</v>
-      </c>
-      <c r="B65" t="s">
-        <v>150</v>
-      </c>
-      <c r="C65" t="s">
-        <v>235</v>
-      </c>
-      <c r="D65" t="s">
-        <v>31</v>
-      </c>
-      <c r="E65" t="s">
-        <v>31</v>
-      </c>
-      <c r="F65" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="15">
-        <v>1</v>
-      </c>
-      <c r="B66" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C66" s="15" t="s">
-        <v>235</v>
-      </c>
-      <c r="D66" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E66" s="15">
-        <v>3.1</v>
-      </c>
-      <c r="F66" s="15" t="s">
-        <v>205</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67">
-        <v>2</v>
-      </c>
-      <c r="B67" t="s">
-        <v>83</v>
-      </c>
-      <c r="C67" t="s">
-        <v>248</v>
-      </c>
-      <c r="D67" t="s">
-        <v>50</v>
-      </c>
-      <c r="E67">
-        <v>14.9</v>
-      </c>
-      <c r="F67" t="s">
-        <v>249</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" s="15">
-        <v>3</v>
-      </c>
-      <c r="B68" s="15" t="s">
-        <v>251</v>
-      </c>
-      <c r="C68" s="15" t="s">
-        <v>248</v>
-      </c>
-      <c r="D68" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E68" s="15">
-        <v>12.3</v>
-      </c>
-      <c r="F68" s="15" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69">
-        <v>4</v>
-      </c>
-      <c r="B69" t="s">
-        <v>82</v>
-      </c>
-      <c r="C69" t="s">
-        <v>235</v>
-      </c>
-      <c r="D69" t="s">
-        <v>50</v>
-      </c>
-      <c r="E69">
-        <v>15.1</v>
-      </c>
-      <c r="F69" t="s">
-        <v>216</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70" s="15">
-        <v>5</v>
-      </c>
-      <c r="B70" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C70" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="D70" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E70" s="15">
-        <v>7.6</v>
-      </c>
-      <c r="F70" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71">
-        <v>6</v>
-      </c>
-      <c r="B71" t="s">
-        <v>84</v>
-      </c>
-      <c r="C71" t="s">
-        <v>252</v>
-      </c>
-      <c r="D71" t="s">
-        <v>58</v>
-      </c>
-      <c r="E71">
-        <v>3.6</v>
-      </c>
-      <c r="F71" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72" s="15">
-        <v>7</v>
-      </c>
-      <c r="B72" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="C72" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="D72" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E72" s="15">
-        <v>4.4</v>
-      </c>
-      <c r="F72" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73">
-        <v>8</v>
-      </c>
-      <c r="B73" t="s">
-        <v>75</v>
-      </c>
-      <c r="C73" t="s">
-        <v>235</v>
-      </c>
-      <c r="D73" t="s">
-        <v>58</v>
-      </c>
-      <c r="E73">
-        <v>8.9</v>
-      </c>
-      <c r="F73" t="s">
-        <v>154</v>
-      </c>
-    </row>
-    <row r="74" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A74" s="15" t="s">
-        <v>149</v>
-      </c>
-      <c r="B74" s="15" t="s">
-        <v>166</v>
-      </c>
-      <c r="C74" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D74" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E74" s="15">
-        <v>2.5</v>
-      </c>
-      <c r="F74" s="15" t="s">
-        <v>159</v>
+      <c r="B73" s="15" t="s">
+        <v>164</v>
+      </c>
+      <c r="C73" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73" s="15">
+        <v>12.8</v>
+      </c>
+      <c r="F73" s="15" t="s">
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -7073,10 +7081,10 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A28:F28"/>
-    <mergeCell ref="A38:F38"/>
-    <mergeCell ref="A51:F51"/>
-    <mergeCell ref="A63:F63"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A42:F42"/>
+    <mergeCell ref="A56:F56"/>
+    <mergeCell ref="A66:F66"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -7102,7 +7110,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7122,121 +7130,121 @@
         <v>45</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G3" s="4" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="H3" s="4" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="I3" s="4" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="J3" s="4" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D4" t="s">
-        <v>240</v>
+        <v>245</v>
       </c>
       <c r="E4" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="F4" t="s">
         <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H4" t="s">
         <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J4" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>253</v>
-      </c>
-      <c r="B5" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" t="s">
-        <v>284</v>
-      </c>
-      <c r="D5" t="s">
-        <v>252</v>
-      </c>
-      <c r="E5" t="s">
+      <c r="A5" s="11" t="s">
+        <v>79</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>50</v>
+      </c>
+      <c r="C5" s="11" t="s">
+        <v>286</v>
+      </c>
+      <c r="D5" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="E5" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="F5" s="11" t="s">
+        <v>80</v>
+      </c>
+      <c r="G5" s="11" t="s">
         <v>285</v>
       </c>
-      <c r="F5" t="s">
-        <v>80</v>
-      </c>
-      <c r="G5" t="s">
-        <v>283</v>
-      </c>
-      <c r="H5" t="s">
-        <v>80</v>
-      </c>
-      <c r="I5" t="s">
-        <v>282</v>
-      </c>
-      <c r="J5" t="s">
+      <c r="H5" s="11" t="s">
+        <v>78</v>
+      </c>
+      <c r="I5" s="11" t="s">
+        <v>288</v>
+      </c>
+      <c r="J5" s="11" t="s">
         <v>76</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="B6" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>76</v>
@@ -7244,31 +7252,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D7" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E7" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="F7" t="s">
         <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H7" t="s">
         <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J7" t="s">
         <v>76</v>
@@ -7282,57 +7290,57 @@
         <v>50</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="B9" t="s">
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D9" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E9" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F9" t="s">
         <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H9" t="s">
         <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J9" t="s">
         <v>51</v>
@@ -7340,31 +7348,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="E10" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="F10" t="s">
         <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H10" t="s">
         <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J10" t="s">
         <v>51</v>
@@ -7372,31 +7380,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D11" t="s">
-        <v>197</v>
+        <v>218</v>
       </c>
       <c r="E11" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="F11" t="s">
         <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H11" t="s">
         <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J11" t="s">
         <v>51</v>
@@ -7404,31 +7412,31 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B12" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>76</v>
@@ -7436,31 +7444,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>209</v>
+        <v>195</v>
       </c>
       <c r="B13" t="s">
         <v>50</v>
       </c>
       <c r="C13" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D13" t="s">
-        <v>210</v>
+        <v>196</v>
       </c>
       <c r="E13" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="F13" t="s">
         <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H13" t="s">
         <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J13" t="s">
         <v>51</v>
@@ -7474,28 +7482,28 @@
         <v>50</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D14" s="9" t="s">
         <v>173</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -7506,57 +7514,57 @@
         <v>50</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D15" s="9" t="s">
         <v>171</v>
       </c>
       <c r="E15" s="9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>256</v>
+        <v>239</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D16" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E16" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
       <c r="F16" t="s">
         <v>78</v>
       </c>
       <c r="G16" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="H16" t="s">
         <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="J16" t="s">
         <v>76</v>
@@ -7564,31 +7572,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D17" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="E17" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="F17" t="s">
         <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H17" t="s">
         <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J17" t="s">
         <v>76</v>
@@ -7602,28 +7610,28 @@
         <v>50</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7634,57 +7642,57 @@
         <v>50</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A20" s="11" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="B20" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>76</v>
@@ -7692,31 +7700,31 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>201</v>
+        <v>212</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D21" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E21" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="F21" t="s">
         <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H21" t="s">
         <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J21" t="s">
         <v>51</v>
@@ -7724,31 +7732,31 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>156</v>
+      </c>
+      <c r="B22" t="s">
+        <v>50</v>
+      </c>
+      <c r="C22" t="s">
+        <v>313</v>
+      </c>
+      <c r="D22" t="s">
         <v>157</v>
       </c>
-      <c r="B22" t="s">
-        <v>50</v>
-      </c>
-      <c r="C22" t="s">
-        <v>311</v>
-      </c>
-      <c r="D22" t="s">
-        <v>158</v>
-      </c>
       <c r="E22" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H22" t="s">
         <v>80</v>
       </c>
       <c r="I22" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J22" t="s">
         <v>52</v>
@@ -7756,31 +7764,31 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B23" t="s">
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D23" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E23" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="F23" t="s">
         <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H23" t="s">
         <v>80</v>
       </c>
       <c r="I23" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J23" t="s">
         <v>52</v>
@@ -7788,31 +7796,31 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B24" t="s">
         <v>50</v>
       </c>
       <c r="C24" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D24" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E24" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="F24" t="s">
         <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H24" t="s">
         <v>80</v>
       </c>
       <c r="I24" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J24" t="s">
         <v>52</v>
@@ -7820,31 +7828,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
+        <v>151</v>
+      </c>
+      <c r="B25" t="s">
+        <v>50</v>
+      </c>
+      <c r="C25" t="s">
+        <v>313</v>
+      </c>
+      <c r="D25" t="s">
         <v>152</v>
       </c>
-      <c r="B25" t="s">
-        <v>50</v>
-      </c>
-      <c r="C25" t="s">
-        <v>311</v>
-      </c>
-      <c r="D25" t="s">
-        <v>153</v>
-      </c>
       <c r="E25" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="F25" t="s">
         <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H25" t="s">
         <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
@@ -7852,31 +7860,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>203</v>
+        <v>215</v>
       </c>
       <c r="B26" t="s">
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D26" t="s">
-        <v>204</v>
+        <v>216</v>
       </c>
       <c r="E26" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F26" t="s">
         <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H26" t="s">
         <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="J26" t="s">
         <v>51</v>
@@ -7890,57 +7898,57 @@
         <v>50</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>212</v>
+        <v>198</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D28" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E28" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="F28" t="s">
         <v>78</v>
       </c>
       <c r="G28" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="H28" t="s">
         <v>78</v>
       </c>
       <c r="I28" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="J28" t="s">
         <v>76</v>
@@ -7948,31 +7956,31 @@
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B29" s="11" t="s">
         <v>50</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>76</v>
@@ -7986,57 +7994,57 @@
         <v>50</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="B31" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>76</v>
@@ -8044,31 +8052,31 @@
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A32" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B32" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>52</v>
@@ -8082,25 +8090,25 @@
         <v>58</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>328</v>
+        <v>288</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>76</v>
@@ -8114,28 +8122,28 @@
         <v>58</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -8146,57 +8154,57 @@
         <v>58</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>188</v>
+        <v>169</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>215</v>
+        <v>225</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>304</v>
+        <v>324</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>51</v>
@@ -8204,31 +8212,31 @@
     </row>
     <row r="37" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B37" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>160</v>
+        <v>179</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>52</v>
@@ -8236,31 +8244,31 @@
     </row>
     <row r="38" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A38" s="11" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="B38" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>52</v>
@@ -8268,31 +8276,31 @@
     </row>
     <row r="39" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A39" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B39" s="11" t="s">
         <v>58</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>319</v>
+        <v>307</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>76</v>
@@ -8306,57 +8314,57 @@
         <v>58</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>320</v>
+        <v>288</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D41" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="E41" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="F41" t="s">
         <v>78</v>
       </c>
       <c r="G41" t="s">
-        <v>304</v>
+        <v>288</v>
       </c>
       <c r="H41" t="s">
         <v>78</v>
       </c>
       <c r="I41" t="s">
-        <v>305</v>
+        <v>321</v>
       </c>
       <c r="J41" t="s">
         <v>76</v>
@@ -8364,31 +8372,31 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>241</v>
+        <v>263</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D42" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E42" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="F42" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G42" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H42" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I42" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="J42" t="s">
         <v>76</v>
@@ -8402,57 +8410,57 @@
         <v>62</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G43" s="9" t="s">
         <v>343</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="B44" t="s">
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D44" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="E44" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="F44" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G44" t="s">
+        <v>347</v>
+      </c>
+      <c r="H44" t="s">
         <v>341</v>
       </c>
-      <c r="H44" t="s">
-        <v>339</v>
-      </c>
       <c r="I44" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="J44" t="s">
         <v>51</v>
@@ -8460,31 +8468,31 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>264</v>
+        <v>259</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D45" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E45" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="F45" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G45" t="s">
         <v>343</v>
       </c>
       <c r="H45" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I45" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J45" t="s">
         <v>76</v>
@@ -8498,57 +8506,57 @@
         <v>62</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="D47" t="s">
-        <v>257</v>
+        <v>240</v>
       </c>
       <c r="E47" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="F47" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G47" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="H47" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I47" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="J47" t="s">
         <v>76</v>
@@ -8556,31 +8564,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>244</v>
+        <v>268</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="D48" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="E48" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="F48" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G48" t="s">
+        <v>345</v>
+      </c>
+      <c r="H48" t="s">
+        <v>341</v>
+      </c>
+      <c r="I48" t="s">
         <v>348</v>
-      </c>
-      <c r="H48" t="s">
-        <v>339</v>
-      </c>
-      <c r="I48" t="s">
-        <v>341</v>
       </c>
       <c r="J48" t="s">
         <v>76</v>
@@ -8588,31 +8596,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="B49" t="s">
         <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D49" t="s">
-        <v>202</v>
+        <v>213</v>
       </c>
       <c r="E49" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="F49" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G49" t="s">
+        <v>347</v>
+      </c>
+      <c r="H49" t="s">
         <v>341</v>
       </c>
-      <c r="H49" t="s">
-        <v>339</v>
-      </c>
       <c r="I49" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="J49" t="s">
         <v>51</v>
@@ -8620,31 +8628,31 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>190</v>
+        <v>159</v>
       </c>
       <c r="B50" t="s">
         <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="D50" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="E50" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="F50" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G50" t="s">
-        <v>344</v>
+        <v>351</v>
       </c>
       <c r="H50" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I50" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="J50" t="s">
         <v>52</v>
@@ -8652,31 +8660,31 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>250</v>
+        <v>266</v>
       </c>
       <c r="B51" t="s">
         <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D51" t="s">
-        <v>248</v>
+        <v>253</v>
       </c>
       <c r="E51" t="s">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="F51" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G51" t="s">
+        <v>347</v>
+      </c>
+      <c r="H51" t="s">
         <v>341</v>
       </c>
-      <c r="H51" t="s">
-        <v>339</v>
-      </c>
       <c r="I51" t="s">
-        <v>340</v>
+        <v>345</v>
       </c>
       <c r="J51" t="s">
         <v>76</v>
@@ -8684,31 +8692,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>261</v>
+        <v>256</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D52" t="s">
-        <v>262</v>
+        <v>257</v>
       </c>
       <c r="E52" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="F52" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G52" t="s">
         <v>343</v>
       </c>
       <c r="H52" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I52" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J52" t="s">
         <v>76</v>
@@ -8722,57 +8730,57 @@
         <v>62</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>213</v>
+        <v>199</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G53" s="9" t="s">
+        <v>347</v>
+      </c>
+      <c r="H53" s="9" t="s">
         <v>341</v>
       </c>
-      <c r="H53" s="9" t="s">
-        <v>339</v>
-      </c>
       <c r="I53" s="9" t="s">
-        <v>348</v>
+        <v>343</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="D54" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="E54" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="F54" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G54" t="s">
         <v>343</v>
       </c>
       <c r="H54" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I54" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="J54" t="s">
         <v>76</v>
@@ -8786,57 +8794,57 @@
         <v>62</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>214</v>
+        <v>201</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>340</v>
+        <v>347</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>219</v>
+        <v>206</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="D56" t="s">
-        <v>220</v>
+        <v>207</v>
       </c>
       <c r="E56" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="F56" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="G56" t="s">
         <v>343</v>
       </c>
       <c r="H56" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="I56" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J56" t="s">
         <v>51</v>
@@ -8844,7 +8852,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -8878,7 +8886,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8886,7 +8894,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8897,13 +8905,13 @@
         <v>9</v>
       </c>
       <c r="B4" s="4" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C4" s="4" t="s">
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -8911,13 +8919,13 @@
         <v>52</v>
       </c>
       <c r="B5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C5">
         <v>6</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -8925,13 +8933,13 @@
         <v>52</v>
       </c>
       <c r="B6" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C6">
         <v>6</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -8939,13 +8947,13 @@
         <v>52</v>
       </c>
       <c r="B7" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C7">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -8953,13 +8961,13 @@
         <v>52</v>
       </c>
       <c r="B8" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C8">
         <v>6</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -8967,13 +8975,13 @@
         <v>52</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -8981,13 +8989,13 @@
         <v>52</v>
       </c>
       <c r="B10" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C10">
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -8995,13 +9003,13 @@
         <v>51</v>
       </c>
       <c r="B12" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C12">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9009,13 +9017,13 @@
         <v>51</v>
       </c>
       <c r="B13" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C13">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9023,13 +9031,13 @@
         <v>51</v>
       </c>
       <c r="B14" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C14">
         <v>7</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9037,13 +9045,13 @@
         <v>51</v>
       </c>
       <c r="B15" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C15">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9051,13 +9059,13 @@
         <v>51</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9065,13 +9073,13 @@
         <v>51</v>
       </c>
       <c r="B17" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C17">
         <v>6</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -9079,13 +9087,13 @@
         <v>76</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C19">
         <v>6</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9093,13 +9101,13 @@
         <v>76</v>
       </c>
       <c r="B20" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C20">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9107,13 +9115,13 @@
         <v>76</v>
       </c>
       <c r="B21" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9121,13 +9129,13 @@
         <v>76</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C22">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9135,13 +9143,13 @@
         <v>76</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C23">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9149,13 +9157,13 @@
         <v>76</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C24">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
   </sheetData>

--- a/Estudo-Rotas-RJ-Eficiencia.xlsx
+++ b/Estudo-Rotas-RJ-Eficiencia.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1724" uniqueCount="381">
   <si>
     <t>ESTUDO 2 — EFICIÊNCIA MÁXIMA · ROTAS RJ (Cleide · Lucas · Anderson)</t>
   </si>
@@ -94,7 +94,7 @@
     <t>Lucas — PROPOSTA</t>
   </si>
   <si>
-    <t>15h59</t>
+    <t>15h32</t>
   </si>
   <si>
     <t>Anderson — HOJE</t>
@@ -106,7 +106,7 @@
     <t>Anderson — PROPOSTA</t>
   </si>
   <si>
-    <t>14h26</t>
+    <t>14h28</t>
   </si>
   <si>
     <t>TOTAL (3 promotores)</t>
@@ -121,7 +121,7 @@
     <t>130 → 114</t>
   </si>
   <si>
-    <t>1524 → 1407 km</t>
+    <t>1524 → 1399 km</t>
   </si>
   <si>
     <t>10 → 8 (1 dia)</t>
@@ -130,7 +130,7 @@
     <t>O QUE MUDA (resumo executivo)</t>
   </si>
   <si>
-    <t>• TODO MUNDO roda menos: Cleide 434 → 379 km (-56), Anderson 509 → 475 (-35), Lucas 581 → 554 (-27). Total -117 km/sem (-7%).</t>
+    <t>• TODO MUNDO roda menos: Cleide 434 → 379 km (-56), Anderson 509 → 476 (-33), Lucas 581 → 544 (-37). Total -125 km/sem (-7%).</t>
   </si>
   <si>
     <t>• Cleide (ônibus): seg/qua/sex viram loops LOCAIS de Nova Iguaçu/Mesquita/Nilópolis (37-42 km); ter/qui/sáb = corredor Meriti→Caxias (ônibus direto Via Light/Dutra). Nunca mais de 6 lojas/dia. Adeus Tijuca.</t>
@@ -328,51 +328,51 @@
     <t>→</t>
   </si>
   <si>
+    <t>2h11</t>
+  </si>
+  <si>
+    <t>Terça</t>
+  </si>
+  <si>
+    <t>1h29</t>
+  </si>
+  <si>
     <t>1h31</t>
   </si>
   <si>
-    <t>Terça</t>
-  </si>
-  <si>
-    <t>1h29</t>
+    <t>Quarta</t>
+  </si>
+  <si>
+    <t>2h06</t>
   </si>
   <si>
     <t>2h19</t>
   </si>
   <si>
-    <t>Quarta</t>
-  </si>
-  <si>
-    <t>2h06</t>
+    <t>Quinta</t>
+  </si>
+  <si>
+    <t>1h17</t>
+  </si>
+  <si>
+    <t>Sexta</t>
+  </si>
+  <si>
+    <t>2h02</t>
+  </si>
+  <si>
+    <t>1h55</t>
+  </si>
+  <si>
+    <t>Sábado</t>
+  </si>
+  <si>
+    <t>1h53</t>
   </si>
   <si>
     <t>1h33</t>
   </si>
   <si>
-    <t>Quinta</t>
-  </si>
-  <si>
-    <t>1h55</t>
-  </si>
-  <si>
-    <t>Sexta</t>
-  </si>
-  <si>
-    <t>2h02</t>
-  </si>
-  <si>
-    <t>1h17</t>
-  </si>
-  <si>
-    <t>Sábado</t>
-  </si>
-  <si>
-    <t>1h53</t>
-  </si>
-  <si>
-    <t>2h11</t>
-  </si>
-  <si>
     <t>SEMANA</t>
   </si>
   <si>
@@ -385,67 +385,61 @@
     <t>2h47</t>
   </si>
   <si>
-    <t>2h18</t>
+    <t>2h17</t>
   </si>
   <si>
     <t>2h38</t>
   </si>
   <si>
-    <t>2h50</t>
+    <t>2h42</t>
   </si>
   <si>
     <t>2h40</t>
   </si>
   <si>
-    <t>2h41</t>
+    <t>2h28</t>
   </si>
   <si>
     <t>2h36</t>
   </si>
   <si>
-    <t>2h52</t>
-  </si>
-  <si>
-    <t>2h31</t>
+    <t>2h46</t>
+  </si>
+  <si>
+    <t>2h35</t>
   </si>
   <si>
     <t>Anderson (Moto)</t>
   </si>
   <si>
-    <t>2h35</t>
-  </si>
-  <si>
-    <t>2h46</t>
-  </si>
-  <si>
-    <t>1h57</t>
+    <t>2h39</t>
+  </si>
+  <si>
+    <t>1h52</t>
   </si>
   <si>
     <t>1h41</t>
   </si>
   <si>
-    <t>2h45</t>
-  </si>
-  <si>
     <t>2h53</t>
   </si>
   <si>
     <t>2h26</t>
   </si>
   <si>
-    <t>2h39</t>
-  </si>
-  <si>
     <t>3h07</t>
   </si>
   <si>
+    <t>1h54</t>
+  </si>
+  <si>
     <t>Cleide de Oliveira Lira — ROTA PROPOSTA (Ônibus)</t>
   </si>
   <si>
     <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (carro, referência — ela roda de ônibus)</t>
   </si>
   <si>
-    <t>SEGUNDA — 6 lojas · 41.1 km · 1h31</t>
+    <t>SEGUNDA — 6 lojas · 98.8 km · 2h11</t>
   </si>
   <si>
     <t>#</t>
@@ -472,6 +466,45 @@
     <t>Rosa dos Ventos</t>
   </si>
   <si>
+    <t>Centro</t>
+  </si>
+  <si>
+    <t>22 min</t>
+  </si>
+  <si>
+    <t>Vila Meriti</t>
+  </si>
+  <si>
+    <t>13 min</t>
+  </si>
+  <si>
+    <t>Vila São Luis</t>
+  </si>
+  <si>
+    <t>11 min</t>
+  </si>
+  <si>
+    <t>Santa Cruz da Serra</t>
+  </si>
+  <si>
+    <t>18 min</t>
+  </si>
+  <si>
+    <t>São Bento</t>
+  </si>
+  <si>
+    <t>Vila Centenario</t>
+  </si>
+  <si>
+    <t>CASA (volta)</t>
+  </si>
+  <si>
+    <t>35 min</t>
+  </si>
+  <si>
+    <t>TERÇA — 5 lojas · 41.1 km · 1h31</t>
+  </si>
+  <si>
     <t>ASSAÍ NOVA IGUAÇU VIA LIGHT - 291 - RJ</t>
   </si>
   <si>
@@ -496,103 +529,67 @@
     <t>7 min</t>
   </si>
   <si>
+    <t>ASSAÍ NILÓPOLIS - 36 - RJ</t>
+  </si>
+  <si>
+    <t>17 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ NOVA IGUAÇU - 30 - RJ</t>
+  </si>
+  <si>
+    <t>19 min</t>
+  </si>
+  <si>
+    <t>QUARTA — 6 lojas · 91 km · 2h19</t>
+  </si>
+  <si>
+    <t>Piam</t>
+  </si>
+  <si>
+    <t>25 min</t>
+  </si>
+  <si>
+    <t>41 min</t>
+  </si>
+  <si>
+    <t>Venda Velha</t>
+  </si>
+  <si>
+    <t>2 min</t>
+  </si>
+  <si>
+    <t>24 min</t>
+  </si>
+  <si>
+    <t>QUINTA — 6 lojas · 36.9 km · 1h17</t>
+  </si>
+  <si>
+    <t>6 min</t>
+  </si>
+  <si>
+    <t>Bairro Industrial</t>
+  </si>
+  <si>
+    <t>1 min</t>
+  </si>
+  <si>
     <t>PREZUNIC NILÓPOLIS</t>
   </si>
   <si>
-    <t>Centro</t>
-  </si>
-  <si>
-    <t>ASSAÍ NILÓPOLIS - 36 - RJ</t>
-  </si>
-  <si>
-    <t>1 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ NOVA IGUAÇU - 30 - RJ</t>
-  </si>
-  <si>
-    <t>CASA (volta)</t>
-  </si>
-  <si>
-    <t>19 min</t>
-  </si>
-  <si>
-    <t>TERÇA — 6 lojas · 91 km · 2h19</t>
-  </si>
-  <si>
-    <t>Piam</t>
-  </si>
-  <si>
-    <t>25 min</t>
-  </si>
-  <si>
-    <t>Santa Cruz da Serra</t>
-  </si>
-  <si>
-    <t>41 min</t>
-  </si>
-  <si>
-    <t>São Bento</t>
-  </si>
-  <si>
-    <t>22 min</t>
-  </si>
-  <si>
-    <t>Vila Centenario</t>
-  </si>
-  <si>
-    <t>11 min</t>
-  </si>
-  <si>
-    <t>Venda Velha</t>
-  </si>
-  <si>
-    <t>2 min</t>
-  </si>
-  <si>
-    <t>24 min</t>
-  </si>
-  <si>
-    <t>QUARTA — 6 lojas · 41.3 km · 1h33</t>
-  </si>
-  <si>
-    <t>Bairro Industrial</t>
-  </si>
-  <si>
-    <t>18 min</t>
-  </si>
-  <si>
-    <t>QUINTA — 6 lojas · 69.4 km · 1h55</t>
+    <t>29 min</t>
+  </si>
+  <si>
+    <t>SEXTA — 6 lojas · 69.4 km · 1h55</t>
   </si>
   <si>
     <t>23 min</t>
   </si>
   <si>
-    <t>Vila São Luis</t>
-  </si>
-  <si>
     <t>14 min</t>
   </si>
   <si>
-    <t>13 min</t>
-  </si>
-  <si>
-    <t>SEXTA — 5 lojas · 36.9 km · 1h17</t>
-  </si>
-  <si>
-    <t>6 min</t>
-  </si>
-  <si>
-    <t>29 min</t>
-  </si>
-  <si>
-    <t>SÁBADO — 6 lojas · 98.8 km · 2h11</t>
-  </si>
-  <si>
-    <t>Vila Meriti</t>
-  </si>
-  <si>
-    <t>35 min</t>
+    <t>SÁBADO — 6 lojas · 41.3 km · 1h33</t>
   </si>
   <si>
     <t>Lucas Braz Monassa Vidal de Negreiros — ROTA PROPOSTA (Moto)</t>
@@ -601,7 +598,7 @@
     <t>Saída: R. Berlim, 171 - Rosa dos Ventos, Nova Iguaçu - RJ, 26278-610 · km/tempo por trecho = Google (moto)</t>
   </si>
   <si>
-    <t>SEGUNDA — 7 lojas · 98.6 km · 2h47</t>
+    <t>SEGUNDA — 7 lojas · 96.1 km · 2h44</t>
   </si>
   <si>
     <t>ASSAÍ CORDOVIL - 231 - RJ</t>
@@ -622,115 +619,166 @@
     <t>10 min</t>
   </si>
   <si>
+    <t>4 min</t>
+  </si>
+  <si>
     <t>Vila Isabel</t>
   </si>
   <si>
+    <t>8 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ CARIOCA - 316 - RJ</t>
+  </si>
+  <si>
+    <t>Vila da Penha</t>
+  </si>
+  <si>
+    <t>28 min</t>
+  </si>
+  <si>
+    <t>45 min</t>
+  </si>
+  <si>
+    <t>TERÇA — 6 lojas · 80.6 km · 2h17</t>
+  </si>
+  <si>
+    <t>PREZUNIC VISTA ALEGRE</t>
+  </si>
+  <si>
+    <t>Vista Alegre</t>
+  </si>
+  <si>
+    <t>36 min</t>
+  </si>
+  <si>
     <t>ASSAÍ CAMPINHO - 37 - RJ</t>
   </si>
   <si>
     <t>Campinho</t>
   </si>
   <si>
+    <t>PREZUNIC MÉIER</t>
+  </si>
+  <si>
+    <t>Méier</t>
+  </si>
+  <si>
+    <t>ASSAÍ MEIER - 160 - RJ</t>
+  </si>
+  <si>
+    <t>ASSAÍ PILARES - 128 - RJ</t>
+  </si>
+  <si>
+    <t>Pilares</t>
+  </si>
+  <si>
+    <t>ASSAÍ CEASA - 42 - RJ</t>
+  </si>
+  <si>
+    <t>Irajá</t>
+  </si>
+  <si>
+    <t>37 min</t>
+  </si>
+  <si>
+    <t>QUARTA — 7 lojas · 95.2 km · 2h42</t>
+  </si>
+  <si>
+    <t>QUINTA — 5 lojas · 87.1 km · 2h28</t>
+  </si>
+  <si>
+    <t>Inhaúma</t>
+  </si>
+  <si>
+    <t>12 min</t>
+  </si>
+  <si>
     <t>51 min</t>
   </si>
   <si>
-    <t>TERÇA — 5 lojas · 83.3 km · 2h18</t>
-  </si>
-  <si>
-    <t>PREZUNIC VISTA ALEGRE</t>
-  </si>
-  <si>
-    <t>Vista Alegre</t>
-  </si>
-  <si>
-    <t>36 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ CARIOCA - 316 - RJ</t>
-  </si>
-  <si>
-    <t>Vila da Penha</t>
-  </si>
-  <si>
-    <t>8 min</t>
-  </si>
-  <si>
-    <t>ASSAÍ MEIER - 160 - RJ</t>
-  </si>
-  <si>
-    <t>Méier</t>
+    <t>SEXTA — 7 lojas · 95.9 km · 2h46</t>
+  </si>
+  <si>
+    <t>Benfica</t>
+  </si>
+  <si>
+    <t>SÁBADO — 6 lojas · 89.2 km · 2h35</t>
+  </si>
+  <si>
+    <t>PREZUNIC CAMPINHO</t>
+  </si>
+  <si>
+    <t>Anderson Camilo Supeleto — ROTA PROPOSTA (Moto)</t>
+  </si>
+  <si>
+    <t>Saída: Est. do Pré, 674 - Campo Grande, Rio de Janeiro - RJ, 23013-550 · km/tempo por trecho = Google (moto)</t>
+  </si>
+  <si>
+    <t>SEGUNDA — 5 lojas · 92.9 km · 2h39</t>
+  </si>
+  <si>
+    <t>Campo Grande</t>
+  </si>
+  <si>
+    <t>PREZUNIC JARDIM OCEÂNICO</t>
+  </si>
+  <si>
+    <t>Barra da Tijuca</t>
+  </si>
+  <si>
+    <t>68 min</t>
+  </si>
+  <si>
+    <t>ASSAÍ BARRA DA TIJUCA - 245 - RJ</t>
+  </si>
+  <si>
+    <t>ASSAÍ AYRTON SENNA - 133 - RJ</t>
+  </si>
+  <si>
+    <t>Jacarepaguá</t>
+  </si>
+  <si>
+    <t>ASSAÍ JACAREPAGUÁ MERCADÃO - 340 - RJ</t>
+  </si>
+  <si>
+    <t>Taquara</t>
+  </si>
+  <si>
+    <t>DOM TAQUARA</t>
+  </si>
+  <si>
+    <t>TERÇA — 9 lojas · 61.4 km · 1h52</t>
+  </si>
+  <si>
+    <t>ASSAÍ SANTA CRUZ - 201 - RJ</t>
+  </si>
+  <si>
+    <t>Santa Cruz</t>
   </si>
   <si>
     <t>27 min</t>
   </si>
   <si>
-    <t>ASSAÍ PILARES - 128 - RJ</t>
-  </si>
-  <si>
-    <t>Pilares</t>
-  </si>
-  <si>
-    <t>ASSAÍ CEASA - 42 - RJ</t>
-  </si>
-  <si>
-    <t>Irajá</t>
-  </si>
-  <si>
     <t>20 min</t>
   </si>
   <si>
-    <t>37 min</t>
-  </si>
-  <si>
-    <t>QUARTA — 7 lojas · 99.6 km · 2h50</t>
-  </si>
-  <si>
-    <t>4 min</t>
-  </si>
-  <si>
-    <t>28 min</t>
-  </si>
-  <si>
-    <t>QUINTA — 6 lojas · 90.1 km · 2h41</t>
-  </si>
-  <si>
-    <t>Inhaúma</t>
-  </si>
-  <si>
-    <t>Benfica</t>
-  </si>
-  <si>
-    <t>45 min</t>
-  </si>
-  <si>
-    <t>SEXTA — 7 lojas · 95.6 km · 2h52</t>
-  </si>
-  <si>
-    <t>PREZUNIC CAMPINHO</t>
-  </si>
-  <si>
-    <t>58 min</t>
-  </si>
-  <si>
-    <t>SÁBADO — 6 lojas · 86.7 km · 2h31</t>
-  </si>
-  <si>
-    <t>PREZUNIC MÉIER</t>
-  </si>
-  <si>
-    <t>17 min</t>
-  </si>
-  <si>
-    <t>Anderson Camilo Supeleto — ROTA PROPOSTA (Moto)</t>
-  </si>
-  <si>
-    <t>Saída: Est. do Pré, 674 - Campo Grande, Rio de Janeiro - RJ, 23013-550 · km/tempo por trecho = Google (moto)</t>
-  </si>
-  <si>
-    <t>SEGUNDA — 6 lojas · 91.4 km · 2h52</t>
-  </si>
-  <si>
-    <t>Campo Grande</t>
+    <t>Bangu</t>
+  </si>
+  <si>
+    <t>PREZUNIC SENADOR CAMARÁ</t>
+  </si>
+  <si>
+    <t>Senador Camará</t>
+  </si>
+  <si>
+    <t>9 min</t>
+  </si>
+  <si>
+    <t>PREZUNIC CAMPO GRANDE</t>
+  </si>
+  <si>
+    <t>QUARTA — 7 lojas · 91.5 km · 2h53</t>
   </si>
   <si>
     <t>Realengo</t>
@@ -745,61 +793,25 @@
     <t>33 min</t>
   </si>
   <si>
-    <t>ASSAÍ BARRA DA TIJUCA - 245 - RJ</t>
-  </si>
-  <si>
-    <t>Barra da Tijuca</t>
-  </si>
-  <si>
-    <t>ASSAÍ AYRTON SENNA - 133 - RJ</t>
-  </si>
-  <si>
-    <t>Jacarepaguá</t>
-  </si>
-  <si>
-    <t>ASSAÍ JACAREPAGUÁ MERCADÃO - 340 - RJ</t>
-  </si>
-  <si>
-    <t>Taquara</t>
-  </si>
-  <si>
-    <t>12 min</t>
-  </si>
-  <si>
-    <t>DOM TAQUARA</t>
-  </si>
-  <si>
-    <t>TERÇA — 10 lojas · 62.8 km · 1h57</t>
+    <t>PREZUNIC BARRA MARAPENDI</t>
+  </si>
+  <si>
+    <t>QUINTA — 9 lojas · 73.8 km · 2h26</t>
+  </si>
+  <si>
+    <t>5 min</t>
   </si>
   <si>
     <t>PREZUNIC TINGUÍ</t>
   </si>
   <si>
-    <t>ASSAÍ SANTA CRUZ - 201 - RJ</t>
-  </si>
-  <si>
-    <t>Santa Cruz</t>
-  </si>
-  <si>
     <t>21 min</t>
   </si>
   <si>
-    <t>Bangu</t>
-  </si>
-  <si>
-    <t>PREZUNIC SENADOR CAMARÁ</t>
-  </si>
-  <si>
-    <t>Senador Camará</t>
-  </si>
-  <si>
-    <t>9 min</t>
-  </si>
-  <si>
-    <t>PREZUNIC CAMPO GRANDE</t>
-  </si>
-  <si>
-    <t>QUARTA — 7 lojas · 93.9 km · 2h45</t>
+    <t>32 min</t>
+  </si>
+  <si>
+    <t>SEXTA — 6 lojas · 93.9 km · 2h44</t>
   </si>
   <si>
     <t>PREZUNIC FREGUESIA</t>
@@ -808,36 +820,15 @@
     <t>3 min</t>
   </si>
   <si>
-    <t>PREZUNIC BARRA MARAPENDI</t>
-  </si>
-  <si>
     <t>63 min</t>
   </si>
   <si>
-    <t>QUINTA — 9 lojas · 73.2 km · 2h18</t>
+    <t>SÁBADO — 5 lojas · 62.5 km · 1h54</t>
   </si>
   <si>
     <t>PREZUNIC SANTA CRUZ</t>
   </si>
   <si>
-    <t>SEXTA — 5 lojas · 92.9 km · 2h39</t>
-  </si>
-  <si>
-    <t>PREZUNIC JARDIM OCEÂNICO</t>
-  </si>
-  <si>
-    <t>68 min</t>
-  </si>
-  <si>
-    <t>SÁBADO — 4 lojas · 60.4 km · 1h55</t>
-  </si>
-  <si>
-    <t>34 min</t>
-  </si>
-  <si>
-    <t>32 min</t>
-  </si>
-  <si>
     <t>TODAS AS LOJAS — DE/PARA (promotor, frequência e dias)</t>
   </si>
   <si>
@@ -940,96 +931,96 @@
     <t>Estr. de Jacarepaguá, 7753 - Freguesia (Jacarepaguá), Rio de Janeiro - RJ, 22755-158</t>
   </si>
   <si>
+    <t>Qua/Sex</t>
+  </si>
+  <si>
+    <t>Estr. dos Bandeirantes, 1430 - Taquara, Rio de Janeiro - RJ, 22710-310</t>
+  </si>
+  <si>
+    <t>Av. Maracanã, 1188 - Tijuca, Rio de Janeiro - RJ, 20511-001</t>
+  </si>
+  <si>
+    <t>R. Mariz e Barros, 975 - Tijuca, Rio de Janeiro - RJ, 20270-004</t>
+  </si>
+  <si>
+    <t>Estr. do Mendanha, 3457 - Campo Grande, Rio de Janeiro - RJ, 23092-001</t>
+  </si>
+  <si>
+    <t>R. Dias da Cruz, 371 - Méier, Rio de Janeiro - RJ, 20720-010</t>
+  </si>
+  <si>
+    <t>BAIXADA</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 10521 - Jacutinga, Mesquita - RJ, 26574-751</t>
+  </si>
+  <si>
+    <t>Av. Getúlio de Moura, 1983 - Centro, Nilópolis - RJ, 26525-002</t>
+  </si>
+  <si>
+    <t>Av. Mal. Floriano Peixoto, 1448 - Centro, Nova Iguaçu - RJ, 26220-060</t>
+  </si>
+  <si>
+    <t>Av. Tancredo Neves, 3424 - Santa Eugenia, Nova Iguaçu - RJ, 26285-002</t>
+  </si>
+  <si>
+    <t>Av. Dom Hélder Câmara, 6350 - Pilares, Rio de Janeiro - RJ, 20771-001</t>
+  </si>
+  <si>
+    <t>Av. Brasil, 2251 - Vasco da Gama, Rio de Janeiro - RJ, 20930-041</t>
+  </si>
+  <si>
+    <t>Av. Padre Guilherme Decaminada, 2385 - Santa Cruz, Rio de Janeiro - RJ, 23575-000</t>
+  </si>
+  <si>
+    <t>Seg/Sex</t>
+  </si>
+  <si>
+    <t>Estr. da Pedra, 2.500 - Santa Cruz, Rio de Janeiro - RJ, 23520-241</t>
+  </si>
+  <si>
+    <t>Seg/Sex/Sáb</t>
+  </si>
+  <si>
+    <t>Qui/Sáb</t>
+  </si>
+  <si>
+    <t>MERITI</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 4301 - Centro, São João de Meriti - RJ, 25515-230</t>
+  </si>
+  <si>
+    <t>Av. Brasil, 32238 - Bangu, Rio de Janeiro - RJ, 21863-000</t>
+  </si>
+  <si>
+    <t>Av. Joaquim da Costa Lima, 2009 - Piam, Belford Roxo - RJ, 26183-000</t>
+  </si>
+  <si>
+    <t>Av. de Santa Cruz, Avenue, 12,516 - Campo Grande, Rio de Janeiro - RJ, 23010-002</t>
+  </si>
+  <si>
+    <t>Rod. Washington Luiz, 3853 - Vila São Luis, Duque de Caxias - RJ, 25065-135</t>
+  </si>
+  <si>
+    <t>Avenida Automóvel Clube QUADRA37L - LOTE 489 - Santa Cruz da Serra, Duque de Caxias - RJ, 25267-135</t>
+  </si>
+  <si>
     <t>Seg/Qua</t>
   </si>
   <si>
-    <t>Estr. dos Bandeirantes, 1430 - Taquara, Rio de Janeiro - RJ, 22710-310</t>
-  </si>
-  <si>
-    <t>Av. Maracanã, 1188 - Tijuca, Rio de Janeiro - RJ, 20511-001</t>
-  </si>
-  <si>
-    <t>R. Mariz e Barros, 975 - Tijuca, Rio de Janeiro - RJ, 20270-004</t>
-  </si>
-  <si>
-    <t>Estr. do Mendanha, 3457 - Campo Grande, Rio de Janeiro - RJ, 23092-001</t>
-  </si>
-  <si>
-    <t>R. Dias da Cruz, 371 - Méier, Rio de Janeiro - RJ, 20720-010</t>
-  </si>
-  <si>
-    <t>BAIXADA</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 10521 - Jacutinga, Mesquita - RJ, 26574-751</t>
-  </si>
-  <si>
-    <t>Av. Getúlio de Moura, 1983 - Centro, Nilópolis - RJ, 26525-002</t>
-  </si>
-  <si>
-    <t>Av. Mal. Floriano Peixoto, 1448 - Centro, Nova Iguaçu - RJ, 26220-060</t>
-  </si>
-  <si>
-    <t>Av. Tancredo Neves, 3424 - Santa Eugenia, Nova Iguaçu - RJ, 26285-002</t>
-  </si>
-  <si>
-    <t>Av. Dom Hélder Câmara, 6350 - Pilares, Rio de Janeiro - RJ, 20771-001</t>
-  </si>
-  <si>
-    <t>Av. Brasil, 2251 - Vasco da Gama, Rio de Janeiro - RJ, 20930-041</t>
-  </si>
-  <si>
-    <t>Av. Padre Guilherme Decaminada, 2385 - Santa Cruz, Rio de Janeiro - RJ, 23575-000</t>
-  </si>
-  <si>
-    <t>Seg/Sex</t>
-  </si>
-  <si>
-    <t>Estr. da Pedra, 2.500 - Santa Cruz, Rio de Janeiro - RJ, 23520-241</t>
-  </si>
-  <si>
-    <t>Seg/Sex/Sáb</t>
-  </si>
-  <si>
-    <t>Qui/Sáb</t>
-  </si>
-  <si>
-    <t>MERITI</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 4301 - Centro, São João de Meriti - RJ, 25515-230</t>
-  </si>
-  <si>
-    <t>Av. Brasil, 32238 - Bangu, Rio de Janeiro - RJ, 21863-000</t>
-  </si>
-  <si>
-    <t>Av. Joaquim da Costa Lima, 2009 - Piam, Belford Roxo - RJ, 26183-000</t>
-  </si>
-  <si>
-    <t>Av. de Santa Cruz, Avenue, 12,516 - Campo Grande, Rio de Janeiro - RJ, 23010-002</t>
-  </si>
-  <si>
-    <t>Rod. Washington Luiz, 3853 - Vila São Luis, Duque de Caxias - RJ, 25065-135</t>
-  </si>
-  <si>
-    <t>Avenida Automóvel Clube QUADRA37L - LOTE 489 - Santa Cruz da Serra, Duque de Caxias - RJ, 25267-135</t>
+    <t>Av. Itaóca, 2650 - Inhaúma, Rio de Janeiro - RJ, 21061-770</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 10201B - Bairro Industrial, Mesquita - RJ, 26574-751</t>
+  </si>
+  <si>
+    <t>Rod. Pres. Dutra, 13900 - Jardim Tropical, Nova Iguaçu - RJ, 26015-005</t>
   </si>
   <si>
     <t>Ter/Sáb</t>
   </si>
   <si>
-    <t>Av. Itaóca, 2650 - Inhaúma, Rio de Janeiro - RJ, 21061-770</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 10201B - Bairro Industrial, Mesquita - RJ, 26574-751</t>
-  </si>
-  <si>
-    <t>Qua/Sex</t>
-  </si>
-  <si>
-    <t>Rod. Pres. Dutra, 13900 - Jardim Tropical, Nova Iguaçu - RJ, 26015-005</t>
-  </si>
-  <si>
     <t>Estr. Gen. Canrobert Pereira da Costa, 203 - Realengo, Rio de Janeiro - RJ, 21710-400</t>
   </si>
   <si>
@@ -1054,30 +1045,30 @@
     <t>Av. Dom Hélder Câmara, 105 - Benfica, Rio de Janeiro - RJ, 20911-291</t>
   </si>
   <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>R. Cândido Benício, 20 - Campinho, Rio de Janeiro - RJ, 21320-060</t>
+  </si>
+  <si>
+    <t>Seg</t>
+  </si>
+  <si>
+    <t>Sáb</t>
+  </si>
+  <si>
+    <t>Est. do Cabuçu, 1654 - Campo Grande, Rio de Janeiro - RJ, 23052-230</t>
+  </si>
+  <si>
+    <t>R. Dr. Manoel Reis, 175 - Vila Meriti, Duque de Caxias - RJ, 25025-010</t>
+  </si>
+  <si>
+    <t>Estr. de Jacarepaguá, 7153 - Freguesia (Jacarepaguá), Rio de Janeiro - RJ, 22753-033</t>
+  </si>
+  <si>
     <t>Qui</t>
   </si>
   <si>
-    <t>R. Cândido Benício, 20 - Campinho, Rio de Janeiro - RJ, 21320-060</t>
-  </si>
-  <si>
-    <t>Seg</t>
-  </si>
-  <si>
-    <t>Sex</t>
-  </si>
-  <si>
-    <t>Est. do Cabuçu, 1654 - Campo Grande, Rio de Janeiro - RJ, 23052-230</t>
-  </si>
-  <si>
-    <t>R. Dr. Manoel Reis, 175 - Vila Meriti, Duque de Caxias - RJ, 25025-010</t>
-  </si>
-  <si>
-    <t>Sáb</t>
-  </si>
-  <si>
-    <t>Estr. de Jacarepaguá, 7153 - Freguesia (Jacarepaguá), Rio de Janeiro - RJ, 22753-033</t>
-  </si>
-  <si>
     <t>Av. Rodolfo Amoedo, 347 - Barra da Tijuca, Rio de Janeiro - RJ, 22620-350</t>
   </si>
   <si>
@@ -1117,58 +1108,58 @@
     <t>Link (Casa → paradas → Casa)</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.807575,-43.416172%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.799075,-43.357408%7C-22.780278,-43.310000%7C-22.781013,-43.286252%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.775841,-43.308631&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
   </si>
   <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.747852,-43.392257%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.775841,-43.308631%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
   </si>
   <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.761935,-43.445172%7C-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.807575,-43.416172%7C-22.804718,-43.418825&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.747852,-43.392257%7C-22.726211,-43.313020%7C-22.781013,-43.286252%7C-22.775841,-43.308631%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
+  </si>
+  <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.754258,-43.433102%7C-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.804718,-43.418825%7C-22.761935,-43.445172&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.747852,-43.392257%7C-22.726211,-43.313020%7C-22.781013,-43.286252%7C-22.775841,-43.308631%7C-22.798746,-43.354000%7C-22.799075,-43.357408&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.754058,-43.463158%7C-22.761935,-43.445172%7C-22.769066,-43.410775%7C-22.773459,-43.404854%7C-22.804718,-43.418825&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.799075,-43.357408%7C-22.780278,-43.310000%7C-22.781013,-43.286252%7C-22.641768,-43.277839%7C-22.726211,-43.313020%7C-22.775841,-43.308631&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.914747,-43.241269%7C-22.881347,-43.342096&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.834535,-43.318511%7C-22.849155,-43.311358%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.827684,-43.338882&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.930622,-43.242526%7C-22.919957,-43.244485%7C-22.881347,-43.342096&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.871506,-43.277717%7C-22.892195,-43.241108%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.881347,-43.342096%7C-22.883440,-43.343393&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.871506,-43.277717%7C-22.905431,-43.291154%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.849155,-43.311358&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.941113,-43.343251%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.884020,-43.575133%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.882288,-43.488152%7C-22.893845,-43.534011%7C-22.913861,-43.544483&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.935560,-43.372767%7C-22.959146,-43.356197%7C-22.941113,-43.343251%7C-22.945679,-43.340096%7C-23.000610,-43.356417%7C-23.001891,-43.323279&amp;travelmode=driving</t>
-  </si>
-  <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.915624,-43.682502%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.893845,-43.534011&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.930622,-43.242526%7C-22.919957,-43.244485%7C-22.849155,-43.311358&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.834535,-43.318511%7C-22.881347,-43.342096%7C-22.905431,-43.291154%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.827684,-43.338882&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.914747,-43.241269%7C-22.849155,-43.311358&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.881347,-43.342096%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.871506,-43.277717&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.818676,-43.288131%7C-22.886476,-43.228562%7C-22.892195,-43.241108%7C-22.918390,-43.222149%7C-22.926863,-43.238707%7C-22.919957,-43.244485%7C-22.849155,-43.311358&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.753177,-43.511537&amp;destination=-22.753177,-43.511537&amp;waypoints=-22.827684,-43.338882%7C-22.881347,-43.342096%7C-22.883440,-43.343393%7C-22.904671,-43.286274%7C-22.882973,-43.290316%7C-22.871506,-43.277717&amp;travelmode=driving</t>
   </si>
   <si>
     <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-23.008411,-43.316903%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
   </si>
   <si>
-    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.950972,-43.652551%7C-22.906919,-43.564898%7C-22.863251,-43.549364%7C-22.856798,-43.477684&amp;travelmode=driving</t>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.891011,-43.676538%7C-22.863251,-43.549364%7C-22.856798,-43.477684%7C-22.858758,-43.460071%7C-22.879019,-43.465396%7C-22.882288,-43.488152%7C-22.893845,-43.534011%7C-22.913861,-43.544483&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.941113,-43.343251%7C-23.000610,-43.356417%7C-23.001891,-43.323279%7C-22.959146,-43.356197%7C-22.935560,-43.372767%7C-22.924799,-43.373430&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.893845,-43.534011%7C-22.879019,-43.465396%7C-22.858758,-43.460071%7C-22.856798,-43.477684%7C-22.863251,-43.549364%7C-22.884020,-43.575133%7C-22.891011,-43.676538%7C-22.950972,-43.652551%7C-22.906919,-43.564898&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.877465,-43.422793%7C-22.935560,-43.372767%7C-22.959146,-43.356197%7C-22.941113,-43.343251%7C-22.945679,-43.340096%7C-23.001891,-43.323279&amp;travelmode=driving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/dir/?api=1&amp;origin=-22.911329,-43.545822&amp;destination=-22.911329,-43.545822&amp;waypoints=-22.906919,-43.564898%7C-22.950972,-43.652551%7C-22.915624,-43.682502%7C-22.863251,-43.549364%7C-22.856798,-43.477684&amp;travelmode=driving</t>
   </si>
 </sst>
 </file>
@@ -1852,7 +1843,7 @@
         <v>38</v>
       </c>
       <c r="E16" s="6">
-        <v>553.9</v>
+        <v>544.1</v>
       </c>
       <c r="F16" s="6" t="s">
         <v>25</v>
@@ -1898,13 +1889,13 @@
         <v>41</v>
       </c>
       <c r="E18" s="6">
-        <v>474.6</v>
+        <v>476</v>
       </c>
       <c r="F18" s="6" t="s">
         <v>29</v>
       </c>
       <c r="G18" s="6">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.25">
@@ -2793,7 +2784,7 @@
         <v>6</v>
       </c>
       <c r="G5">
-        <v>41.1</v>
+        <v>98.8</v>
       </c>
       <c r="H5" t="s">
         <v>103</v>
@@ -2816,10 +2807,10 @@
         <v>102</v>
       </c>
       <c r="F6" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G6">
-        <v>91</v>
+        <v>41.1</v>
       </c>
       <c r="H6" t="s">
         <v>106</v>
@@ -2845,7 +2836,7 @@
         <v>6</v>
       </c>
       <c r="G7">
-        <v>41.3</v>
+        <v>91</v>
       </c>
       <c r="H7" t="s">
         <v>109</v>
@@ -2871,7 +2862,7 @@
         <v>6</v>
       </c>
       <c r="G8">
-        <v>69.4</v>
+        <v>36.9</v>
       </c>
       <c r="H8" t="s">
         <v>111</v>
@@ -2894,10 +2885,10 @@
         <v>102</v>
       </c>
       <c r="F9" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G9">
-        <v>36.9</v>
+        <v>69.4</v>
       </c>
       <c r="H9" t="s">
         <v>114</v>
@@ -2923,7 +2914,7 @@
         <v>6</v>
       </c>
       <c r="G10">
-        <v>98.8</v>
+        <v>41.3</v>
       </c>
       <c r="H10" t="s">
         <v>117</v>
@@ -3013,10 +3004,10 @@
         <v>7</v>
       </c>
       <c r="G15">
-        <v>98.6</v>
+        <v>96.1</v>
       </c>
       <c r="H15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.25">
@@ -3036,10 +3027,10 @@
         <v>102</v>
       </c>
       <c r="F16" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G16">
-        <v>83.3</v>
+        <v>80.6</v>
       </c>
       <c r="H16" t="s">
         <v>122</v>
@@ -3065,7 +3056,7 @@
         <v>7</v>
       </c>
       <c r="G17">
-        <v>99.6</v>
+        <v>95.2</v>
       </c>
       <c r="H17" t="s">
         <v>124</v>
@@ -3088,10 +3079,10 @@
         <v>102</v>
       </c>
       <c r="F18" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G18">
-        <v>90.1</v>
+        <v>87.1</v>
       </c>
       <c r="H18" t="s">
         <v>126</v>
@@ -3117,7 +3108,7 @@
         <v>7</v>
       </c>
       <c r="G19">
-        <v>95.6</v>
+        <v>95.9</v>
       </c>
       <c r="H19" t="s">
         <v>128</v>
@@ -3143,7 +3134,7 @@
         <v>6</v>
       </c>
       <c r="G20">
-        <v>86.7</v>
+        <v>89.2</v>
       </c>
       <c r="H20" t="s">
         <v>129</v>
@@ -3169,7 +3160,7 @@
         <v>38</v>
       </c>
       <c r="G21" s="13">
-        <v>553.9</v>
+        <v>544.1</v>
       </c>
       <c r="H21" s="13" t="s">
         <v>25</v>
@@ -3224,19 +3215,19 @@
         <v>79.6</v>
       </c>
       <c r="D25" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="E25" t="s">
         <v>102</v>
       </c>
       <c r="F25" s="11">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G25">
-        <v>91.4</v>
+        <v>92.9</v>
       </c>
       <c r="H25" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.25">
@@ -3250,19 +3241,19 @@
         <v>95.1</v>
       </c>
       <c r="D26" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E26" t="s">
         <v>102</v>
       </c>
       <c r="F26" s="11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G26">
-        <v>62.8</v>
+        <v>61.4</v>
       </c>
       <c r="H26" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -3276,7 +3267,7 @@
         <v>48</v>
       </c>
       <c r="D27" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E27" t="s">
         <v>102</v>
@@ -3285,10 +3276,10 @@
         <v>7</v>
       </c>
       <c r="G27">
-        <v>93.9</v>
+        <v>91.5</v>
       </c>
       <c r="H27" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -3302,7 +3293,7 @@
         <v>98.4</v>
       </c>
       <c r="D28" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E28" t="s">
         <v>102</v>
@@ -3311,10 +3302,10 @@
         <v>9</v>
       </c>
       <c r="G28">
-        <v>73.2</v>
+        <v>73.8</v>
       </c>
       <c r="H28" t="s">
-        <v>122</v>
+        <v>135</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
@@ -3328,19 +3319,19 @@
         <v>77.4</v>
       </c>
       <c r="D29" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E29" t="s">
         <v>102</v>
       </c>
       <c r="F29" s="11">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G29">
-        <v>92.9</v>
+        <v>93.9</v>
       </c>
       <c r="H29" t="s">
-        <v>138</v>
+        <v>120</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -3354,19 +3345,19 @@
         <v>110.6</v>
       </c>
       <c r="D30" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="E30" t="s">
         <v>102</v>
       </c>
       <c r="F30" s="11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G30">
-        <v>60.4</v>
+        <v>62.5</v>
       </c>
       <c r="H30" t="s">
-        <v>111</v>
+        <v>137</v>
       </c>
     </row>
     <row r="31" spans="1:8" x14ac:dyDescent="0.25">
@@ -3389,7 +3380,7 @@
         <v>41</v>
       </c>
       <c r="G31" s="13">
-        <v>474.6</v>
+        <v>476</v>
       </c>
       <c r="H31" s="13" t="s">
         <v>29</v>
@@ -3421,7 +3412,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -3431,7 +3422,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -3441,7 +3432,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -3451,33 +3442,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" t="s">
         <v>148</v>
-      </c>
-      <c r="B6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" t="s">
-        <v>150</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -3494,19 +3485,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>151</v>
+        <v>55</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E7" s="15">
-        <v>7.9</v>
+        <v>19.5</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -3514,19 +3505,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>89</v>
+        <v>61</v>
       </c>
       <c r="C8" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="D8" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E8">
-        <v>5.5</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -3534,19 +3525,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>156</v>
+        <v>57</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E9" s="15">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -3554,19 +3545,19 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>159</v>
+        <v>59</v>
       </c>
       <c r="C10" t="s">
-        <v>160</v>
+        <v>155</v>
       </c>
       <c r="D10" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E10">
-        <v>8.2</v>
+        <v>17.9</v>
       </c>
       <c r="F10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -3574,19 +3565,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>161</v>
+        <v>54</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="D11" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E11" s="15">
-        <v>0.4</v>
+        <v>14.5</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>162</v>
+        <v>150</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -3594,27 +3585,27 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>163</v>
+        <v>49</v>
       </c>
       <c r="C12" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="D12" t="s">
         <v>50</v>
       </c>
       <c r="E12">
-        <v>7.1</v>
+        <v>6.3</v>
       </c>
       <c r="F12" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>31</v>
@@ -3623,15 +3614,15 @@
         <v>31</v>
       </c>
       <c r="E13" s="15">
-        <v>8.5</v>
+        <v>27</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="14" t="s">
-        <v>166</v>
+        <v>161</v>
       </c>
       <c r="B15" s="14"/>
       <c r="C15" s="14"/>
@@ -3641,33 +3632,33 @@
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C16" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D16" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
+        <v>146</v>
+      </c>
+      <c r="B17" t="s">
+        <v>147</v>
+      </c>
+      <c r="C17" t="s">
         <v>148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" t="s">
-        <v>150</v>
       </c>
       <c r="D17" t="s">
         <v>31</v>
@@ -3684,19 +3675,19 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>86</v>
+        <v>162</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E18" s="15">
-        <v>16.3</v>
+        <v>7.9</v>
       </c>
       <c r="F18" s="15" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -3704,19 +3695,19 @@
         <v>2</v>
       </c>
       <c r="B19" t="s">
-        <v>59</v>
+        <v>89</v>
       </c>
       <c r="C19" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="D19" t="s">
         <v>58</v>
       </c>
       <c r="E19">
-        <v>24.8</v>
+        <v>5.5</v>
       </c>
       <c r="F19" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -3724,19 +3715,19 @@
         <v>3</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>54</v>
+        <v>167</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="D20" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E20" s="15">
-        <v>14.5</v>
+        <v>3.5</v>
       </c>
       <c r="F20" s="15" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -3744,19 +3735,19 @@
         <v>4</v>
       </c>
       <c r="B21" t="s">
-        <v>49</v>
+        <v>170</v>
       </c>
       <c r="C21" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D21" t="s">
         <v>50</v>
       </c>
       <c r="E21">
-        <v>6.3</v>
+        <v>8.6</v>
       </c>
       <c r="F21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -3764,614 +3755,614 @@
         <v>5</v>
       </c>
       <c r="B22" s="15" t="s">
+        <v>172</v>
+      </c>
+      <c r="C22" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D22" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22" s="15">
+        <v>7.1</v>
+      </c>
+      <c r="F22" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>146</v>
+      </c>
+      <c r="B23" t="s">
+        <v>159</v>
+      </c>
+      <c r="C23" t="s">
+        <v>31</v>
+      </c>
+      <c r="D23" t="s">
+        <v>31</v>
+      </c>
+      <c r="E23">
+        <v>8.5</v>
+      </c>
+      <c r="F23" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="14" t="s">
+        <v>174</v>
+      </c>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
+      <c r="E25" s="14"/>
+      <c r="F25" s="14"/>
+    </row>
+    <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F26" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>146</v>
+      </c>
+      <c r="B27" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" t="s">
+        <v>31</v>
+      </c>
+      <c r="E27" t="s">
+        <v>31</v>
+      </c>
+      <c r="F27" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="15">
+        <v>1</v>
+      </c>
+      <c r="B28" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C28" s="15" t="s">
+        <v>175</v>
+      </c>
+      <c r="D28" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E28" s="15">
+        <v>16.3</v>
+      </c>
+      <c r="F28" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29">
+        <v>2</v>
+      </c>
+      <c r="B29" t="s">
+        <v>59</v>
+      </c>
+      <c r="C29" t="s">
+        <v>155</v>
+      </c>
+      <c r="D29" t="s">
+        <v>58</v>
+      </c>
+      <c r="E29">
+        <v>24.8</v>
+      </c>
+      <c r="F29" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
+        <v>3</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>157</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="15">
+        <v>14.5</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>4</v>
+      </c>
+      <c r="B31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>158</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31">
+        <v>6.3</v>
+      </c>
+      <c r="F31" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
+        <v>5</v>
+      </c>
+      <c r="B32" s="15" t="s">
         <v>60</v>
       </c>
-      <c r="C22" s="15" t="s">
+      <c r="C32" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E32" s="15">
+        <v>7.4</v>
+      </c>
+      <c r="F32" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>6</v>
+      </c>
+      <c r="B33" t="s">
+        <v>55</v>
+      </c>
+      <c r="C33" t="s">
+        <v>149</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33">
+        <v>0.9</v>
+      </c>
+      <c r="F33" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E34" s="15">
+        <v>20.9</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="36" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="B36" s="14"/>
+      <c r="C36" s="14"/>
+      <c r="D36" s="14"/>
+      <c r="E36" s="14"/>
+      <c r="F36" s="14"/>
+    </row>
+    <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B37" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E37" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F37" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>146</v>
+      </c>
+      <c r="B38" t="s">
+        <v>147</v>
+      </c>
+      <c r="C38" t="s">
+        <v>148</v>
+      </c>
+      <c r="D38" t="s">
+        <v>31</v>
+      </c>
+      <c r="E38" t="s">
+        <v>31</v>
+      </c>
+      <c r="F38" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="15">
+        <v>1</v>
+      </c>
+      <c r="B39" s="15" t="s">
+        <v>162</v>
+      </c>
+      <c r="C39" s="15" t="s">
+        <v>163</v>
+      </c>
+      <c r="D39" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E39" s="15">
+        <v>7.9</v>
+      </c>
+      <c r="F39" s="15" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40">
+        <v>2</v>
+      </c>
+      <c r="B40" t="s">
+        <v>172</v>
+      </c>
+      <c r="C40" t="s">
+        <v>149</v>
+      </c>
+      <c r="D40" t="s">
+        <v>50</v>
+      </c>
+      <c r="E40">
+        <v>2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="15">
+        <v>3</v>
+      </c>
+      <c r="B41" s="15" t="s">
+        <v>167</v>
+      </c>
+      <c r="C41" s="15" t="s">
+        <v>168</v>
+      </c>
+      <c r="D41" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E41" s="15">
+        <v>4.2</v>
+      </c>
+      <c r="F41" s="15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
+        <v>88</v>
+      </c>
+      <c r="C42" t="s">
+        <v>183</v>
+      </c>
+      <c r="D42" t="s">
+        <v>58</v>
+      </c>
+      <c r="E42">
+        <v>0.9</v>
+      </c>
+      <c r="F42" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15">
+        <v>5</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>149</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E43" s="15">
+        <v>7.6</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44">
+        <v>6</v>
+      </c>
+      <c r="B44" t="s">
+        <v>170</v>
+      </c>
+      <c r="C44" t="s">
+        <v>149</v>
+      </c>
+      <c r="D44" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44">
+        <v>0.4</v>
+      </c>
+      <c r="F44" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B45" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C45" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D45" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E45" s="15">
+        <v>14</v>
+      </c>
+      <c r="F45" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="47" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" s="14" t="s">
+        <v>187</v>
+      </c>
+      <c r="B47" s="14"/>
+      <c r="C47" s="14"/>
+      <c r="D47" s="14"/>
+      <c r="E47" s="14"/>
+      <c r="F47" s="14"/>
+    </row>
+    <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A48" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B48" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D48" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E48" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F48" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>146</v>
+      </c>
+      <c r="B49" t="s">
+        <v>147</v>
+      </c>
+      <c r="C49" t="s">
+        <v>148</v>
+      </c>
+      <c r="D49" t="s">
+        <v>31</v>
+      </c>
+      <c r="E49" t="s">
+        <v>31</v>
+      </c>
+      <c r="F49" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A50" s="15">
+        <v>1</v>
+      </c>
+      <c r="B50" s="15" t="s">
+        <v>86</v>
+      </c>
+      <c r="C50" s="15" t="s">
         <v>175</v>
       </c>
-      <c r="D22" s="15" t="s">
+      <c r="D50" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E22" s="15">
+      <c r="E50" s="15">
+        <v>16.3</v>
+      </c>
+      <c r="F50" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A51">
+        <v>2</v>
+      </c>
+      <c r="B51" t="s">
+        <v>54</v>
+      </c>
+      <c r="C51" t="s">
+        <v>157</v>
+      </c>
+      <c r="D51" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51">
+        <v>11.4</v>
+      </c>
+      <c r="F51" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" s="15">
+        <v>3</v>
+      </c>
+      <c r="B52" s="15" t="s">
+        <v>57</v>
+      </c>
+      <c r="C52" s="15" t="s">
+        <v>153</v>
+      </c>
+      <c r="D52" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E52" s="15">
+        <v>8.3</v>
+      </c>
+      <c r="F52" s="15" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A53">
+        <v>4</v>
+      </c>
+      <c r="B53" t="s">
+        <v>49</v>
+      </c>
+      <c r="C53" t="s">
+        <v>158</v>
+      </c>
+      <c r="D53" t="s">
+        <v>50</v>
+      </c>
+      <c r="E53">
+        <v>4.2</v>
+      </c>
+      <c r="F53" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="15">
+        <v>5</v>
+      </c>
+      <c r="B54" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="C54" s="15" t="s">
+        <v>178</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E54" s="15">
         <v>7.4</v>
       </c>
-      <c r="F22" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
+      <c r="F54" s="15" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55">
         <v>6</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B55" t="s">
         <v>55</v>
       </c>
-      <c r="C23" t="s">
-        <v>160</v>
-      </c>
-      <c r="D23" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23">
+      <c r="C55" t="s">
+        <v>149</v>
+      </c>
+      <c r="D55" t="s">
+        <v>50</v>
+      </c>
+      <c r="E55">
         <v>0.9</v>
       </c>
-      <c r="F23" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="15">
+      <c r="F55" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C56" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D56" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" s="15">
         <v>20.9</v>
       </c>
-      <c r="F24" s="15" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-    </row>
-    <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F27" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>148</v>
-      </c>
-      <c r="B28" t="s">
-        <v>149</v>
-      </c>
-      <c r="C28" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="15">
-        <v>1</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E29" s="15">
-        <v>7.9</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2</v>
-      </c>
-      <c r="B30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C30" t="s">
-        <v>154</v>
-      </c>
-      <c r="D30" t="s">
-        <v>58</v>
-      </c>
-      <c r="E30">
-        <v>5.5</v>
-      </c>
-      <c r="F30" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="15">
-        <v>3</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="15">
-        <v>3.5</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>88</v>
-      </c>
-      <c r="C32" t="s">
-        <v>179</v>
-      </c>
-      <c r="D32" t="s">
-        <v>58</v>
-      </c>
-      <c r="E32">
-        <v>0.9</v>
-      </c>
-      <c r="F32" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="15">
-        <v>5</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E33" s="15">
-        <v>8</v>
-      </c>
-      <c r="F33" s="15" t="s">
+      <c r="F56" s="15" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>6</v>
-      </c>
-      <c r="B34" t="s">
-        <v>163</v>
-      </c>
-      <c r="C34" t="s">
-        <v>160</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34">
-        <v>7.1</v>
-      </c>
-      <c r="F34" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E35" s="15">
-        <v>8.5</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="37" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A37" s="14" t="s">
-        <v>181</v>
-      </c>
-      <c r="B37" s="14"/>
-      <c r="C37" s="14"/>
-      <c r="D37" s="14"/>
-      <c r="E37" s="14"/>
-      <c r="F37" s="14"/>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D38" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E38" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F38" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" t="s">
-        <v>148</v>
-      </c>
-      <c r="B39" t="s">
-        <v>149</v>
-      </c>
-      <c r="C39" t="s">
-        <v>150</v>
-      </c>
-      <c r="D39" t="s">
-        <v>31</v>
-      </c>
-      <c r="E39" t="s">
-        <v>31</v>
-      </c>
-      <c r="F39" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" s="15">
-        <v>1</v>
-      </c>
-      <c r="B40" s="15" t="s">
-        <v>86</v>
-      </c>
-      <c r="C40" s="15" t="s">
-        <v>167</v>
-      </c>
-      <c r="D40" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E40" s="15">
-        <v>16.3</v>
-      </c>
-      <c r="F40" s="15" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41">
-        <v>2</v>
-      </c>
-      <c r="B41" t="s">
-        <v>54</v>
-      </c>
-      <c r="C41" t="s">
-        <v>171</v>
-      </c>
-      <c r="D41" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41">
-        <v>11.4</v>
-      </c>
-      <c r="F41" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="15">
-        <v>3</v>
-      </c>
-      <c r="B42" s="15" t="s">
-        <v>57</v>
-      </c>
-      <c r="C42" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="D42" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42" s="15">
-        <v>8.3</v>
-      </c>
-      <c r="F42" s="15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43">
-        <v>4</v>
-      </c>
-      <c r="B43" t="s">
-        <v>49</v>
-      </c>
-      <c r="C43" t="s">
-        <v>173</v>
-      </c>
-      <c r="D43" t="s">
-        <v>50</v>
-      </c>
-      <c r="E43">
-        <v>4.2</v>
-      </c>
-      <c r="F43" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" s="15">
-        <v>5</v>
-      </c>
-      <c r="B44" s="15" t="s">
-        <v>60</v>
-      </c>
-      <c r="C44" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="D44" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E44" s="15">
-        <v>7.4</v>
-      </c>
-      <c r="F44" s="15" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45">
-        <v>6</v>
-      </c>
-      <c r="B45" t="s">
-        <v>55</v>
-      </c>
-      <c r="C45" t="s">
-        <v>160</v>
-      </c>
-      <c r="D45" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45">
-        <v>0.9</v>
-      </c>
-      <c r="F45" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B46" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C46" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D46" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E46" s="15">
-        <v>20.9</v>
-      </c>
-      <c r="F46" s="15" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="48" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A48" s="14" t="s">
-        <v>186</v>
-      </c>
-      <c r="B48" s="14"/>
-      <c r="C48" s="14"/>
-      <c r="D48" s="14"/>
-      <c r="E48" s="14"/>
-      <c r="F48" s="14"/>
-    </row>
-    <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D49" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E49" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F49" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A50" t="s">
-        <v>148</v>
-      </c>
-      <c r="B50" t="s">
-        <v>149</v>
-      </c>
-      <c r="C50" t="s">
-        <v>150</v>
-      </c>
-      <c r="D50" t="s">
-        <v>31</v>
-      </c>
-      <c r="E50" t="s">
-        <v>31</v>
-      </c>
-      <c r="F50" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A51" s="15">
-        <v>1</v>
-      </c>
-      <c r="B51" s="15" t="s">
-        <v>151</v>
-      </c>
-      <c r="C51" s="15" t="s">
-        <v>152</v>
-      </c>
-      <c r="D51" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E51" s="15">
-        <v>7.9</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>2</v>
-      </c>
-      <c r="B52" t="s">
-        <v>163</v>
-      </c>
-      <c r="C52" t="s">
-        <v>160</v>
-      </c>
-      <c r="D52" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52">
-        <v>2</v>
-      </c>
-      <c r="F52" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="15">
-        <v>3</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>156</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>157</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E53" s="15">
-        <v>4.2</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54">
-        <v>4</v>
-      </c>
-      <c r="B54" t="s">
-        <v>88</v>
-      </c>
-      <c r="C54" t="s">
-        <v>179</v>
-      </c>
-      <c r="D54" t="s">
-        <v>58</v>
-      </c>
-      <c r="E54">
-        <v>0.9</v>
-      </c>
-      <c r="F54" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A55" s="15">
-        <v>5</v>
-      </c>
-      <c r="B55" s="15" t="s">
-        <v>161</v>
-      </c>
-      <c r="C55" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="D55" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E55" s="15">
-        <v>8</v>
-      </c>
-      <c r="F55" s="15" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" t="s">
-        <v>148</v>
-      </c>
-      <c r="B56" t="s">
-        <v>164</v>
-      </c>
-      <c r="C56" t="s">
-        <v>31</v>
-      </c>
-      <c r="D56" t="s">
-        <v>31</v>
-      </c>
-      <c r="E56">
-        <v>14</v>
-      </c>
-      <c r="F56" t="s">
-        <v>188</v>
       </c>
     </row>
     <row r="58" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A58" s="14" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="B58" s="14"/>
       <c r="C58" s="14"/>
@@ -4381,33 +4372,33 @@
     </row>
     <row r="59" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C59" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F59" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
+        <v>146</v>
+      </c>
+      <c r="B60" t="s">
+        <v>147</v>
+      </c>
+      <c r="C60" t="s">
         <v>148</v>
-      </c>
-      <c r="B60" t="s">
-        <v>149</v>
-      </c>
-      <c r="C60" t="s">
-        <v>150</v>
       </c>
       <c r="D60" t="s">
         <v>31</v>
@@ -4424,19 +4415,19 @@
         <v>1</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>55</v>
+        <v>162</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="D61" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E61" s="15">
-        <v>19.5</v>
+        <v>7.9</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
@@ -4444,19 +4435,19 @@
         <v>2</v>
       </c>
       <c r="B62" t="s">
-        <v>61</v>
+        <v>89</v>
       </c>
       <c r="C62" t="s">
-        <v>190</v>
+        <v>165</v>
       </c>
       <c r="D62" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E62">
-        <v>10</v>
+        <v>5.5</v>
       </c>
       <c r="F62" t="s">
-        <v>185</v>
+        <v>166</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
@@ -4464,19 +4455,19 @@
         <v>3</v>
       </c>
       <c r="B63" s="15" t="s">
-        <v>57</v>
+        <v>167</v>
       </c>
       <c r="C63" s="15" t="s">
-        <v>183</v>
+        <v>168</v>
       </c>
       <c r="D63" s="15" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E63" s="15">
-        <v>3.7</v>
+        <v>3.5</v>
       </c>
       <c r="F63" s="15" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.25">
@@ -4484,19 +4475,19 @@
         <v>4</v>
       </c>
       <c r="B64" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
       <c r="C64" t="s">
-        <v>169</v>
+        <v>183</v>
       </c>
       <c r="D64" t="s">
         <v>58</v>
       </c>
       <c r="E64">
-        <v>17.9</v>
+        <v>0.9</v>
       </c>
       <c r="F64" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.25">
@@ -4504,19 +4495,19 @@
         <v>5</v>
       </c>
       <c r="B65" s="15" t="s">
-        <v>54</v>
+        <v>170</v>
       </c>
       <c r="C65" s="15" t="s">
-        <v>171</v>
+        <v>149</v>
       </c>
       <c r="D65" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E65" s="15">
-        <v>14.5</v>
+        <v>8</v>
       </c>
       <c r="F65" s="15" t="s">
-        <v>172</v>
+        <v>156</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -4524,27 +4515,27 @@
         <v>6</v>
       </c>
       <c r="B66" t="s">
-        <v>49</v>
+        <v>172</v>
       </c>
       <c r="C66" t="s">
-        <v>173</v>
+        <v>149</v>
       </c>
       <c r="D66" t="s">
         <v>50</v>
       </c>
       <c r="E66">
-        <v>6.3</v>
+        <v>7.1</v>
       </c>
       <c r="F66" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A67" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B67" s="15" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C67" s="15" t="s">
         <v>31</v>
@@ -4553,10 +4544,10 @@
         <v>31</v>
       </c>
       <c r="E67" s="15">
-        <v>27</v>
+        <v>8.5</v>
       </c>
       <c r="F67" s="15" t="s">
-        <v>191</v>
+        <v>173</v>
       </c>
     </row>
   </sheetData>
@@ -4565,9 +4556,9 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A37:F37"/>
-    <mergeCell ref="A48:F48"/>
+    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A58:F58"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4589,7 +4580,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -4599,7 +4590,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -4609,7 +4600,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -4619,33 +4610,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>146</v>
+      </c>
+      <c r="B6" t="s">
+        <v>147</v>
+      </c>
+      <c r="C6" t="s">
         <v>148</v>
-      </c>
-      <c r="B6" t="s">
-        <v>149</v>
-      </c>
-      <c r="C6" t="s">
-        <v>150</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -4662,10 +4653,10 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C7" s="15" t="s">
         <v>195</v>
-      </c>
-      <c r="C7" s="15" t="s">
-        <v>196</v>
       </c>
       <c r="D7" s="15" t="s">
         <v>50</v>
@@ -4674,7 +4665,7 @@
         <v>28.4</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -4685,7 +4676,7 @@
         <v>67</v>
       </c>
       <c r="C8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
@@ -4694,7 +4685,7 @@
         <v>11.3</v>
       </c>
       <c r="F8" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -4705,7 +4696,7 @@
         <v>66</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>50</v>
@@ -4714,7 +4705,7 @@
         <v>6.9</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>153</v>
+        <v>164</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -4725,7 +4716,7 @@
         <v>65</v>
       </c>
       <c r="C10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
@@ -4734,7 +4725,7 @@
         <v>2.8</v>
       </c>
       <c r="F10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -4742,19 +4733,19 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>63</v>
+        <v>69</v>
       </c>
       <c r="C11" s="15" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D11" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E11" s="15">
-        <v>1.8</v>
+        <v>0.9</v>
       </c>
       <c r="F11" s="15" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -4762,19 +4753,19 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>63</v>
       </c>
       <c r="C12" t="s">
         <v>201</v>
       </c>
       <c r="D12" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E12">
-        <v>1.4</v>
+        <v>2.5</v>
       </c>
       <c r="F12" t="s">
-        <v>187</v>
+        <v>202</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -4782,27 +4773,27 @@
         <v>7</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="C13" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D13" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E13" s="15">
-        <v>12.6</v>
+        <v>13.9</v>
       </c>
       <c r="F13" s="15" t="s">
-        <v>168</v>
+        <v>205</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B14" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C14" t="s">
         <v>31</v>
@@ -4811,15 +4802,15 @@
         <v>31</v>
       </c>
       <c r="E14">
-        <v>33.4</v>
+        <v>29.4</v>
       </c>
       <c r="F14" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
     </row>
     <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="14" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="B16" s="14"/>
       <c r="C16" s="14"/>
@@ -4829,33 +4820,33 @@
     </row>
     <row r="17" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C17" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F17" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
+        <v>146</v>
+      </c>
+      <c r="B18" t="s">
+        <v>147</v>
+      </c>
+      <c r="C18" t="s">
         <v>148</v>
-      </c>
-      <c r="B18" t="s">
-        <v>149</v>
-      </c>
-      <c r="C18" t="s">
-        <v>150</v>
       </c>
       <c r="D18" t="s">
         <v>31</v>
@@ -4872,10 +4863,10 @@
         <v>1</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D19" s="15" t="s">
         <v>62</v>
@@ -4884,7 +4875,7 @@
         <v>25.5</v>
       </c>
       <c r="F19" s="15" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
@@ -4892,19 +4883,19 @@
         <v>2</v>
       </c>
       <c r="B20" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="C20" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D20" t="s">
         <v>50</v>
       </c>
       <c r="E20">
-        <v>2.6</v>
+        <v>6.8</v>
       </c>
       <c r="F20" t="s">
-        <v>211</v>
+        <v>171</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
@@ -4912,19 +4903,19 @@
         <v>3</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="C21" s="15" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E21" s="15">
-        <v>14.4</v>
+        <v>7.5</v>
       </c>
       <c r="F21" s="15" t="s">
-        <v>214</v>
+        <v>164</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -4935,16 +4926,16 @@
         <v>215</v>
       </c>
       <c r="C22" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D22" t="s">
         <v>50</v>
       </c>
       <c r="E22">
-        <v>3.3</v>
+        <v>0.5</v>
       </c>
       <c r="F22" t="s">
-        <v>200</v>
+        <v>179</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -4952,444 +4943,444 @@
         <v>5</v>
       </c>
       <c r="B23" s="15" t="s">
+        <v>216</v>
+      </c>
+      <c r="C23" s="15" t="s">
         <v>217</v>
       </c>
-      <c r="C23" s="15" t="s">
+      <c r="D23" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E23" s="15">
+        <v>3.2</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>6</v>
+      </c>
+      <c r="B24" t="s">
         <v>218</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E23" s="15">
-        <v>10.4</v>
-      </c>
-      <c r="F23" s="15" t="s">
+      <c r="C24" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" t="s">
+      <c r="D24" t="s">
+        <v>50</v>
+      </c>
+      <c r="E24">
+        <v>10.1</v>
+      </c>
+      <c r="F24" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E25" s="15">
+        <v>27</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A27" s="14" t="s">
+        <v>221</v>
+      </c>
+      <c r="B27" s="14"/>
+      <c r="C27" s="14"/>
+      <c r="D27" s="14"/>
+      <c r="E27" s="14"/>
+      <c r="F27" s="14"/>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F28" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>146</v>
+      </c>
+      <c r="B29" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" t="s">
         <v>148</v>
       </c>
-      <c r="B24" t="s">
+      <c r="D29" t="s">
+        <v>31</v>
+      </c>
+      <c r="E29" t="s">
+        <v>31</v>
+      </c>
+      <c r="F29" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" s="15">
+        <v>1</v>
+      </c>
+      <c r="B30" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" s="15" t="s">
+        <v>195</v>
+      </c>
+      <c r="D30" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E30" s="15">
+        <v>28.4</v>
+      </c>
+      <c r="F30" s="15" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
+        <v>67</v>
+      </c>
+      <c r="C31" t="s">
+        <v>197</v>
+      </c>
+      <c r="D31" t="s">
+        <v>50</v>
+      </c>
+      <c r="E31">
+        <v>11.3</v>
+      </c>
+      <c r="F31" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32" s="15">
+        <v>3</v>
+      </c>
+      <c r="B32" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="C32" s="15" t="s">
+        <v>198</v>
+      </c>
+      <c r="D32" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32" s="15">
+        <v>6.9</v>
+      </c>
+      <c r="F32" s="15" t="s">
         <v>164</v>
       </c>
-      <c r="C24" t="s">
-        <v>31</v>
-      </c>
-      <c r="D24" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24">
-        <v>27</v>
-      </c>
-      <c r="F24" t="s">
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A33">
+        <v>4</v>
+      </c>
+      <c r="B33" t="s">
+        <v>65</v>
+      </c>
+      <c r="C33" t="s">
+        <v>198</v>
+      </c>
+      <c r="D33" t="s">
+        <v>50</v>
+      </c>
+      <c r="E33">
+        <v>2.8</v>
+      </c>
+      <c r="F33" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A34" s="15">
+        <v>5</v>
+      </c>
+      <c r="B34" s="15" t="s">
+        <v>63</v>
+      </c>
+      <c r="C34" s="15" t="s">
+        <v>201</v>
+      </c>
+      <c r="D34" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E34" s="15">
+        <v>1.8</v>
+      </c>
+      <c r="F34" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A35">
+        <v>6</v>
+      </c>
+      <c r="B35" t="s">
+        <v>70</v>
+      </c>
+      <c r="C35" t="s">
+        <v>201</v>
+      </c>
+      <c r="D35" t="s">
+        <v>62</v>
+      </c>
+      <c r="E35">
+        <v>1.4</v>
+      </c>
+      <c r="F35" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A36" s="15">
+        <v>7</v>
+      </c>
+      <c r="B36" s="15" t="s">
+        <v>203</v>
+      </c>
+      <c r="C36" s="15" t="s">
+        <v>204</v>
+      </c>
+      <c r="D36" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E36" s="15">
+        <v>13.2</v>
+      </c>
+      <c r="F36" s="15" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>146</v>
+      </c>
+      <c r="B37" t="s">
+        <v>159</v>
+      </c>
+      <c r="C37" t="s">
+        <v>31</v>
+      </c>
+      <c r="D37" t="s">
+        <v>31</v>
+      </c>
+      <c r="E37">
+        <v>29.4</v>
+      </c>
+      <c r="F37" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A39" s="14" t="s">
+        <v>222</v>
+      </c>
+      <c r="B39" s="14"/>
+      <c r="C39" s="14"/>
+      <c r="D39" s="14"/>
+      <c r="E39" s="14"/>
+      <c r="F39" s="14"/>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E40" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F40" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>146</v>
+      </c>
+      <c r="B41" t="s">
+        <v>147</v>
+      </c>
+      <c r="C41" t="s">
+        <v>148</v>
+      </c>
+      <c r="D41" t="s">
+        <v>31</v>
+      </c>
+      <c r="E41" t="s">
+        <v>31</v>
+      </c>
+      <c r="F41" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" s="15">
+        <v>1</v>
+      </c>
+      <c r="B42" s="15" t="s">
+        <v>218</v>
+      </c>
+      <c r="C42" s="15" t="s">
+        <v>219</v>
+      </c>
+      <c r="D42" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="15">
+        <v>27.4</v>
+      </c>
+      <c r="F42" s="15" t="s">
         <v>220</v>
       </c>
     </row>
-    <row r="26" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="14" t="s">
-        <v>221</v>
-      </c>
-      <c r="B26" s="14"/>
-      <c r="C26" s="14"/>
-      <c r="D26" s="14"/>
-      <c r="E26" s="14"/>
-      <c r="F26" s="14"/>
-    </row>
-    <row r="27" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E27" s="4" t="s">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43">
+        <v>2</v>
+      </c>
+      <c r="B43" t="s">
+        <v>211</v>
+      </c>
+      <c r="C43" t="s">
+        <v>212</v>
+      </c>
+      <c r="D43" t="s">
+        <v>50</v>
+      </c>
+      <c r="E43">
+        <v>8.2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A44" s="15">
+        <v>3</v>
+      </c>
+      <c r="B44" s="15" t="s">
+        <v>215</v>
+      </c>
+      <c r="C44" s="15" t="s">
+        <v>214</v>
+      </c>
+      <c r="D44" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E44" s="15">
+        <v>8</v>
+      </c>
+      <c r="F44" s="15" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A45">
+        <v>4</v>
+      </c>
+      <c r="B45" t="s">
+        <v>216</v>
+      </c>
+      <c r="C45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D45" t="s">
+        <v>50</v>
+      </c>
+      <c r="E45">
+        <v>3.3</v>
+      </c>
+      <c r="F45" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A46" s="15">
+        <v>5</v>
+      </c>
+      <c r="B46" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C46" s="15" t="s">
+        <v>223</v>
+      </c>
+      <c r="D46" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E46" s="15">
+        <v>5.4</v>
+      </c>
+      <c r="F46" s="15" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
         <v>146</v>
       </c>
-      <c r="F27" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" t="s">
-        <v>148</v>
-      </c>
-      <c r="B28" t="s">
-        <v>149</v>
-      </c>
-      <c r="C28" t="s">
-        <v>150</v>
-      </c>
-      <c r="D28" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" t="s">
-        <v>31</v>
-      </c>
-      <c r="F28" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A29" s="15">
-        <v>1</v>
-      </c>
-      <c r="B29" s="15" t="s">
-        <v>195</v>
-      </c>
-      <c r="C29" s="15" t="s">
-        <v>196</v>
-      </c>
-      <c r="D29" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E29" s="15">
-        <v>28.4</v>
-      </c>
-      <c r="F29" s="15" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30">
-        <v>2</v>
-      </c>
-      <c r="B30" t="s">
-        <v>67</v>
-      </c>
-      <c r="C30" t="s">
-        <v>198</v>
-      </c>
-      <c r="D30" t="s">
-        <v>50</v>
-      </c>
-      <c r="E30">
-        <v>11.3</v>
-      </c>
-      <c r="F30" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="15">
-        <v>3</v>
-      </c>
-      <c r="B31" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="C31" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="D31" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E31" s="15">
-        <v>6.9</v>
-      </c>
-      <c r="F31" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32">
-        <v>4</v>
-      </c>
-      <c r="B32" t="s">
-        <v>65</v>
-      </c>
-      <c r="C32" t="s">
-        <v>199</v>
-      </c>
-      <c r="D32" t="s">
-        <v>50</v>
-      </c>
-      <c r="E32">
-        <v>2.8</v>
-      </c>
-      <c r="F32" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="15">
-        <v>5</v>
-      </c>
-      <c r="B33" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="C33" s="15" t="s">
-        <v>199</v>
-      </c>
-      <c r="D33" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E33" s="15">
-        <v>0.9</v>
-      </c>
-      <c r="F33" s="15" t="s">
-        <v>222</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A34">
-        <v>6</v>
-      </c>
-      <c r="B34" t="s">
-        <v>63</v>
-      </c>
-      <c r="C34" t="s">
-        <v>201</v>
-      </c>
-      <c r="D34" t="s">
-        <v>50</v>
-      </c>
-      <c r="E34">
-        <v>2.5</v>
-      </c>
-      <c r="F34" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A35" s="15">
-        <v>7</v>
-      </c>
-      <c r="B35" s="15" t="s">
-        <v>202</v>
-      </c>
-      <c r="C35" s="15" t="s">
-        <v>203</v>
-      </c>
-      <c r="D35" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E35" s="15">
-        <v>13.3</v>
-      </c>
-      <c r="F35" s="15" t="s">
-        <v>223</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A36" t="s">
-        <v>148</v>
-      </c>
-      <c r="B36" t="s">
-        <v>164</v>
-      </c>
-      <c r="C36" t="s">
-        <v>31</v>
-      </c>
-      <c r="D36" t="s">
-        <v>31</v>
-      </c>
-      <c r="E36">
-        <v>33.4</v>
-      </c>
-      <c r="F36" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="38" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38" s="14" t="s">
-        <v>224</v>
-      </c>
-      <c r="B38" s="14"/>
-      <c r="C38" s="14"/>
-      <c r="D38" s="14"/>
-      <c r="E38" s="14"/>
-      <c r="F38" s="14"/>
-    </row>
-    <row r="39" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D39" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E39" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F39" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>148</v>
-      </c>
-      <c r="B40" t="s">
-        <v>149</v>
-      </c>
-      <c r="C40" t="s">
-        <v>150</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40" t="s">
-        <v>31</v>
-      </c>
-      <c r="F40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A41" s="15">
-        <v>1</v>
-      </c>
-      <c r="B41" s="15" t="s">
-        <v>217</v>
-      </c>
-      <c r="C41" s="15" t="s">
-        <v>218</v>
-      </c>
-      <c r="D41" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E41" s="15">
-        <v>27.4</v>
-      </c>
-      <c r="F41" s="15" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42">
-        <v>2</v>
-      </c>
-      <c r="B42" t="s">
-        <v>87</v>
-      </c>
-      <c r="C42" t="s">
+      <c r="B47" t="s">
+        <v>159</v>
+      </c>
+      <c r="C47" t="s">
+        <v>31</v>
+      </c>
+      <c r="D47" t="s">
+        <v>31</v>
+      </c>
+      <c r="E47">
+        <v>34.8</v>
+      </c>
+      <c r="F47" t="s">
         <v>225</v>
-      </c>
-      <c r="D42" t="s">
-        <v>58</v>
-      </c>
-      <c r="E42">
-        <v>10.2</v>
-      </c>
-      <c r="F42" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="15">
-        <v>3</v>
-      </c>
-      <c r="B43" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C43" s="15" t="s">
-        <v>226</v>
-      </c>
-      <c r="D43" s="15" t="s">
-        <v>62</v>
-      </c>
-      <c r="E43" s="15">
-        <v>6.6</v>
-      </c>
-      <c r="F43" s="15" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44">
-        <v>4</v>
-      </c>
-      <c r="B44" t="s">
-        <v>212</v>
-      </c>
-      <c r="C44" t="s">
-        <v>213</v>
-      </c>
-      <c r="D44" t="s">
-        <v>50</v>
-      </c>
-      <c r="E44">
-        <v>6.9</v>
-      </c>
-      <c r="F44" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A45" s="15">
-        <v>5</v>
-      </c>
-      <c r="B45" s="15" t="s">
-        <v>215</v>
-      </c>
-      <c r="C45" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="D45" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E45" s="15">
-        <v>3.2</v>
-      </c>
-      <c r="F45" s="15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A46">
-        <v>6</v>
-      </c>
-      <c r="B46" t="s">
-        <v>209</v>
-      </c>
-      <c r="C46" t="s">
-        <v>210</v>
-      </c>
-      <c r="D46" t="s">
-        <v>50</v>
-      </c>
-      <c r="E46">
-        <v>6.4</v>
-      </c>
-      <c r="F46" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A47" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B47" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C47" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D47" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E47" s="15">
-        <v>29.4</v>
-      </c>
-      <c r="F47" s="15" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="49" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="14" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="B49" s="14"/>
       <c r="C49" s="14"/>
@@ -5399,33 +5390,33 @@
     </row>
     <row r="50" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C50" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D50" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E50" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F50" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
+        <v>146</v>
+      </c>
+      <c r="B51" t="s">
+        <v>147</v>
+      </c>
+      <c r="C51" t="s">
         <v>148</v>
-      </c>
-      <c r="B51" t="s">
-        <v>149</v>
-      </c>
-      <c r="C51" t="s">
-        <v>150</v>
       </c>
       <c r="D51" t="s">
         <v>31</v>
@@ -5442,10 +5433,10 @@
         <v>1</v>
       </c>
       <c r="B52" s="15" t="s">
+        <v>194</v>
+      </c>
+      <c r="C52" s="15" t="s">
         <v>195</v>
-      </c>
-      <c r="C52" s="15" t="s">
-        <v>196</v>
       </c>
       <c r="D52" s="15" t="s">
         <v>50</v>
@@ -5454,7 +5445,7 @@
         <v>28.4</v>
       </c>
       <c r="F52" s="15" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.25">
@@ -5465,7 +5456,7 @@
         <v>67</v>
       </c>
       <c r="C53" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="D53" t="s">
         <v>50</v>
@@ -5474,7 +5465,7 @@
         <v>11.3</v>
       </c>
       <c r="F53" t="s">
-        <v>155</v>
+        <v>166</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.25">
@@ -5482,19 +5473,19 @@
         <v>3</v>
       </c>
       <c r="B54" s="15" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C54" s="15" t="s">
+        <v>227</v>
+      </c>
+      <c r="D54" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E54" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="F54" s="15" t="s">
         <v>199</v>
-      </c>
-      <c r="D54" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E54" s="15">
-        <v>6.9</v>
-      </c>
-      <c r="F54" s="15" t="s">
-        <v>153</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.25">
@@ -5502,19 +5493,19 @@
         <v>4</v>
       </c>
       <c r="B55" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="D55" t="s">
         <v>50</v>
       </c>
       <c r="E55">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="F55" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.25">
@@ -5522,19 +5513,19 @@
         <v>5</v>
       </c>
       <c r="B56" s="15" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C56" s="15" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="D56" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E56" s="15">
-        <v>1.8</v>
+        <v>2.8</v>
       </c>
       <c r="F56" s="15" t="s">
-        <v>187</v>
+        <v>199</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.25">
@@ -5542,19 +5533,19 @@
         <v>6</v>
       </c>
       <c r="B57" t="s">
-        <v>202</v>
+        <v>63</v>
       </c>
       <c r="C57" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D57" t="s">
         <v>50</v>
       </c>
       <c r="E57">
-        <v>13.3</v>
+        <v>1.8</v>
       </c>
       <c r="F57" t="s">
-        <v>223</v>
+        <v>182</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
@@ -5562,27 +5553,27 @@
         <v>7</v>
       </c>
       <c r="B58" s="15" t="s">
-        <v>229</v>
+        <v>203</v>
       </c>
       <c r="C58" s="15" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="D58" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E58" s="15">
-        <v>0.4</v>
+        <v>13.9</v>
       </c>
       <c r="F58" s="15" t="s">
-        <v>176</v>
+        <v>205</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B59" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C59" t="s">
         <v>31</v>
@@ -5591,15 +5582,15 @@
         <v>31</v>
       </c>
       <c r="E59">
-        <v>30.7</v>
+        <v>29.4</v>
       </c>
       <c r="F59" t="s">
-        <v>230</v>
+        <v>206</v>
       </c>
     </row>
     <row r="61" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="14" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="B61" s="14"/>
       <c r="C61" s="14"/>
@@ -5609,33 +5600,33 @@
     </row>
     <row r="62" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C62" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D62" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E62" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F62" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" t="s">
+        <v>147</v>
+      </c>
+      <c r="C63" t="s">
         <v>148</v>
-      </c>
-      <c r="B63" t="s">
-        <v>149</v>
-      </c>
-      <c r="C63" t="s">
-        <v>150</v>
       </c>
       <c r="D63" t="s">
         <v>31</v>
@@ -5652,10 +5643,10 @@
         <v>1</v>
       </c>
       <c r="B64" s="15" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C64" s="15" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="D64" s="15" t="s">
         <v>50</v>
@@ -5672,19 +5663,19 @@
         <v>2</v>
       </c>
       <c r="B65" t="s">
-        <v>87</v>
+        <v>211</v>
       </c>
       <c r="C65" t="s">
-        <v>225</v>
+        <v>212</v>
       </c>
       <c r="D65" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E65">
-        <v>10.2</v>
+        <v>8.2</v>
       </c>
       <c r="F65" t="s">
-        <v>177</v>
+        <v>173</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.25">
@@ -5692,19 +5683,19 @@
         <v>3</v>
       </c>
       <c r="B66" s="15" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="C66" s="15" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D66" s="15" t="s">
         <v>62</v>
       </c>
       <c r="E66" s="15">
-        <v>9.6</v>
+        <v>0.4</v>
       </c>
       <c r="F66" s="15" t="s">
-        <v>233</v>
+        <v>179</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.25">
@@ -5712,19 +5703,19 @@
         <v>4</v>
       </c>
       <c r="B67" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="C67" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="D67" t="s">
         <v>50</v>
       </c>
       <c r="E67">
-        <v>0.5</v>
+        <v>10.1</v>
       </c>
       <c r="F67" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.25">
@@ -5732,10 +5723,10 @@
         <v>5</v>
       </c>
       <c r="B68" s="15" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="C68" s="15" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="D68" s="15" t="s">
         <v>50</v>
@@ -5744,7 +5735,7 @@
         <v>3.2</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.25">
@@ -5752,27 +5743,27 @@
         <v>6</v>
       </c>
       <c r="B69" t="s">
-        <v>209</v>
+        <v>87</v>
       </c>
       <c r="C69" t="s">
-        <v>210</v>
+        <v>223</v>
       </c>
       <c r="D69" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E69">
-        <v>6.4</v>
+        <v>5.1</v>
       </c>
       <c r="F69" t="s">
-        <v>153</v>
+        <v>224</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A70" s="15" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B70" s="15" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="C70" s="15" t="s">
         <v>31</v>
@@ -5781,10 +5772,10 @@
         <v>31</v>
       </c>
       <c r="E70" s="15">
-        <v>29.4</v>
+        <v>34.8</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
     </row>
   </sheetData>
@@ -5793,8 +5784,8 @@
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
     <mergeCell ref="A16:F16"/>
-    <mergeCell ref="A26:F26"/>
-    <mergeCell ref="A38:F38"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A39:F39"/>
     <mergeCell ref="A49:F49"/>
     <mergeCell ref="A61:F61"/>
   </mergeCells>
@@ -5817,7 +5808,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -5827,7 +5818,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -5837,7 +5828,7 @@
     </row>
     <row r="4" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="14" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B4" s="14"/>
       <c r="C4" s="14"/>
@@ -5847,33 +5838,33 @@
     </row>
     <row r="5" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C5" s="4" t="s">
         <v>143</v>
-      </c>
-      <c r="B5" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C5" s="4" t="s">
-        <v>145</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>45</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="B6" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C6" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="D6" t="s">
         <v>31</v>
@@ -5890,19 +5881,19 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>90</v>
+        <v>234</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E7" s="15">
-        <v>14.8</v>
+        <v>44.2</v>
       </c>
       <c r="F7" s="15" t="s">
-        <v>188</v>
+        <v>236</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
@@ -5910,19 +5901,19 @@
         <v>2</v>
       </c>
       <c r="B8" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="D8" t="s">
         <v>50</v>
       </c>
       <c r="E8">
-        <v>15.1</v>
+        <v>3</v>
       </c>
       <c r="F8" t="s">
-        <v>241</v>
+        <v>202</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
@@ -5930,19 +5921,19 @@
         <v>3</v>
       </c>
       <c r="B9" s="15" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D9" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E9" s="15">
-        <v>15.9</v>
+        <v>9.2</v>
       </c>
       <c r="F9" s="15" t="s">
-        <v>223</v>
+        <v>189</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -5950,19 +5941,19 @@
         <v>4</v>
       </c>
       <c r="B10" t="s">
-        <v>244</v>
+        <v>240</v>
       </c>
       <c r="C10" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
       <c r="D10" t="s">
         <v>50</v>
       </c>
       <c r="E10">
-        <v>9.2</v>
+        <v>4.7</v>
       </c>
       <c r="F10" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
@@ -5970,1109 +5961,1109 @@
         <v>5</v>
       </c>
       <c r="B11" s="15" t="s">
+        <v>242</v>
+      </c>
+      <c r="C11" s="15" t="s">
+        <v>241</v>
+      </c>
+      <c r="D11" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E11" s="15">
+        <v>1.9</v>
+      </c>
+      <c r="F11" s="15" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>146</v>
+      </c>
+      <c r="B12" t="s">
+        <v>159</v>
+      </c>
+      <c r="C12" t="s">
+        <v>31</v>
+      </c>
+      <c r="D12" t="s">
+        <v>31</v>
+      </c>
+      <c r="E12">
+        <v>29.8</v>
+      </c>
+      <c r="F12" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A14" s="14" t="s">
+        <v>243</v>
+      </c>
+      <c r="B14" s="14"/>
+      <c r="C14" s="14"/>
+      <c r="D14" s="14"/>
+      <c r="E14" s="14"/>
+      <c r="F14" s="14"/>
+    </row>
+    <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A15" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>146</v>
+      </c>
+      <c r="B16" t="s">
+        <v>147</v>
+      </c>
+      <c r="C16" t="s">
+        <v>233</v>
+      </c>
+      <c r="D16" t="s">
+        <v>31</v>
+      </c>
+      <c r="E16" t="s">
+        <v>31</v>
+      </c>
+      <c r="F16" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A17" s="15">
+        <v>1</v>
+      </c>
+      <c r="B17" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C17" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D17" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E17" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A18">
+        <v>2</v>
+      </c>
+      <c r="B18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C18" t="s">
+        <v>245</v>
+      </c>
+      <c r="D18" t="s">
+        <v>50</v>
+      </c>
+      <c r="E18">
+        <v>15.3</v>
+      </c>
+      <c r="F18" t="s">
         <v>246</v>
       </c>
-      <c r="C11" s="15" t="s">
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A19" s="15">
+        <v>3</v>
+      </c>
+      <c r="B19" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D19" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E19" s="15">
+        <v>15.1</v>
+      </c>
+      <c r="F19" s="15" t="s">
         <v>247</v>
       </c>
-      <c r="D11" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11" s="15">
-        <v>4.7</v>
-      </c>
-      <c r="F11" s="15" t="s">
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A20">
+        <v>4</v>
+      </c>
+      <c r="B20" t="s">
+        <v>81</v>
+      </c>
+      <c r="C20" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12">
+      <c r="D20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20">
+        <v>7.6</v>
+      </c>
+      <c r="F20" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A21" s="15">
+        <v>5</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="C21" s="15" t="s">
+        <v>248</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E21" s="15">
+        <v>3.6</v>
+      </c>
+      <c r="F21" s="15" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A22">
         <v>6</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B22" t="s">
+        <v>79</v>
+      </c>
+      <c r="C22" t="s">
+        <v>248</v>
+      </c>
+      <c r="D22" t="s">
+        <v>50</v>
+      </c>
+      <c r="E22">
+        <v>4.4</v>
+      </c>
+      <c r="F22" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A23" s="15">
+        <v>7</v>
+      </c>
+      <c r="B23" s="15" t="s">
         <v>249</v>
       </c>
-      <c r="C12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D12" t="s">
+      <c r="C23" s="15" t="s">
+        <v>250</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E23" s="15">
+        <v>3.5</v>
+      </c>
+      <c r="F23" s="15" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A24">
+        <v>8</v>
+      </c>
+      <c r="B24" t="s">
+        <v>75</v>
+      </c>
+      <c r="C24" t="s">
+        <v>233</v>
+      </c>
+      <c r="D24" t="s">
         <v>58</v>
       </c>
-      <c r="E12">
-        <v>1.9</v>
-      </c>
-      <c r="F12" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B13" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E13" s="15">
-        <v>29.8</v>
-      </c>
-      <c r="F13" s="15" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="15" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="14" t="s">
-        <v>250</v>
-      </c>
-      <c r="B15" s="14"/>
-      <c r="C15" s="14"/>
-      <c r="D15" s="14"/>
-      <c r="E15" s="14"/>
-      <c r="F15" s="14"/>
-    </row>
-    <row r="16" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="E24">
+        <v>5.5</v>
+      </c>
+      <c r="F24" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A25" s="15">
+        <v>9</v>
+      </c>
+      <c r="B25" s="15" t="s">
+        <v>252</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E25" s="15">
+        <v>3</v>
+      </c>
+      <c r="F25" s="15" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>146</v>
+      </c>
+      <c r="B26" t="s">
+        <v>159</v>
+      </c>
+      <c r="C26" t="s">
+        <v>31</v>
+      </c>
+      <c r="D26" t="s">
+        <v>31</v>
+      </c>
+      <c r="E26">
+        <v>0.3</v>
+      </c>
+      <c r="F26" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="28" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A28" s="14" t="s">
+        <v>253</v>
+      </c>
+      <c r="B28" s="14"/>
+      <c r="C28" s="14"/>
+      <c r="D28" s="14"/>
+      <c r="E28" s="14"/>
+      <c r="F28" s="14"/>
+    </row>
+    <row r="29" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A29" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C29" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="D29" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="F29" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E16" s="4" t="s">
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
         <v>146</v>
       </c>
-      <c r="F16" s="4" t="s">
+      <c r="B30" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>149</v>
-      </c>
-      <c r="C17" t="s">
-        <v>237</v>
-      </c>
-      <c r="D17" t="s">
-        <v>31</v>
-      </c>
-      <c r="E17" t="s">
-        <v>31</v>
-      </c>
-      <c r="F17" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="15">
+      <c r="C30" t="s">
+        <v>233</v>
+      </c>
+      <c r="D30" t="s">
+        <v>31</v>
+      </c>
+      <c r="E30" t="s">
+        <v>31</v>
+      </c>
+      <c r="F30" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A31" s="15">
         <v>1</v>
       </c>
-      <c r="B18" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="C18" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E18" s="15">
-        <v>3.1</v>
-      </c>
-      <c r="F18" s="15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19">
+      <c r="B31" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C31" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D31" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E31" s="15">
+        <v>14.8</v>
+      </c>
+      <c r="F31" s="15" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A32">
         <v>2</v>
       </c>
-      <c r="B19" t="s">
-        <v>251</v>
-      </c>
-      <c r="C19" t="s">
-        <v>237</v>
-      </c>
-      <c r="D19" t="s">
-        <v>62</v>
-      </c>
-      <c r="E19">
-        <v>3.8</v>
-      </c>
-      <c r="F19" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="15">
-        <v>3</v>
-      </c>
-      <c r="B20" s="15" t="s">
-        <v>252</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E20" s="15">
-        <v>13</v>
-      </c>
-      <c r="F20" s="15" t="s">
-        <v>254</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A21">
-        <v>4</v>
-      </c>
-      <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" t="s">
-        <v>237</v>
-      </c>
-      <c r="D21" t="s">
-        <v>50</v>
-      </c>
-      <c r="E21">
+      <c r="B32" t="s">
+        <v>255</v>
+      </c>
+      <c r="C32" t="s">
+        <v>256</v>
+      </c>
+      <c r="D32" t="s">
+        <v>50</v>
+      </c>
+      <c r="E32">
         <v>15.1</v>
       </c>
-      <c r="F21" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A22" s="15">
-        <v>5</v>
-      </c>
-      <c r="B22" s="15" t="s">
-        <v>81</v>
-      </c>
-      <c r="C22" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="D22" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E22" s="15">
-        <v>7.6</v>
-      </c>
-      <c r="F22" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A23">
-        <v>6</v>
-      </c>
-      <c r="B23" t="s">
-        <v>85</v>
-      </c>
-      <c r="C23" t="s">
-        <v>255</v>
-      </c>
-      <c r="D23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23">
-        <v>3.6</v>
-      </c>
-      <c r="F23" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A24" s="15">
-        <v>7</v>
-      </c>
-      <c r="B24" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E24" s="15">
-        <v>4.4</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A25">
-        <v>8</v>
-      </c>
-      <c r="B25" t="s">
-        <v>256</v>
-      </c>
-      <c r="C25" t="s">
+      <c r="F32" t="s">
         <v>257</v>
-      </c>
-      <c r="D25" t="s">
-        <v>62</v>
-      </c>
-      <c r="E25">
-        <v>3.5</v>
-      </c>
-      <c r="F25" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A26" s="15">
-        <v>9</v>
-      </c>
-      <c r="B26" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E26" s="15">
-        <v>5.5</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A27">
-        <v>10</v>
-      </c>
-      <c r="B27" t="s">
-        <v>259</v>
-      </c>
-      <c r="C27" t="s">
-        <v>237</v>
-      </c>
-      <c r="D27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27">
-        <v>3</v>
-      </c>
-      <c r="F27" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A28" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B28" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C28" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E28" s="15">
-        <v>0.3</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="30" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A30" s="14" t="s">
-        <v>260</v>
-      </c>
-      <c r="B30" s="14"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="14"/>
-      <c r="E30" s="14"/>
-      <c r="F30" s="14"/>
-    </row>
-    <row r="31" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A31" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E31" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F31" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>148</v>
-      </c>
-      <c r="B32" t="s">
-        <v>149</v>
-      </c>
-      <c r="C32" t="s">
-        <v>237</v>
-      </c>
-      <c r="D32" t="s">
-        <v>31</v>
-      </c>
-      <c r="E32" t="s">
-        <v>31</v>
-      </c>
-      <c r="F32" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B33" s="15" t="s">
-        <v>90</v>
+        <v>258</v>
       </c>
       <c r="C33" s="15" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="D33" s="15" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="E33" s="15">
-        <v>14.8</v>
+        <v>10.7</v>
       </c>
       <c r="F33" s="15" t="s">
-        <v>188</v>
+        <v>156</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B34" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="C34" t="s">
-        <v>247</v>
+        <v>235</v>
       </c>
       <c r="D34" t="s">
         <v>50</v>
       </c>
       <c r="E34">
-        <v>12</v>
+        <v>5.3</v>
       </c>
       <c r="F34" t="s">
-        <v>177</v>
+        <v>199</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B35" s="15" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="C35" s="15" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="D35" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E35" s="15">
-        <v>6.3</v>
+        <v>9.2</v>
       </c>
       <c r="F35" s="15" t="s">
-        <v>184</v>
+        <v>189</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B36" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="C36" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D36" t="s">
         <v>50</v>
       </c>
       <c r="E36">
-        <v>3.1</v>
+        <v>4.7</v>
       </c>
       <c r="F36" t="s">
-        <v>211</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B37" s="15" t="s">
-        <v>261</v>
+        <v>242</v>
       </c>
       <c r="C37" s="15" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="D37" s="15" t="s">
-        <v>62</v>
+        <v>58</v>
       </c>
       <c r="E37" s="15">
-        <v>0.9</v>
+        <v>1.9</v>
       </c>
       <c r="F37" s="15" t="s">
-        <v>262</v>
+        <v>169</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A38">
-        <v>6</v>
+      <c r="A38" t="s">
+        <v>146</v>
       </c>
       <c r="B38" t="s">
-        <v>263</v>
+        <v>159</v>
       </c>
       <c r="C38" t="s">
-        <v>243</v>
+        <v>31</v>
       </c>
       <c r="D38" t="s">
-        <v>62</v>
+        <v>31</v>
       </c>
       <c r="E38">
-        <v>9.8</v>
+        <v>29.8</v>
       </c>
       <c r="F38" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A39" s="15">
-        <v>7</v>
-      </c>
-      <c r="B39" s="15" t="s">
-        <v>242</v>
-      </c>
-      <c r="C39" s="15" t="s">
-        <v>243</v>
-      </c>
-      <c r="D39" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E39" s="15">
-        <v>5.3</v>
-      </c>
-      <c r="F39" s="15" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A40" t="s">
-        <v>148</v>
-      </c>
-      <c r="B40" t="s">
-        <v>164</v>
-      </c>
-      <c r="C40" t="s">
-        <v>31</v>
-      </c>
-      <c r="D40" t="s">
-        <v>31</v>
-      </c>
-      <c r="E40">
-        <v>41.8</v>
-      </c>
-      <c r="F40" t="s">
-        <v>264</v>
-      </c>
-    </row>
-    <row r="42" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A42" s="14" t="s">
-        <v>265</v>
-      </c>
-      <c r="B42" s="14"/>
-      <c r="C42" s="14"/>
-      <c r="D42" s="14"/>
-      <c r="E42" s="14"/>
-      <c r="F42" s="14"/>
-    </row>
-    <row r="43" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A43" s="4" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="40" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A40" s="14" t="s">
+        <v>259</v>
+      </c>
+      <c r="B40" s="14"/>
+      <c r="C40" s="14"/>
+      <c r="D40" s="14"/>
+      <c r="E40" s="14"/>
+      <c r="F40" s="14"/>
+    </row>
+    <row r="41" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A41" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>143</v>
       </c>
-      <c r="B43" s="4" t="s">
+      <c r="D41" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E41" s="4" t="s">
         <v>144</v>
       </c>
-      <c r="C43" s="4" t="s">
+      <c r="F41" s="4" t="s">
         <v>145</v>
       </c>
-      <c r="D43" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E43" s="4" t="s">
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
         <v>146</v>
       </c>
-      <c r="F43" s="4" t="s">
+      <c r="B42" t="s">
         <v>147</v>
       </c>
+      <c r="C42" t="s">
+        <v>233</v>
+      </c>
+      <c r="D42" t="s">
+        <v>31</v>
+      </c>
+      <c r="E42" t="s">
+        <v>31</v>
+      </c>
+      <c r="F42" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A43" s="15">
+        <v>1</v>
+      </c>
+      <c r="B43" s="15" t="s">
+        <v>75</v>
+      </c>
+      <c r="C43" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D43" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="E43" s="15">
+        <v>3</v>
+      </c>
+      <c r="F43" s="15" t="s">
+        <v>169</v>
+      </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>148</v>
+      <c r="A44">
+        <v>2</v>
       </c>
       <c r="B44" t="s">
-        <v>149</v>
+        <v>79</v>
       </c>
       <c r="C44" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D44" t="s">
-        <v>31</v>
-      </c>
-      <c r="E44" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="E44">
+        <v>8</v>
       </c>
       <c r="F44" t="s">
-        <v>31</v>
+        <v>189</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B45" s="15" t="s">
-        <v>82</v>
+        <v>85</v>
       </c>
       <c r="C45" s="15" t="s">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="D45" s="15" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="E45" s="15">
-        <v>3.1</v>
+        <v>5.5</v>
       </c>
       <c r="F45" s="15" t="s">
-        <v>200</v>
+        <v>152</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B46" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="C46" t="s">
-        <v>253</v>
+        <v>248</v>
       </c>
       <c r="D46" t="s">
         <v>50</v>
       </c>
       <c r="E46">
-        <v>14.9</v>
+        <v>2.3</v>
       </c>
       <c r="F46" t="s">
-        <v>223</v>
+        <v>260</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B47" s="15" t="s">
-        <v>266</v>
+        <v>83</v>
       </c>
       <c r="C47" s="15" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="D47" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E47" s="15">
-        <v>6.6</v>
+        <v>9.5</v>
       </c>
       <c r="F47" s="15" t="s">
-        <v>233</v>
+        <v>189</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A48">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B48" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="C48" t="s">
-        <v>253</v>
+        <v>233</v>
       </c>
       <c r="D48" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E48">
-        <v>6.5</v>
+        <v>4.8</v>
       </c>
       <c r="F48" t="s">
-        <v>184</v>
+        <v>224</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A49" s="15">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B49" s="15" t="s">
-        <v>83</v>
+        <v>244</v>
       </c>
       <c r="C49" s="15" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="D49" s="15" t="s">
         <v>50</v>
       </c>
       <c r="E49" s="15">
-        <v>15.1</v>
+        <v>13</v>
       </c>
       <c r="F49" s="15" t="s">
-        <v>219</v>
+        <v>262</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A50">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B50" t="s">
-        <v>81</v>
+        <v>84</v>
       </c>
       <c r="C50" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="D50" t="s">
         <v>50</v>
       </c>
       <c r="E50">
-        <v>7.6</v>
+        <v>10</v>
       </c>
       <c r="F50" t="s">
-        <v>174</v>
+        <v>262</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A51" s="15">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B51" s="15" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="C51" s="15" t="s">
-        <v>255</v>
+        <v>233</v>
       </c>
       <c r="D51" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E51" s="15">
+        <v>15.2</v>
+      </c>
+      <c r="F51" s="15" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>146</v>
+      </c>
+      <c r="B52" t="s">
+        <v>159</v>
+      </c>
+      <c r="C52" t="s">
+        <v>31</v>
+      </c>
+      <c r="D52" t="s">
+        <v>31</v>
+      </c>
+      <c r="E52">
+        <v>2.8</v>
+      </c>
+      <c r="F52" t="s">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="54" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A54" s="14" t="s">
+        <v>264</v>
+      </c>
+      <c r="B54" s="14"/>
+      <c r="C54" s="14"/>
+      <c r="D54" s="14"/>
+      <c r="E54" s="14"/>
+      <c r="F54" s="14"/>
+    </row>
+    <row r="55" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A55" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B55" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D55" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E55" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F55" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>146</v>
+      </c>
+      <c r="B56" t="s">
+        <v>147</v>
+      </c>
+      <c r="C56" t="s">
+        <v>233</v>
+      </c>
+      <c r="D56" t="s">
+        <v>31</v>
+      </c>
+      <c r="E56" t="s">
+        <v>31</v>
+      </c>
+      <c r="F56" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A57" s="15">
+        <v>1</v>
+      </c>
+      <c r="B57" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="C57" s="15" t="s">
+        <v>254</v>
+      </c>
+      <c r="D57" s="15" t="s">
         <v>58</v>
       </c>
-      <c r="E51" s="15">
-        <v>3.6</v>
-      </c>
-      <c r="F51" s="15" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A52">
-        <v>8</v>
-      </c>
-      <c r="B52" t="s">
-        <v>79</v>
-      </c>
-      <c r="C52" t="s">
-        <v>255</v>
-      </c>
-      <c r="D52" t="s">
-        <v>50</v>
-      </c>
-      <c r="E52">
-        <v>4.4</v>
-      </c>
-      <c r="F52" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A53" s="15">
-        <v>9</v>
-      </c>
-      <c r="B53" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="C53" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D53" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E53" s="15">
-        <v>8.9</v>
-      </c>
-      <c r="F53" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A54" t="s">
-        <v>148</v>
-      </c>
-      <c r="B54" t="s">
-        <v>164</v>
-      </c>
-      <c r="C54" t="s">
-        <v>31</v>
-      </c>
-      <c r="D54" t="s">
-        <v>31</v>
-      </c>
-      <c r="E54">
-        <v>2.5</v>
-      </c>
-      <c r="F54" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="56" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A56" s="14" t="s">
-        <v>267</v>
-      </c>
-      <c r="B56" s="14"/>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
-    </row>
-    <row r="57" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A57" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D57" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E57" s="4" t="s">
-        <v>146</v>
-      </c>
-      <c r="F57" s="4" t="s">
-        <v>147</v>
+      <c r="E57" s="15">
+        <v>14.8</v>
+      </c>
+      <c r="F57" s="15" t="s">
+        <v>186</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A58" t="s">
-        <v>148</v>
+      <c r="A58">
+        <v>2</v>
       </c>
       <c r="B58" t="s">
-        <v>149</v>
+        <v>240</v>
       </c>
       <c r="C58" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="D58" t="s">
-        <v>31</v>
-      </c>
-      <c r="E58" t="s">
-        <v>31</v>
+        <v>50</v>
+      </c>
+      <c r="E58">
+        <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>31</v>
+        <v>180</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A59" s="15">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="B59" s="15" t="s">
-        <v>268</v>
+        <v>238</v>
       </c>
       <c r="C59" s="15" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="D59" s="15" t="s">
-        <v>62</v>
+        <v>50</v>
       </c>
       <c r="E59" s="15">
-        <v>44.2</v>
+        <v>6.3</v>
       </c>
       <c r="F59" s="15" t="s">
-        <v>269</v>
+        <v>189</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A60">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="B60" t="s">
-        <v>242</v>
+        <v>255</v>
       </c>
       <c r="C60" t="s">
-        <v>243</v>
+        <v>256</v>
       </c>
       <c r="D60" t="s">
         <v>50</v>
       </c>
       <c r="E60">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="F60" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A61" s="15">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B61" s="15" t="s">
-        <v>244</v>
+        <v>265</v>
       </c>
       <c r="C61" s="15" t="s">
-        <v>245</v>
+        <v>256</v>
       </c>
       <c r="D61" s="15" t="s">
-        <v>50</v>
+        <v>62</v>
       </c>
       <c r="E61" s="15">
-        <v>9.2</v>
+        <v>0.9</v>
       </c>
       <c r="F61" s="15" t="s">
-        <v>184</v>
+        <v>266</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A62">
+        <v>6</v>
+      </c>
+      <c r="B62" t="s">
+        <v>237</v>
+      </c>
+      <c r="C62" t="s">
+        <v>235</v>
+      </c>
+      <c r="D62" t="s">
+        <v>50</v>
+      </c>
+      <c r="E62">
+        <v>15</v>
+      </c>
+      <c r="F62" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A63" s="15" t="s">
+        <v>146</v>
+      </c>
+      <c r="B63" s="15" t="s">
+        <v>159</v>
+      </c>
+      <c r="C63" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="D63" s="15" t="s">
+        <v>31</v>
+      </c>
+      <c r="E63" s="15">
+        <v>41.8</v>
+      </c>
+      <c r="F63" s="15" t="s">
+        <v>267</v>
+      </c>
+    </row>
+    <row r="65" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A65" s="14" t="s">
+        <v>268</v>
+      </c>
+      <c r="B65" s="14"/>
+      <c r="C65" s="14"/>
+      <c r="D65" s="14"/>
+      <c r="E65" s="14"/>
+      <c r="F65" s="14"/>
+    </row>
+    <row r="66" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A66" s="4" t="s">
+        <v>141</v>
+      </c>
+      <c r="B66" s="4" t="s">
+        <v>142</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>143</v>
+      </c>
+      <c r="D66" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="E66" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F66" s="4" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>146</v>
+      </c>
+      <c r="B67" t="s">
+        <v>147</v>
+      </c>
+      <c r="C67" t="s">
+        <v>233</v>
+      </c>
+      <c r="D67" t="s">
+        <v>31</v>
+      </c>
+      <c r="E67" t="s">
+        <v>31</v>
+      </c>
+      <c r="F67" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A68" s="15">
+        <v>1</v>
+      </c>
+      <c r="B68" s="15" t="s">
+        <v>82</v>
+      </c>
+      <c r="C68" s="15" t="s">
+        <v>233</v>
+      </c>
+      <c r="D68" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E68" s="15">
+        <v>3.1</v>
+      </c>
+      <c r="F68" s="15" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A69">
+        <v>2</v>
+      </c>
+      <c r="B69" t="s">
+        <v>84</v>
+      </c>
+      <c r="C69" t="s">
+        <v>245</v>
+      </c>
+      <c r="D69" t="s">
+        <v>50</v>
+      </c>
+      <c r="E69">
+        <v>14.9</v>
+      </c>
+      <c r="F69" t="s">
+        <v>205</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A70" s="15">
+        <v>3</v>
+      </c>
+      <c r="B70" s="15" t="s">
+        <v>269</v>
+      </c>
+      <c r="C70" s="15" t="s">
+        <v>245</v>
+      </c>
+      <c r="D70" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="E70" s="15">
+        <v>6.6</v>
+      </c>
+      <c r="F70" s="15" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A71">
         <v>4</v>
       </c>
-      <c r="B62" t="s">
-        <v>246</v>
-      </c>
-      <c r="C62" t="s">
-        <v>247</v>
-      </c>
-      <c r="D62" t="s">
-        <v>50</v>
-      </c>
-      <c r="E62">
-        <v>4.7</v>
-      </c>
-      <c r="F62" t="s">
+      <c r="B71" t="s">
+        <v>83</v>
+      </c>
+      <c r="C71" t="s">
+        <v>233</v>
+      </c>
+      <c r="D71" t="s">
+        <v>50</v>
+      </c>
+      <c r="E71">
+        <v>17.4</v>
+      </c>
+      <c r="F71" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A72" s="15">
+        <v>5</v>
+      </c>
+      <c r="B72" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C72" s="15" t="s">
         <v>248</v>
       </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A63" s="15">
-        <v>5</v>
-      </c>
-      <c r="B63" s="15" t="s">
-        <v>249</v>
-      </c>
-      <c r="C63" s="15" t="s">
-        <v>247</v>
-      </c>
-      <c r="D63" s="15" t="s">
-        <v>58</v>
-      </c>
-      <c r="E63" s="15">
-        <v>1.9</v>
-      </c>
-      <c r="F63" s="15" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A64" t="s">
-        <v>148</v>
-      </c>
-      <c r="B64" t="s">
-        <v>164</v>
-      </c>
-      <c r="C64" t="s">
-        <v>31</v>
-      </c>
-      <c r="D64" t="s">
-        <v>31</v>
-      </c>
-      <c r="E64">
-        <v>29.8</v>
-      </c>
-      <c r="F64" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="66" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A66" s="14" t="s">
-        <v>270</v>
-      </c>
-      <c r="B66" s="14"/>
-      <c r="C66" s="14"/>
-      <c r="D66" s="14"/>
-      <c r="E66" s="14"/>
-      <c r="F66" s="14"/>
-    </row>
-    <row r="67" ht="20" customHeight="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A67" s="4" t="s">
-        <v>143</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>144</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="D67" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="E67" s="4" t="s">
+      <c r="D72" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="E72" s="15">
+        <v>7.6</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
         <v>146</v>
       </c>
-      <c r="F67" s="4" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A68" t="s">
-        <v>148</v>
-      </c>
-      <c r="B68" t="s">
-        <v>149</v>
-      </c>
-      <c r="C68" t="s">
-        <v>237</v>
-      </c>
-      <c r="D68" t="s">
-        <v>31</v>
-      </c>
-      <c r="E68" t="s">
-        <v>31</v>
-      </c>
-      <c r="F68" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="69" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A69" s="15">
-        <v>1</v>
-      </c>
-      <c r="B69" s="15" t="s">
-        <v>84</v>
-      </c>
-      <c r="C69" s="15" t="s">
-        <v>253</v>
-      </c>
-      <c r="D69" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E69" s="15">
-        <v>17</v>
-      </c>
-      <c r="F69" s="15" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="70" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A70">
-        <v>2</v>
-      </c>
-      <c r="B70" t="s">
-        <v>82</v>
-      </c>
-      <c r="C70" t="s">
-        <v>237</v>
-      </c>
-      <c r="D70" t="s">
-        <v>50</v>
-      </c>
-      <c r="E70">
-        <v>15.2</v>
-      </c>
-      <c r="F70" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A71" s="15">
-        <v>3</v>
-      </c>
-      <c r="B71" s="15" t="s">
-        <v>83</v>
-      </c>
-      <c r="C71" s="15" t="s">
-        <v>237</v>
-      </c>
-      <c r="D71" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="E71" s="15">
-        <v>7.7</v>
-      </c>
-      <c r="F71" s="15" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A72">
-        <v>4</v>
-      </c>
-      <c r="B72" t="s">
-        <v>81</v>
-      </c>
-      <c r="C72" t="s">
-        <v>255</v>
-      </c>
-      <c r="D72" t="s">
-        <v>50</v>
-      </c>
-      <c r="E72">
-        <v>7.6</v>
-      </c>
-      <c r="F72" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="73" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A73" s="15" t="s">
-        <v>148</v>
-      </c>
-      <c r="B73" s="15" t="s">
-        <v>164</v>
-      </c>
-      <c r="C73" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D73" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="E73" s="15">
+      <c r="B73" t="s">
+        <v>159</v>
+      </c>
+      <c r="C73" t="s">
+        <v>31</v>
+      </c>
+      <c r="D73" t="s">
+        <v>31</v>
+      </c>
+      <c r="E73">
         <v>12.8</v>
       </c>
-      <c r="F73" s="15" t="s">
-        <v>177</v>
+      <c r="F73" t="s">
+        <v>180</v>
       </c>
     </row>
   </sheetData>
@@ -7080,11 +7071,11 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A15:F15"/>
-    <mergeCell ref="A30:F30"/>
-    <mergeCell ref="A42:F42"/>
-    <mergeCell ref="A56:F56"/>
-    <mergeCell ref="A66:F66"/>
+    <mergeCell ref="A14:F14"/>
+    <mergeCell ref="A28:F28"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A54:F54"/>
+    <mergeCell ref="A65:F65"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
@@ -7110,7 +7101,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -7130,57 +7121,57 @@
         <v>45</v>
       </c>
       <c r="C3" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>273</v>
+      </c>
+      <c r="F3" s="4" t="s">
         <v>274</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>276</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>277</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="J3" s="4" t="s">
         <v>278</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>279</v>
-      </c>
-      <c r="I3" s="4" t="s">
-        <v>280</v>
-      </c>
-      <c r="J3" s="4" t="s">
-        <v>281</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="B4" t="s">
         <v>50</v>
       </c>
       <c r="C4" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D4" t="s">
-        <v>245</v>
+        <v>239</v>
       </c>
       <c r="E4" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F4" t="s">
         <v>80</v>
       </c>
       <c r="G4" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H4" t="s">
         <v>80</v>
       </c>
       <c r="I4" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J4" t="s">
         <v>76</v>
@@ -7194,25 +7185,25 @@
         <v>50</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F5" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H5" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J5" s="11" t="s">
         <v>76</v>
@@ -7226,25 +7217,25 @@
         <v>50</v>
       </c>
       <c r="C6" s="11" t="s">
+        <v>283</v>
+      </c>
+      <c r="D6" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="E6" s="11" t="s">
         <v>286</v>
-      </c>
-      <c r="D6" s="11" t="s">
-        <v>255</v>
-      </c>
-      <c r="E6" s="11" t="s">
-        <v>289</v>
       </c>
       <c r="F6" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H6" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I6" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J6" s="11" t="s">
         <v>76</v>
@@ -7252,31 +7243,31 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="B7" t="s">
         <v>50</v>
       </c>
       <c r="C7" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D7" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E7" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="F7" t="s">
         <v>80</v>
       </c>
       <c r="G7" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H7" t="s">
         <v>80</v>
       </c>
       <c r="I7" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J7" t="s">
         <v>76</v>
@@ -7290,57 +7281,57 @@
         <v>50</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D8" s="9" t="s">
         <v>201</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H8" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I8" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J8" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="B9" t="s">
         <v>50</v>
       </c>
       <c r="C9" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D9" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E9" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="F9" t="s">
         <v>80</v>
       </c>
       <c r="G9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H9" t="s">
         <v>80</v>
       </c>
       <c r="I9" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J9" t="s">
         <v>51</v>
@@ -7348,31 +7339,31 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="B10" t="s">
         <v>50</v>
       </c>
       <c r="C10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D10" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="E10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="F10" t="s">
         <v>80</v>
       </c>
       <c r="G10" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H10" t="s">
         <v>80</v>
       </c>
       <c r="I10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J10" t="s">
         <v>51</v>
@@ -7380,31 +7371,31 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B11" t="s">
         <v>50</v>
       </c>
       <c r="C11" t="s">
+        <v>293</v>
+      </c>
+      <c r="D11" t="s">
+        <v>219</v>
+      </c>
+      <c r="E11" t="s">
         <v>296</v>
-      </c>
-      <c r="D11" t="s">
-        <v>218</v>
-      </c>
-      <c r="E11" t="s">
-        <v>299</v>
       </c>
       <c r="F11" t="s">
         <v>80</v>
       </c>
       <c r="G11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H11" t="s">
         <v>80</v>
       </c>
       <c r="I11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J11" t="s">
         <v>51</v>
@@ -7418,25 +7409,25 @@
         <v>50</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D12" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F12" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G12" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H12" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I12" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J12" s="11" t="s">
         <v>76</v>
@@ -7444,31 +7435,31 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
+        <v>194</v>
+      </c>
+      <c r="B13" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" t="s">
+        <v>293</v>
+      </c>
+      <c r="D13" t="s">
         <v>195</v>
       </c>
-      <c r="B13" t="s">
-        <v>50</v>
-      </c>
-      <c r="C13" t="s">
-        <v>296</v>
-      </c>
-      <c r="D13" t="s">
-        <v>196</v>
-      </c>
       <c r="E13" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="F13" t="s">
         <v>80</v>
       </c>
       <c r="G13" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H13" t="s">
         <v>80</v>
       </c>
       <c r="I13" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J13" t="s">
         <v>51</v>
@@ -7482,28 +7473,28 @@
         <v>50</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
       <c r="F14" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G14" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H14" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I14" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J14" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
@@ -7514,57 +7505,57 @@
         <v>50</v>
       </c>
       <c r="C15" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="D15" s="9" t="s">
+        <v>157</v>
+      </c>
+      <c r="E15" s="9" t="s">
         <v>302</v>
-      </c>
-      <c r="D15" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="E15" s="9" t="s">
-        <v>305</v>
       </c>
       <c r="F15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G15" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H15" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I15" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J15" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>239</v>
+        <v>255</v>
       </c>
       <c r="B16" t="s">
         <v>50</v>
       </c>
       <c r="C16" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D16" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="E16" t="s">
-        <v>306</v>
+        <v>303</v>
       </c>
       <c r="F16" t="s">
         <v>78</v>
       </c>
       <c r="G16" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H16" t="s">
         <v>78</v>
       </c>
       <c r="I16" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J16" t="s">
         <v>76</v>
@@ -7572,31 +7563,31 @@
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="B17" t="s">
         <v>50</v>
       </c>
       <c r="C17" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D17" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E17" t="s">
-        <v>308</v>
+        <v>305</v>
       </c>
       <c r="F17" t="s">
         <v>80</v>
       </c>
       <c r="G17" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H17" t="s">
         <v>80</v>
       </c>
       <c r="I17" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J17" t="s">
         <v>76</v>
@@ -7610,28 +7601,28 @@
         <v>50</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G18" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H18" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I18" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J18" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.25">
@@ -7642,28 +7633,28 @@
         <v>50</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>310</v>
+        <v>307</v>
       </c>
       <c r="F19" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G19" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H19" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I19" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J19" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.25">
@@ -7674,25 +7665,25 @@
         <v>50</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D20" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="F20" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G20" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H20" s="11" t="s">
         <v>80</v>
       </c>
       <c r="I20" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J20" s="11" t="s">
         <v>76</v>
@@ -7700,31 +7691,31 @@
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="B21" t="s">
         <v>50</v>
       </c>
       <c r="C21" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D21" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E21" t="s">
-        <v>312</v>
+        <v>309</v>
       </c>
       <c r="F21" t="s">
         <v>80</v>
       </c>
       <c r="G21" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H21" t="s">
         <v>80</v>
       </c>
       <c r="I21" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J21" t="s">
         <v>51</v>
@@ -7732,31 +7723,31 @@
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>156</v>
+        <v>167</v>
       </c>
       <c r="B22" t="s">
         <v>50</v>
       </c>
       <c r="C22" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D22" t="s">
-        <v>157</v>
+        <v>168</v>
       </c>
       <c r="E22" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="F22" t="s">
         <v>80</v>
       </c>
       <c r="G22" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H22" t="s">
         <v>80</v>
       </c>
       <c r="I22" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J22" t="s">
         <v>52</v>
@@ -7764,31 +7755,31 @@
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
       <c r="B23" t="s">
         <v>50</v>
       </c>
       <c r="C23" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D23" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E23" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
       <c r="F23" t="s">
         <v>80</v>
       </c>
       <c r="G23" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H23" t="s">
         <v>80</v>
       </c>
       <c r="I23" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J23" t="s">
         <v>52</v>
@@ -7796,31 +7787,31 @@
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="B24" t="s">
         <v>50</v>
       </c>
       <c r="C24" t="s">
+        <v>310</v>
+      </c>
+      <c r="D24" t="s">
+        <v>149</v>
+      </c>
+      <c r="E24" t="s">
         <v>313</v>
-      </c>
-      <c r="D24" t="s">
-        <v>160</v>
-      </c>
-      <c r="E24" t="s">
-        <v>316</v>
       </c>
       <c r="F24" t="s">
         <v>80</v>
       </c>
       <c r="G24" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H24" t="s">
         <v>80</v>
       </c>
       <c r="I24" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J24" t="s">
         <v>52</v>
@@ -7828,31 +7819,31 @@
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>151</v>
+        <v>162</v>
       </c>
       <c r="B25" t="s">
         <v>50</v>
       </c>
       <c r="C25" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D25" t="s">
-        <v>152</v>
+        <v>163</v>
       </c>
       <c r="E25" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F25" t="s">
         <v>80</v>
       </c>
       <c r="G25" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H25" t="s">
         <v>80</v>
       </c>
       <c r="I25" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="J25" t="s">
         <v>52</v>
@@ -7860,31 +7851,31 @@
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s">
         <v>50</v>
       </c>
       <c r="C26" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D26" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="E26" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="F26" t="s">
         <v>80</v>
       </c>
       <c r="G26" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H26" t="s">
         <v>80</v>
       </c>
       <c r="I26" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="J26" t="s">
         <v>51</v>
@@ -7898,57 +7889,57 @@
         <v>50</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="E27" s="9" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="F27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G27" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H27" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I27" s="9" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="J27" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="B28" t="s">
         <v>50</v>
       </c>
       <c r="C28" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D28" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E28" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F28" t="s">
         <v>78</v>
       </c>
       <c r="G28" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
       <c r="H28" t="s">
         <v>78</v>
       </c>
       <c r="I28" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J28" t="s">
         <v>76</v>
@@ -7962,25 +7953,25 @@
         <v>50</v>
       </c>
       <c r="C29" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D29" s="11" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E29" s="11" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="F29" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G29" s="11" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="H29" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I29" s="11" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J29" s="11" t="s">
         <v>76</v>
@@ -7994,28 +7985,28 @@
         <v>50</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E30" s="9" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="F30" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G30" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H30" s="9" t="s">
         <v>80</v>
       </c>
       <c r="I30" s="9" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="J30" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.25">
@@ -8026,25 +8017,25 @@
         <v>58</v>
       </c>
       <c r="C31" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D31" s="11" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="E31" s="11" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="F31" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G31" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H31" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I31" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J31" s="11" t="s">
         <v>76</v>
@@ -8058,25 +8049,25 @@
         <v>58</v>
       </c>
       <c r="C32" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D32" s="11" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="E32" s="11" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="F32" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G32" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H32" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I32" s="11" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="J32" s="11" t="s">
         <v>52</v>
@@ -8090,25 +8081,25 @@
         <v>58</v>
       </c>
       <c r="C33" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D33" s="11" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E33" s="11" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
       <c r="F33" s="11" t="s">
         <v>77</v>
       </c>
       <c r="G33" s="11" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="H33" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I33" s="11" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="J33" s="11" t="s">
         <v>76</v>
@@ -8122,28 +8113,28 @@
         <v>58</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>183</v>
+        <v>153</v>
       </c>
       <c r="E34" s="9" t="s">
-        <v>330</v>
+        <v>327</v>
       </c>
       <c r="F34" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G34" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H34" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I34" s="9" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="J34" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="35" spans="1:10" x14ac:dyDescent="0.25">
@@ -8154,28 +8145,28 @@
         <v>58</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>169</v>
+        <v>155</v>
       </c>
       <c r="E35" s="9" t="s">
-        <v>331</v>
+        <v>328</v>
       </c>
       <c r="F35" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G35" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H35" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I35" s="9" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="J35" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="36" spans="1:10" x14ac:dyDescent="0.25">
@@ -8186,25 +8177,25 @@
         <v>58</v>
       </c>
       <c r="C36" s="11" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D36" s="11" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E36" s="11" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="F36" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G36" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H36" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I36" s="11" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
       <c r="J36" s="11" t="s">
         <v>51</v>
@@ -8218,25 +8209,25 @@
         <v>58</v>
       </c>
       <c r="C37" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D37" s="11" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="E37" s="11" t="s">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="F37" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G37" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H37" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I37" s="11" t="s">
-        <v>335</v>
+        <v>321</v>
       </c>
       <c r="J37" s="11" t="s">
         <v>52</v>
@@ -8250,25 +8241,25 @@
         <v>58</v>
       </c>
       <c r="C38" s="11" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D38" s="11" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
       <c r="E38" s="11" t="s">
-        <v>336</v>
+        <v>332</v>
       </c>
       <c r="F38" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G38" s="11" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H38" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I38" s="11" t="s">
-        <v>307</v>
+        <v>333</v>
       </c>
       <c r="J38" s="11" t="s">
         <v>52</v>
@@ -8282,25 +8273,25 @@
         <v>58</v>
       </c>
       <c r="C39" s="11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D39" s="11" t="s">
-        <v>238</v>
+        <v>254</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>80</v>
       </c>
       <c r="G39" s="11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="H39" s="11" t="s">
         <v>78</v>
       </c>
       <c r="I39" s="11" t="s">
-        <v>307</v>
+        <v>304</v>
       </c>
       <c r="J39" s="11" t="s">
         <v>76</v>
@@ -8314,57 +8305,57 @@
         <v>58</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="E40" s="9" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="F40" s="9" t="s">
         <v>80</v>
       </c>
       <c r="G40" s="9" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="H40" s="9" t="s">
         <v>78</v>
       </c>
       <c r="I40" s="9" t="s">
-        <v>288</v>
+        <v>304</v>
       </c>
       <c r="J40" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="B41" t="s">
         <v>58</v>
       </c>
       <c r="C41" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D41" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E41" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="F41" t="s">
         <v>78</v>
       </c>
       <c r="G41" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="H41" t="s">
         <v>78</v>
       </c>
       <c r="I41" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="J41" t="s">
         <v>76</v>
@@ -8372,31 +8363,31 @@
     </row>
     <row r="42" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>263</v>
+        <v>258</v>
       </c>
       <c r="B42" t="s">
         <v>62</v>
       </c>
       <c r="C42" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D42" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E42" t="s">
+        <v>337</v>
+      </c>
+      <c r="F42" t="s">
+        <v>338</v>
+      </c>
+      <c r="G42" t="s">
+        <v>339</v>
+      </c>
+      <c r="H42" t="s">
+        <v>338</v>
+      </c>
+      <c r="I42" t="s">
         <v>340</v>
-      </c>
-      <c r="F42" t="s">
-        <v>341</v>
-      </c>
-      <c r="G42" t="s">
-        <v>342</v>
-      </c>
-      <c r="H42" t="s">
-        <v>341</v>
-      </c>
-      <c r="I42" t="s">
-        <v>343</v>
       </c>
       <c r="J42" t="s">
         <v>76</v>
@@ -8410,28 +8401,28 @@
         <v>62</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="E43" s="9" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="F43" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G43" s="9" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H43" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I43" s="9" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="J43" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="44" spans="1:10" x14ac:dyDescent="0.25">
@@ -8442,25 +8433,25 @@
         <v>62</v>
       </c>
       <c r="C44" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D44" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="E44" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
       <c r="F44" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G44" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H44" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I44" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="J44" t="s">
         <v>51</v>
@@ -8468,31 +8459,31 @@
     </row>
     <row r="45" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="B45" t="s">
         <v>62</v>
       </c>
       <c r="C45" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D45" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E45" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="F45" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G45" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H45" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I45" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J45" t="s">
         <v>76</v>
@@ -8506,57 +8497,57 @@
         <v>62</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>190</v>
+        <v>151</v>
       </c>
       <c r="E46" s="9" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="F46" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G46" s="9" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="H46" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I46" s="9" t="s">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="J46" s="9" t="s">
-        <v>304</v>
+        <v>301</v>
       </c>
     </row>
     <row r="47" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B47" t="s">
         <v>62</v>
       </c>
       <c r="C47" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="D47" t="s">
-        <v>240</v>
+        <v>256</v>
       </c>
       <c r="E47" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="F47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G47" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H47" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I47" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="J47" t="s">
         <v>76</v>
@@ -8564,31 +8555,31 @@
     </row>
     <row r="48" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>268</v>
+        <v>234</v>
       </c>
       <c r="B48" t="s">
         <v>62</v>
       </c>
       <c r="C48" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="D48" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="E48" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="F48" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G48" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="H48" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I48" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="J48" t="s">
         <v>76</v>
@@ -8596,31 +8587,31 @@
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>232</v>
+        <v>213</v>
       </c>
       <c r="B49" t="s">
         <v>62</v>
       </c>
       <c r="C49" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D49" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="E49" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="F49" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G49" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H49" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I49" t="s">
-        <v>351</v>
+        <v>339</v>
       </c>
       <c r="J49" t="s">
         <v>51</v>
@@ -8628,31 +8619,31 @@
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>159</v>
+        <v>185</v>
       </c>
       <c r="B50" t="s">
         <v>62</v>
       </c>
       <c r="C50" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
       <c r="D50" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="E50" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="F50" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G50" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="H50" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I50" t="s">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="J50" t="s">
         <v>52</v>
@@ -8660,28 +8651,28 @@
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
       <c r="B51" t="s">
         <v>62</v>
       </c>
       <c r="C51" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D51" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="E51" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="F51" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G51" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H51" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I51" t="s">
         <v>345</v>
@@ -8692,31 +8683,31 @@
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="B52" t="s">
         <v>62</v>
       </c>
       <c r="C52" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D52" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="E52" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="F52" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G52" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H52" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I52" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J52" t="s">
         <v>76</v>
@@ -8730,57 +8721,57 @@
         <v>62</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E53" s="9" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="F53" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G53" s="9" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="H53" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I53" s="9" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="J53" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
       <c r="B54" t="s">
         <v>62</v>
       </c>
       <c r="C54" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="D54" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="E54" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="F54" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G54" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H54" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I54" t="s">
-        <v>342</v>
+        <v>349</v>
       </c>
       <c r="J54" t="s">
         <v>76</v>
@@ -8794,57 +8785,57 @@
         <v>62</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="D55" s="9" t="s">
         <v>201</v>
       </c>
       <c r="E55" s="9" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="F55" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G55" s="9" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="H55" s="9" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I55" s="9" t="s">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="J55" s="9" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="B56" t="s">
         <v>62</v>
       </c>
       <c r="C56" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="D56" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="E56" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="F56" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="G56" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
       <c r="H56" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="I56" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="J56" t="s">
         <v>51</v>
@@ -8852,7 +8843,7 @@
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B58" s="2"/>
       <c r="C58" s="2"/>
@@ -8886,7 +8877,7 @@
   <sheetData>
     <row r="1" ht="24" customHeight="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="B1" s="1"/>
       <c r="C1" s="1"/>
@@ -8894,7 +8885,7 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -8911,7 +8902,7 @@
         <v>11</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
@@ -8925,7 +8916,7 @@
         <v>6</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
@@ -8936,10 +8927,10 @@
         <v>104</v>
       </c>
       <c r="C6">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
@@ -8953,7 +8944,7 @@
         <v>6</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
@@ -8967,7 +8958,7 @@
         <v>6</v>
       </c>
       <c r="D8" s="16" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
@@ -8978,10 +8969,10 @@
         <v>112</v>
       </c>
       <c r="C9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D9" s="16" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
@@ -8995,7 +8986,7 @@
         <v>6</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
@@ -9009,7 +9000,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
@@ -9020,10 +9011,10 @@
         <v>104</v>
       </c>
       <c r="C13">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D13" s="16" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.25">
@@ -9037,7 +9028,7 @@
         <v>7</v>
       </c>
       <c r="D14" s="16" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.25">
@@ -9048,10 +9039,10 @@
         <v>110</v>
       </c>
       <c r="C15">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D15" s="16" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.25">
@@ -9065,7 +9056,7 @@
         <v>7</v>
       </c>
       <c r="D16" s="16" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.25">
@@ -9079,7 +9070,7 @@
         <v>6</v>
       </c>
       <c r="D17" s="16" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.25">
@@ -9090,10 +9081,10 @@
         <v>100</v>
       </c>
       <c r="C19">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D19" s="16" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.25">
@@ -9104,10 +9095,10 @@
         <v>104</v>
       </c>
       <c r="C20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="D20" s="16" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.25">
@@ -9121,7 +9112,7 @@
         <v>7</v>
       </c>
       <c r="D21" s="16" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
@@ -9135,7 +9126,7 @@
         <v>9</v>
       </c>
       <c r="D22" s="16" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.25">
@@ -9146,10 +9137,10 @@
         <v>112</v>
       </c>
       <c r="C23">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D23" s="16" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.25">
@@ -9160,10 +9151,10 @@
         <v>115</v>
       </c>
       <c r="C24">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D24" s="16" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
   </sheetData>
